--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="184">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -430,6 +430,15 @@
     <t>['5']</t>
   </si>
   <si>
+    <t>['23', '46']</t>
+  </si>
+  <si>
+    <t>['9', '41']</t>
+  </si>
+  <si>
+    <t>['7', '41', '65', '70', '90']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -554,6 +563,9 @@
   </si>
   <si>
     <t>['34', '38', '79']</t>
+  </si>
+  <si>
+    <t>['24', '33', '76']</t>
   </si>
 </sst>
 </file>
@@ -915,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP91"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1249,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ2">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1789,7 +1801,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -1867,10 +1879,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ5">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2073,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2407,7 +2419,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2900,7 +2912,7 @@
         <v>2</v>
       </c>
       <c r="AQ10">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3106,7 +3118,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ11">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>1.27</v>
@@ -3231,7 +3243,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3721,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>1.88</v>
@@ -3927,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ15">
         <v>0.11</v>
@@ -4055,7 +4067,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4136,7 +4148,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ16">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR16">
         <v>1.76</v>
@@ -4467,7 +4479,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4545,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ18">
         <v>0.78</v>
@@ -4751,7 +4763,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ19">
         <v>0.89</v>
@@ -5085,7 +5097,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5166,7 +5178,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ21">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR21">
         <v>1.05</v>
@@ -5291,7 +5303,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5372,7 +5384,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ22">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5703,7 +5715,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5909,7 +5921,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -5987,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ25">
         <v>1.33</v>
@@ -6321,7 +6333,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6605,7 +6617,7 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ28">
         <v>2.33</v>
@@ -6733,7 +6745,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6811,10 +6823,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ29">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7145,7 +7157,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7226,7 +7238,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ31">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>1.26</v>
@@ -7432,7 +7444,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -7635,10 +7647,10 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ33">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8047,7 +8059,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ35">
         <v>0.89</v>
@@ -8256,7 +8268,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ36">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR36">
         <v>1.75</v>
@@ -8381,7 +8393,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8668,7 +8680,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
         <v>1.19</v>
@@ -8793,7 +8805,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -8871,7 +8883,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ39">
         <v>0.11</v>
@@ -9077,7 +9089,7 @@
         <v>2.25</v>
       </c>
       <c r="AP40">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ40">
         <v>2</v>
@@ -9283,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ41">
         <v>1.44</v>
@@ -9411,7 +9423,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9489,10 +9501,10 @@
         <v>1.25</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ42">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>2.18</v>
@@ -9823,7 +9835,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10029,7 +10041,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10441,7 +10453,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10647,7 +10659,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11059,7 +11071,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11471,7 +11483,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11552,7 +11564,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ52">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -11758,7 +11770,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR53">
         <v>1.07</v>
@@ -11883,7 +11895,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -11961,7 +11973,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12089,7 +12101,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12167,7 +12179,7 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12295,7 +12307,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12501,7 +12513,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12579,7 +12591,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ57">
         <v>0.89</v>
@@ -12707,7 +12719,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12913,7 +12925,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -12994,7 +13006,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ59">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR59">
         <v>1.36</v>
@@ -13119,7 +13131,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13325,7 +13337,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13531,7 +13543,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13737,7 +13749,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13943,7 +13955,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14024,7 +14036,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR64">
         <v>1.37</v>
@@ -14149,7 +14161,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14433,10 +14445,10 @@
         <v>0.67</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ66">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR66">
         <v>1.87</v>
@@ -14642,7 +14654,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ67">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR67">
         <v>1.12</v>
@@ -14845,7 +14857,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ68">
         <v>0.78</v>
@@ -14973,7 +14985,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15179,7 +15191,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15257,7 +15269,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ70">
         <v>2.33</v>
@@ -15385,7 +15397,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15672,7 +15684,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ72">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR72">
         <v>1.36</v>
@@ -15878,7 +15890,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16081,7 +16093,7 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ74">
         <v>1.44</v>
@@ -16209,7 +16221,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16415,7 +16427,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16699,7 +16711,7 @@
         <v>2.14</v>
       </c>
       <c r="AP77">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ77">
         <v>2</v>
@@ -16827,7 +16839,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17033,7 +17045,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17445,7 +17457,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17526,7 +17538,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -17651,7 +17663,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18347,7 +18359,7 @@
         <v>0.86</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ85">
         <v>0.78</v>
@@ -18681,7 +18693,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18759,10 +18771,10 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ87">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -18887,7 +18899,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19093,7 +19105,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19174,7 +19186,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ89">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19377,7 +19389,7 @@
         <v>0.13</v>
       </c>
       <c r="AP90">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ90">
         <v>0.11</v>
@@ -19505,7 +19517,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19661,6 +19673,624 @@
         <v>0</v>
       </c>
       <c r="BP91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7483763</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F92">
+        <v>19</v>
+      </c>
+      <c r="G92" t="s">
+        <v>74</v>
+      </c>
+      <c r="H92" t="s">
+        <v>78</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>2</v>
+      </c>
+      <c r="K92">
+        <v>3</v>
+      </c>
+      <c r="L92">
+        <v>2</v>
+      </c>
+      <c r="M92">
+        <v>3</v>
+      </c>
+      <c r="N92">
+        <v>5</v>
+      </c>
+      <c r="O92" t="s">
+        <v>138</v>
+      </c>
+      <c r="P92" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q92">
+        <v>2.4</v>
+      </c>
+      <c r="R92">
+        <v>2.2</v>
+      </c>
+      <c r="S92">
+        <v>4</v>
+      </c>
+      <c r="T92">
+        <v>1.36</v>
+      </c>
+      <c r="U92">
+        <v>3</v>
+      </c>
+      <c r="V92">
+        <v>2.63</v>
+      </c>
+      <c r="W92">
+        <v>1.44</v>
+      </c>
+      <c r="X92">
+        <v>6.5</v>
+      </c>
+      <c r="Y92">
+        <v>1.1</v>
+      </c>
+      <c r="Z92">
+        <v>1.76</v>
+      </c>
+      <c r="AA92">
+        <v>3.78</v>
+      </c>
+      <c r="AB92">
+        <v>4.2</v>
+      </c>
+      <c r="AC92">
+        <v>1.01</v>
+      </c>
+      <c r="AD92">
+        <v>8.9</v>
+      </c>
+      <c r="AE92">
+        <v>1.21</v>
+      </c>
+      <c r="AF92">
+        <v>3.58</v>
+      </c>
+      <c r="AG92">
+        <v>1.7</v>
+      </c>
+      <c r="AH92">
+        <v>1.95</v>
+      </c>
+      <c r="AI92">
+        <v>1.73</v>
+      </c>
+      <c r="AJ92">
+        <v>2</v>
+      </c>
+      <c r="AK92">
+        <v>1.22</v>
+      </c>
+      <c r="AL92">
+        <v>1.23</v>
+      </c>
+      <c r="AM92">
+        <v>1.87</v>
+      </c>
+      <c r="AN92">
+        <v>2.11</v>
+      </c>
+      <c r="AO92">
+        <v>1.33</v>
+      </c>
+      <c r="AP92">
+        <v>1.9</v>
+      </c>
+      <c r="AQ92">
+        <v>1.5</v>
+      </c>
+      <c r="AR92">
+        <v>2.06</v>
+      </c>
+      <c r="AS92">
+        <v>1.54</v>
+      </c>
+      <c r="AT92">
+        <v>3.6</v>
+      </c>
+      <c r="AU92">
+        <v>8</v>
+      </c>
+      <c r="AV92">
+        <v>4</v>
+      </c>
+      <c r="AW92">
+        <v>9</v>
+      </c>
+      <c r="AX92">
+        <v>6</v>
+      </c>
+      <c r="AY92">
+        <v>17</v>
+      </c>
+      <c r="AZ92">
+        <v>10</v>
+      </c>
+      <c r="BA92">
+        <v>5</v>
+      </c>
+      <c r="BB92">
+        <v>5</v>
+      </c>
+      <c r="BC92">
+        <v>10</v>
+      </c>
+      <c r="BD92">
+        <v>1.43</v>
+      </c>
+      <c r="BE92">
+        <v>9</v>
+      </c>
+      <c r="BF92">
+        <v>3.25</v>
+      </c>
+      <c r="BG92">
+        <v>1.22</v>
+      </c>
+      <c r="BH92">
+        <v>4.05</v>
+      </c>
+      <c r="BI92">
+        <v>1.36</v>
+      </c>
+      <c r="BJ92">
+        <v>2.7</v>
+      </c>
+      <c r="BK92">
+        <v>1.73</v>
+      </c>
+      <c r="BL92">
+        <v>2</v>
+      </c>
+      <c r="BM92">
+        <v>2.07</v>
+      </c>
+      <c r="BN92">
+        <v>1.64</v>
+      </c>
+      <c r="BO92">
+        <v>2.7</v>
+      </c>
+      <c r="BP92">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7483764</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45689.5625</v>
+      </c>
+      <c r="F93">
+        <v>19</v>
+      </c>
+      <c r="G93" t="s">
+        <v>73</v>
+      </c>
+      <c r="H93" t="s">
+        <v>76</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>3</v>
+      </c>
+      <c r="O93" t="s">
+        <v>139</v>
+      </c>
+      <c r="P93" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q93">
+        <v>1.73</v>
+      </c>
+      <c r="R93">
+        <v>2.5</v>
+      </c>
+      <c r="S93">
+        <v>8</v>
+      </c>
+      <c r="T93">
+        <v>1.3</v>
+      </c>
+      <c r="U93">
+        <v>3.4</v>
+      </c>
+      <c r="V93">
+        <v>2.5</v>
+      </c>
+      <c r="W93">
+        <v>1.5</v>
+      </c>
+      <c r="X93">
+        <v>5.5</v>
+      </c>
+      <c r="Y93">
+        <v>1.13</v>
+      </c>
+      <c r="Z93">
+        <v>1.26</v>
+      </c>
+      <c r="AA93">
+        <v>5.6</v>
+      </c>
+      <c r="AB93">
+        <v>10</v>
+      </c>
+      <c r="AC93">
+        <v>1.01</v>
+      </c>
+      <c r="AD93">
+        <v>13</v>
+      </c>
+      <c r="AE93">
+        <v>1.16</v>
+      </c>
+      <c r="AF93">
+        <v>4.1</v>
+      </c>
+      <c r="AG93">
+        <v>1.61</v>
+      </c>
+      <c r="AH93">
+        <v>2.05</v>
+      </c>
+      <c r="AI93">
+        <v>2.1</v>
+      </c>
+      <c r="AJ93">
+        <v>1.67</v>
+      </c>
+      <c r="AK93">
+        <v>1.01</v>
+      </c>
+      <c r="AL93">
+        <v>1.11</v>
+      </c>
+      <c r="AM93">
+        <v>3.46</v>
+      </c>
+      <c r="AN93">
+        <v>2.22</v>
+      </c>
+      <c r="AO93">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP93">
+        <v>2.3</v>
+      </c>
+      <c r="AQ93">
+        <v>0.5</v>
+      </c>
+      <c r="AR93">
+        <v>1.71</v>
+      </c>
+      <c r="AS93">
+        <v>1.15</v>
+      </c>
+      <c r="AT93">
+        <v>2.86</v>
+      </c>
+      <c r="AU93">
+        <v>11</v>
+      </c>
+      <c r="AV93">
+        <v>3</v>
+      </c>
+      <c r="AW93">
+        <v>12</v>
+      </c>
+      <c r="AX93">
+        <v>8</v>
+      </c>
+      <c r="AY93">
+        <v>23</v>
+      </c>
+      <c r="AZ93">
+        <v>11</v>
+      </c>
+      <c r="BA93">
+        <v>5</v>
+      </c>
+      <c r="BB93">
+        <v>6</v>
+      </c>
+      <c r="BC93">
+        <v>11</v>
+      </c>
+      <c r="BD93">
+        <v>1.1</v>
+      </c>
+      <c r="BE93">
+        <v>10.75</v>
+      </c>
+      <c r="BF93">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG93">
+        <v>1.27</v>
+      </c>
+      <c r="BH93">
+        <v>3.14</v>
+      </c>
+      <c r="BI93">
+        <v>1.51</v>
+      </c>
+      <c r="BJ93">
+        <v>2.26</v>
+      </c>
+      <c r="BK93">
+        <v>1.91</v>
+      </c>
+      <c r="BL93">
+        <v>1.8</v>
+      </c>
+      <c r="BM93">
+        <v>2.46</v>
+      </c>
+      <c r="BN93">
+        <v>1.43</v>
+      </c>
+      <c r="BO93">
+        <v>3.34</v>
+      </c>
+      <c r="BP93">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7483767</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45690.375</v>
+      </c>
+      <c r="F94">
+        <v>19</v>
+      </c>
+      <c r="G94" t="s">
+        <v>70</v>
+      </c>
+      <c r="H94" t="s">
+        <v>79</v>
+      </c>
+      <c r="I94">
+        <v>2</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+      <c r="L94">
+        <v>5</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>5</v>
+      </c>
+      <c r="O94" t="s">
+        <v>140</v>
+      </c>
+      <c r="P94" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>0</v>
+      </c>
+      <c r="U94">
+        <v>0</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0</v>
+      </c>
+      <c r="X94">
+        <v>0</v>
+      </c>
+      <c r="Y94">
+        <v>0</v>
+      </c>
+      <c r="Z94">
+        <v>1.23</v>
+      </c>
+      <c r="AA94">
+        <v>5.8</v>
+      </c>
+      <c r="AB94">
+        <v>12</v>
+      </c>
+      <c r="AC94">
+        <v>0</v>
+      </c>
+      <c r="AD94">
+        <v>0</v>
+      </c>
+      <c r="AE94">
+        <v>0</v>
+      </c>
+      <c r="AF94">
+        <v>0</v>
+      </c>
+      <c r="AG94">
+        <v>1.85</v>
+      </c>
+      <c r="AH94">
+        <v>1.89</v>
+      </c>
+      <c r="AI94">
+        <v>0</v>
+      </c>
+      <c r="AJ94">
+        <v>0</v>
+      </c>
+      <c r="AK94">
+        <v>0</v>
+      </c>
+      <c r="AL94">
+        <v>0</v>
+      </c>
+      <c r="AM94">
+        <v>0</v>
+      </c>
+      <c r="AN94">
+        <v>2</v>
+      </c>
+      <c r="AO94">
+        <v>1.22</v>
+      </c>
+      <c r="AP94">
+        <v>2.1</v>
+      </c>
+      <c r="AQ94">
+        <v>1.1</v>
+      </c>
+      <c r="AR94">
+        <v>1.81</v>
+      </c>
+      <c r="AS94">
+        <v>1.24</v>
+      </c>
+      <c r="AT94">
+        <v>3.05</v>
+      </c>
+      <c r="AU94">
+        <v>-1</v>
+      </c>
+      <c r="AV94">
+        <v>-1</v>
+      </c>
+      <c r="AW94">
+        <v>-1</v>
+      </c>
+      <c r="AX94">
+        <v>-1</v>
+      </c>
+      <c r="AY94">
+        <v>-1</v>
+      </c>
+      <c r="AZ94">
+        <v>-1</v>
+      </c>
+      <c r="BA94">
+        <v>-1</v>
+      </c>
+      <c r="BB94">
+        <v>-1</v>
+      </c>
+      <c r="BC94">
+        <v>-1</v>
+      </c>
+      <c r="BD94">
+        <v>0</v>
+      </c>
+      <c r="BE94">
+        <v>0</v>
+      </c>
+      <c r="BF94">
+        <v>0</v>
+      </c>
+      <c r="BG94">
+        <v>0</v>
+      </c>
+      <c r="BH94">
+        <v>0</v>
+      </c>
+      <c r="BI94">
+        <v>0</v>
+      </c>
+      <c r="BJ94">
+        <v>0</v>
+      </c>
+      <c r="BK94">
+        <v>0</v>
+      </c>
+      <c r="BL94">
+        <v>0</v>
+      </c>
+      <c r="BM94">
+        <v>0</v>
+      </c>
+      <c r="BN94">
+        <v>0</v>
+      </c>
+      <c r="BO94">
+        <v>0</v>
+      </c>
+      <c r="BP94">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="186">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -439,6 +439,9 @@
     <t>['7', '41', '65', '70', '90']</t>
   </si>
   <si>
+    <t>['65']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -566,6 +569,9 @@
   </si>
   <si>
     <t>['24', '33', '76']</t>
+  </si>
+  <si>
+    <t>['71', '83']</t>
   </si>
 </sst>
 </file>
@@ -927,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP94"/>
+  <dimension ref="A1:BP96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1467,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1673,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1801,7 +1807,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2419,7 +2425,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3115,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3243,7 +3249,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3324,7 +3330,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ12">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3527,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3942,7 +3948,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ15">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR15">
         <v>1.3</v>
@@ -4067,7 +4073,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4479,7 +4485,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4972,7 +4978,7 @@
         <v>2</v>
       </c>
       <c r="AQ20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5097,7 +5103,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5303,7 +5309,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5381,7 +5387,7 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
         <v>1.5</v>
@@ -5590,7 +5596,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ23">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR23">
         <v>0.7</v>
@@ -5715,7 +5721,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5793,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
         <v>1.44</v>
@@ -5921,7 +5927,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6205,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
         <v>0.78</v>
@@ -6333,7 +6339,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6414,7 +6420,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR27">
         <v>0.98</v>
@@ -6745,7 +6751,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7032,7 +7038,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR30">
         <v>1.03</v>
@@ -7157,7 +7163,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7441,7 +7447,7 @@
         <v>1.33</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ32">
         <v>1.5</v>
@@ -8265,7 +8271,7 @@
         <v>1.2</v>
       </c>
       <c r="AP36">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ36">
         <v>1.1</v>
@@ -8393,7 +8399,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8471,7 +8477,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ37">
         <v>2.33</v>
@@ -8805,7 +8811,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -8886,7 +8892,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ39">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR39">
         <v>2.18</v>
@@ -9092,7 +9098,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9423,7 +9429,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9835,7 +9841,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10041,7 +10047,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10453,7 +10459,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10659,7 +10665,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11071,7 +11077,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11355,10 +11361,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ51">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR51">
         <v>1.32</v>
@@ -11483,7 +11489,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11561,7 +11567,7 @@
         <v>0.2</v>
       </c>
       <c r="AP52">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ52">
         <v>0.5</v>
@@ -11895,7 +11901,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12101,7 +12107,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12182,7 +12188,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR55">
         <v>1.92</v>
@@ -12307,7 +12313,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12513,7 +12519,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12719,7 +12725,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12925,7 +12931,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13131,7 +13137,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13337,7 +13343,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13543,7 +13549,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13624,7 +13630,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ62">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -13749,7 +13755,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13827,7 +13833,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ63">
         <v>1.44</v>
@@ -13955,7 +13961,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14161,7 +14167,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14239,7 +14245,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ65">
         <v>1.33</v>
@@ -14985,7 +14991,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15191,7 +15197,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15397,7 +15403,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15478,7 +15484,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -16221,7 +16227,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16299,7 +16305,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ75">
         <v>0.89</v>
@@ -16427,7 +16433,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16714,7 +16720,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ77">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR77">
         <v>2</v>
@@ -16839,7 +16845,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -16920,7 +16926,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ78">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR78">
         <v>1.13</v>
@@ -17045,7 +17051,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17123,7 +17129,7 @@
         <v>2.43</v>
       </c>
       <c r="AP79">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ79">
         <v>2.33</v>
@@ -17457,7 +17463,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17663,7 +17669,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18693,7 +18699,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18899,7 +18905,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19105,7 +19111,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19183,7 +19189,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ89">
         <v>1.1</v>
@@ -19392,7 +19398,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ90">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR90">
         <v>1.64</v>
@@ -19517,7 +19523,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19595,10 +19601,10 @@
         <v>1.88</v>
       </c>
       <c r="AP91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ91">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR91">
         <v>1.34</v>
@@ -19723,7 +19729,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20292,6 +20298,418 @@
       </c>
       <c r="BP94">
         <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7483765</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F95">
+        <v>19</v>
+      </c>
+      <c r="G95" t="s">
+        <v>72</v>
+      </c>
+      <c r="H95" t="s">
+        <v>75</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" t="s">
+        <v>81</v>
+      </c>
+      <c r="P95" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q95">
+        <v>2.27</v>
+      </c>
+      <c r="R95">
+        <v>2.09</v>
+      </c>
+      <c r="S95">
+        <v>5.05</v>
+      </c>
+      <c r="T95">
+        <v>1.41</v>
+      </c>
+      <c r="U95">
+        <v>2.77</v>
+      </c>
+      <c r="V95">
+        <v>2.99</v>
+      </c>
+      <c r="W95">
+        <v>1.36</v>
+      </c>
+      <c r="X95">
+        <v>7.4</v>
+      </c>
+      <c r="Y95">
+        <v>1.07</v>
+      </c>
+      <c r="Z95">
+        <v>1.74</v>
+      </c>
+      <c r="AA95">
+        <v>3.76</v>
+      </c>
+      <c r="AB95">
+        <v>4.33</v>
+      </c>
+      <c r="AC95">
+        <v>1.02</v>
+      </c>
+      <c r="AD95">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE95">
+        <v>1.28</v>
+      </c>
+      <c r="AF95">
+        <v>3.08</v>
+      </c>
+      <c r="AG95">
+        <v>1.91</v>
+      </c>
+      <c r="AH95">
+        <v>1.73</v>
+      </c>
+      <c r="AI95">
+        <v>1.87</v>
+      </c>
+      <c r="AJ95">
+        <v>1.79</v>
+      </c>
+      <c r="AK95">
+        <v>1.15</v>
+      </c>
+      <c r="AL95">
+        <v>1.24</v>
+      </c>
+      <c r="AM95">
+        <v>2</v>
+      </c>
+      <c r="AN95">
+        <v>1.44</v>
+      </c>
+      <c r="AO95">
+        <v>0.11</v>
+      </c>
+      <c r="AP95">
+        <v>1.4</v>
+      </c>
+      <c r="AQ95">
+        <v>0.2</v>
+      </c>
+      <c r="AR95">
+        <v>1.41</v>
+      </c>
+      <c r="AS95">
+        <v>1.27</v>
+      </c>
+      <c r="AT95">
+        <v>2.68</v>
+      </c>
+      <c r="AU95">
+        <v>6</v>
+      </c>
+      <c r="AV95">
+        <v>5</v>
+      </c>
+      <c r="AW95">
+        <v>7</v>
+      </c>
+      <c r="AX95">
+        <v>11</v>
+      </c>
+      <c r="AY95">
+        <v>13</v>
+      </c>
+      <c r="AZ95">
+        <v>16</v>
+      </c>
+      <c r="BA95">
+        <v>5</v>
+      </c>
+      <c r="BB95">
+        <v>3</v>
+      </c>
+      <c r="BC95">
+        <v>8</v>
+      </c>
+      <c r="BD95">
+        <v>1.44</v>
+      </c>
+      <c r="BE95">
+        <v>6.95</v>
+      </c>
+      <c r="BF95">
+        <v>3.58</v>
+      </c>
+      <c r="BG95">
+        <v>1.23</v>
+      </c>
+      <c r="BH95">
+        <v>3.42</v>
+      </c>
+      <c r="BI95">
+        <v>1.45</v>
+      </c>
+      <c r="BJ95">
+        <v>2.41</v>
+      </c>
+      <c r="BK95">
+        <v>1.81</v>
+      </c>
+      <c r="BL95">
+        <v>1.85</v>
+      </c>
+      <c r="BM95">
+        <v>2.3</v>
+      </c>
+      <c r="BN95">
+        <v>1.49</v>
+      </c>
+      <c r="BO95">
+        <v>3.08</v>
+      </c>
+      <c r="BP95">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7483766</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45690.5625</v>
+      </c>
+      <c r="F96">
+        <v>19</v>
+      </c>
+      <c r="G96" t="s">
+        <v>71</v>
+      </c>
+      <c r="H96" t="s">
+        <v>77</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>2</v>
+      </c>
+      <c r="N96">
+        <v>3</v>
+      </c>
+      <c r="O96" t="s">
+        <v>141</v>
+      </c>
+      <c r="P96" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q96">
+        <v>4.33</v>
+      </c>
+      <c r="R96">
+        <v>2</v>
+      </c>
+      <c r="S96">
+        <v>2.63</v>
+      </c>
+      <c r="T96">
+        <v>1.5</v>
+      </c>
+      <c r="U96">
+        <v>2.5</v>
+      </c>
+      <c r="V96">
+        <v>3.4</v>
+      </c>
+      <c r="W96">
+        <v>1.3</v>
+      </c>
+      <c r="X96">
+        <v>8</v>
+      </c>
+      <c r="Y96">
+        <v>1.06</v>
+      </c>
+      <c r="Z96">
+        <v>3.7</v>
+      </c>
+      <c r="AA96">
+        <v>3.2</v>
+      </c>
+      <c r="AB96">
+        <v>2.05</v>
+      </c>
+      <c r="AC96">
+        <v>1.07</v>
+      </c>
+      <c r="AD96">
+        <v>7.5</v>
+      </c>
+      <c r="AE96">
+        <v>1.37</v>
+      </c>
+      <c r="AF96">
+        <v>2.9</v>
+      </c>
+      <c r="AG96">
+        <v>2.05</v>
+      </c>
+      <c r="AH96">
+        <v>1.61</v>
+      </c>
+      <c r="AI96">
+        <v>2</v>
+      </c>
+      <c r="AJ96">
+        <v>1.73</v>
+      </c>
+      <c r="AK96">
+        <v>1.65</v>
+      </c>
+      <c r="AL96">
+        <v>1.3</v>
+      </c>
+      <c r="AM96">
+        <v>1.24</v>
+      </c>
+      <c r="AN96">
+        <v>1.33</v>
+      </c>
+      <c r="AO96">
+        <v>2</v>
+      </c>
+      <c r="AP96">
+        <v>1.2</v>
+      </c>
+      <c r="AQ96">
+        <v>2.1</v>
+      </c>
+      <c r="AR96">
+        <v>1.35</v>
+      </c>
+      <c r="AS96">
+        <v>1.38</v>
+      </c>
+      <c r="AT96">
+        <v>2.73</v>
+      </c>
+      <c r="AU96">
+        <v>8</v>
+      </c>
+      <c r="AV96">
+        <v>4</v>
+      </c>
+      <c r="AW96">
+        <v>5</v>
+      </c>
+      <c r="AX96">
+        <v>5</v>
+      </c>
+      <c r="AY96">
+        <v>13</v>
+      </c>
+      <c r="AZ96">
+        <v>9</v>
+      </c>
+      <c r="BA96">
+        <v>3</v>
+      </c>
+      <c r="BB96">
+        <v>4</v>
+      </c>
+      <c r="BC96">
+        <v>7</v>
+      </c>
+      <c r="BD96">
+        <v>2.28</v>
+      </c>
+      <c r="BE96">
+        <v>5.9</v>
+      </c>
+      <c r="BF96">
+        <v>1.96</v>
+      </c>
+      <c r="BG96">
+        <v>1.56</v>
+      </c>
+      <c r="BH96">
+        <v>2.33</v>
+      </c>
+      <c r="BI96">
+        <v>1.95</v>
+      </c>
+      <c r="BJ96">
+        <v>1.8</v>
+      </c>
+      <c r="BK96">
+        <v>2.55</v>
+      </c>
+      <c r="BL96">
+        <v>1.48</v>
+      </c>
+      <c r="BM96">
+        <v>3.52</v>
+      </c>
+      <c r="BN96">
+        <v>1.27</v>
+      </c>
+      <c r="BO96">
+        <v>4.95</v>
+      </c>
+      <c r="BP96">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -20234,31 +20234,31 @@
         <v>3.05</v>
       </c>
       <c r="AU94">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV94">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW94">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX94">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY94">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AZ94">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BA94">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB94">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC94">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD94">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="190">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -442,6 +442,12 @@
     <t>['65']</t>
   </si>
   <si>
+    <t>['34', '44', '63']</t>
+  </si>
+  <si>
+    <t>['63', '90+2']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -572,6 +578,12 @@
   </si>
   <si>
     <t>['71', '83']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['44']</t>
   </si>
 </sst>
 </file>
@@ -933,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP96"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1270,7 +1282,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ2">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1807,7 +1819,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2297,10 +2309,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ7">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2425,7 +2437,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2915,10 +2927,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ10">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3249,7 +3261,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4073,7 +4085,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4151,10 +4163,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ16">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>1.76</v>
@@ -4485,7 +4497,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4566,7 +4578,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ18">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR18">
         <v>2.23</v>
@@ -4975,7 +4987,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ20">
         <v>2.1</v>
@@ -5103,7 +5115,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5309,7 +5321,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5721,7 +5733,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5927,7 +5939,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6214,7 +6226,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ26">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR26">
         <v>1.62</v>
@@ -6339,7 +6351,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6751,7 +6763,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6832,7 +6844,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ29">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7035,7 +7047,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ30">
         <v>0.2</v>
@@ -7163,7 +7175,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7241,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ31">
         <v>0.5</v>
@@ -7656,7 +7668,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ33">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8274,7 +8286,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ36">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.75</v>
@@ -8399,7 +8411,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8683,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ38">
         <v>0.5</v>
@@ -8811,7 +8823,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9429,7 +9441,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9841,7 +9853,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -9919,7 +9931,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ44">
         <v>1.44</v>
@@ -10047,7 +10059,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10331,7 +10343,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ46">
         <v>0.89</v>
@@ -10459,7 +10471,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10665,7 +10677,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10743,7 +10755,7 @@
         <v>1.25</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -10952,7 +10964,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ49">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR49">
         <v>1.31</v>
@@ -11077,7 +11089,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11489,7 +11501,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11901,7 +11913,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12107,7 +12119,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12313,7 +12325,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12394,7 +12406,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ56">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12519,7 +12531,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12725,7 +12737,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12803,7 +12815,7 @@
         <v>2.2</v>
       </c>
       <c r="AP58">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ58">
         <v>2.33</v>
@@ -12931,7 +12943,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13012,7 +13024,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ59">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.36</v>
@@ -13137,7 +13149,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13215,7 +13227,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ60">
         <v>1.44</v>
@@ -13343,7 +13355,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13424,7 +13436,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ61">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR61">
         <v>1.2</v>
@@ -13549,7 +13561,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13755,7 +13767,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13961,7 +13973,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14167,7 +14179,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14660,7 +14672,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ67">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.12</v>
@@ -14866,7 +14878,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ68">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR68">
         <v>1.5</v>
@@ -14991,7 +15003,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15069,7 +15081,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ69">
         <v>0.89</v>
@@ -15197,7 +15209,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15403,7 +15415,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15481,7 +15493,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ71">
         <v>2.1</v>
@@ -15893,7 +15905,7 @@
         <v>0.86</v>
       </c>
       <c r="AP73">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ73">
         <v>1.5</v>
@@ -16227,7 +16239,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16433,7 +16445,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16845,7 +16857,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17051,7 +17063,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17463,7 +17475,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17669,7 +17681,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18159,7 +18171,7 @@
         <v>1.38</v>
       </c>
       <c r="AP84">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -18368,7 +18380,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ85">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR85">
         <v>1.72</v>
@@ -18571,10 +18583,10 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ86">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR86">
         <v>1.46</v>
@@ -18699,7 +18711,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18905,7 +18917,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -18983,7 +18995,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ88">
         <v>2.33</v>
@@ -19111,7 +19123,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19192,7 +19204,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ89">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19523,7 +19535,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19729,7 +19741,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20222,7 +20234,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ94">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.81</v>
@@ -20553,7 +20565,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20710,6 +20722,418 @@
       </c>
       <c r="BP96">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7483768</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45695.45833333334</v>
+      </c>
+      <c r="F97">
+        <v>20</v>
+      </c>
+      <c r="G97" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s">
+        <v>79</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>3</v>
+      </c>
+      <c r="L97">
+        <v>3</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>4</v>
+      </c>
+      <c r="O97" t="s">
+        <v>142</v>
+      </c>
+      <c r="P97" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>0</v>
+      </c>
+      <c r="T97">
+        <v>0</v>
+      </c>
+      <c r="U97">
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0</v>
+      </c>
+      <c r="X97">
+        <v>0</v>
+      </c>
+      <c r="Y97">
+        <v>0</v>
+      </c>
+      <c r="Z97">
+        <v>1.65</v>
+      </c>
+      <c r="AA97">
+        <v>3.4</v>
+      </c>
+      <c r="AB97">
+        <v>4.5</v>
+      </c>
+      <c r="AC97">
+        <v>0</v>
+      </c>
+      <c r="AD97">
+        <v>0</v>
+      </c>
+      <c r="AE97">
+        <v>0</v>
+      </c>
+      <c r="AF97">
+        <v>0</v>
+      </c>
+      <c r="AG97">
+        <v>2</v>
+      </c>
+      <c r="AH97">
+        <v>1.65</v>
+      </c>
+      <c r="AI97">
+        <v>0</v>
+      </c>
+      <c r="AJ97">
+        <v>0</v>
+      </c>
+      <c r="AK97">
+        <v>0</v>
+      </c>
+      <c r="AL97">
+        <v>0</v>
+      </c>
+      <c r="AM97">
+        <v>0</v>
+      </c>
+      <c r="AN97">
+        <v>2</v>
+      </c>
+      <c r="AO97">
+        <v>1.1</v>
+      </c>
+      <c r="AP97">
+        <v>2.1</v>
+      </c>
+      <c r="AQ97">
+        <v>1</v>
+      </c>
+      <c r="AR97">
+        <v>1.44</v>
+      </c>
+      <c r="AS97">
+        <v>1.18</v>
+      </c>
+      <c r="AT97">
+        <v>2.62</v>
+      </c>
+      <c r="AU97">
+        <v>-1</v>
+      </c>
+      <c r="AV97">
+        <v>-1</v>
+      </c>
+      <c r="AW97">
+        <v>-1</v>
+      </c>
+      <c r="AX97">
+        <v>-1</v>
+      </c>
+      <c r="AY97">
+        <v>-1</v>
+      </c>
+      <c r="AZ97">
+        <v>-1</v>
+      </c>
+      <c r="BA97">
+        <v>-1</v>
+      </c>
+      <c r="BB97">
+        <v>-1</v>
+      </c>
+      <c r="BC97">
+        <v>-1</v>
+      </c>
+      <c r="BD97">
+        <v>0</v>
+      </c>
+      <c r="BE97">
+        <v>0</v>
+      </c>
+      <c r="BF97">
+        <v>0</v>
+      </c>
+      <c r="BG97">
+        <v>0</v>
+      </c>
+      <c r="BH97">
+        <v>0</v>
+      </c>
+      <c r="BI97">
+        <v>0</v>
+      </c>
+      <c r="BJ97">
+        <v>0</v>
+      </c>
+      <c r="BK97">
+        <v>0</v>
+      </c>
+      <c r="BL97">
+        <v>0</v>
+      </c>
+      <c r="BM97">
+        <v>0</v>
+      </c>
+      <c r="BN97">
+        <v>0</v>
+      </c>
+      <c r="BO97">
+        <v>0</v>
+      </c>
+      <c r="BP97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7483770</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45695.5625</v>
+      </c>
+      <c r="F98">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>75</v>
+      </c>
+      <c r="H98" t="s">
+        <v>71</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>2</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>3</v>
+      </c>
+      <c r="O98" t="s">
+        <v>143</v>
+      </c>
+      <c r="P98" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q98">
+        <v>3.25</v>
+      </c>
+      <c r="R98">
+        <v>2.03</v>
+      </c>
+      <c r="S98">
+        <v>3.3</v>
+      </c>
+      <c r="T98">
+        <v>1.47</v>
+      </c>
+      <c r="U98">
+        <v>2.5</v>
+      </c>
+      <c r="V98">
+        <v>3</v>
+      </c>
+      <c r="W98">
+        <v>1.33</v>
+      </c>
+      <c r="X98">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y98">
+        <v>1.06</v>
+      </c>
+      <c r="Z98">
+        <v>2.5</v>
+      </c>
+      <c r="AA98">
+        <v>3.1</v>
+      </c>
+      <c r="AB98">
+        <v>2.5</v>
+      </c>
+      <c r="AC98">
+        <v>1.07</v>
+      </c>
+      <c r="AD98">
+        <v>7.5</v>
+      </c>
+      <c r="AE98">
+        <v>1.36</v>
+      </c>
+      <c r="AF98">
+        <v>2.95</v>
+      </c>
+      <c r="AG98">
+        <v>2.05</v>
+      </c>
+      <c r="AH98">
+        <v>1.61</v>
+      </c>
+      <c r="AI98">
+        <v>1.83</v>
+      </c>
+      <c r="AJ98">
+        <v>1.87</v>
+      </c>
+      <c r="AK98">
+        <v>1.44</v>
+      </c>
+      <c r="AL98">
+        <v>1.31</v>
+      </c>
+      <c r="AM98">
+        <v>1.45</v>
+      </c>
+      <c r="AN98">
+        <v>0.89</v>
+      </c>
+      <c r="AO98">
+        <v>0.78</v>
+      </c>
+      <c r="AP98">
+        <v>1.1</v>
+      </c>
+      <c r="AQ98">
+        <v>0.7</v>
+      </c>
+      <c r="AR98">
+        <v>1.44</v>
+      </c>
+      <c r="AS98">
+        <v>1.23</v>
+      </c>
+      <c r="AT98">
+        <v>2.67</v>
+      </c>
+      <c r="AU98">
+        <v>6</v>
+      </c>
+      <c r="AV98">
+        <v>8</v>
+      </c>
+      <c r="AW98">
+        <v>5</v>
+      </c>
+      <c r="AX98">
+        <v>8</v>
+      </c>
+      <c r="AY98">
+        <v>11</v>
+      </c>
+      <c r="AZ98">
+        <v>16</v>
+      </c>
+      <c r="BA98">
+        <v>5</v>
+      </c>
+      <c r="BB98">
+        <v>4</v>
+      </c>
+      <c r="BC98">
+        <v>9</v>
+      </c>
+      <c r="BD98">
+        <v>0</v>
+      </c>
+      <c r="BE98">
+        <v>0</v>
+      </c>
+      <c r="BF98">
+        <v>0</v>
+      </c>
+      <c r="BG98">
+        <v>0</v>
+      </c>
+      <c r="BH98">
+        <v>0</v>
+      </c>
+      <c r="BI98">
+        <v>0</v>
+      </c>
+      <c r="BJ98">
+        <v>0</v>
+      </c>
+      <c r="BK98">
+        <v>0</v>
+      </c>
+      <c r="BL98">
+        <v>0</v>
+      </c>
+      <c r="BM98">
+        <v>0</v>
+      </c>
+      <c r="BN98">
+        <v>0</v>
+      </c>
+      <c r="BO98">
+        <v>0</v>
+      </c>
+      <c r="BP98">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="191">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -585,6 +585,9 @@
   <si>
     <t>['44']</t>
   </si>
+  <si>
+    <t>['34']</t>
+  </si>
 </sst>
 </file>
 
@@ -945,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP98"/>
+  <dimension ref="A1:BP99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2515,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ8">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4369,7 +4372,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ17">
         <v>2.33</v>
@@ -4784,7 +4787,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ19">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR19">
         <v>1.75</v>
@@ -6429,7 +6432,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ27">
         <v>2.1</v>
@@ -8080,7 +8083,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ35">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR35">
         <v>2.01</v>
@@ -9728,7 +9731,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ43">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR43">
         <v>1.26</v>
@@ -10137,7 +10140,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ45">
         <v>1.33</v>
@@ -10346,7 +10349,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ46">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR46">
         <v>1.5</v>
@@ -11167,7 +11170,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ50">
         <v>1.44</v>
@@ -12612,7 +12615,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ57">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR57">
         <v>2.09</v>
@@ -13433,7 +13436,7 @@
         <v>0.6</v>
       </c>
       <c r="AP61">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ61">
         <v>0.7</v>
@@ -14669,7 +14672,7 @@
         <v>1.29</v>
       </c>
       <c r="AP67">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15084,7 +15087,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ69">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -16320,7 +16323,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ75">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR75">
         <v>1.44</v>
@@ -16935,7 +16938,7 @@
         <v>0.14</v>
       </c>
       <c r="AP78">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ78">
         <v>0.2</v>
@@ -17553,7 +17556,7 @@
         <v>1.13</v>
       </c>
       <c r="AP81">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ81">
         <v>1.5</v>
@@ -17968,7 +17971,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ83">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR83">
         <v>1.05</v>
@@ -21133,6 +21136,212 @@
         <v>0</v>
       </c>
       <c r="BP98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7483771</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45696.375</v>
+      </c>
+      <c r="F99">
+        <v>20</v>
+      </c>
+      <c r="G99" t="s">
+        <v>76</v>
+      </c>
+      <c r="H99" t="s">
+        <v>72</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P99" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q99">
+        <v>3.55</v>
+      </c>
+      <c r="R99">
+        <v>2.04</v>
+      </c>
+      <c r="S99">
+        <v>3</v>
+      </c>
+      <c r="T99">
+        <v>1.47</v>
+      </c>
+      <c r="U99">
+        <v>2.5</v>
+      </c>
+      <c r="V99">
+        <v>3.14</v>
+      </c>
+      <c r="W99">
+        <v>1.33</v>
+      </c>
+      <c r="X99">
+        <v>8</v>
+      </c>
+      <c r="Y99">
+        <v>1.06</v>
+      </c>
+      <c r="Z99">
+        <v>3</v>
+      </c>
+      <c r="AA99">
+        <v>3.1</v>
+      </c>
+      <c r="AB99">
+        <v>2.15</v>
+      </c>
+      <c r="AC99">
+        <v>1.02</v>
+      </c>
+      <c r="AD99">
+        <v>7.7</v>
+      </c>
+      <c r="AE99">
+        <v>1.36</v>
+      </c>
+      <c r="AF99">
+        <v>3</v>
+      </c>
+      <c r="AG99">
+        <v>2</v>
+      </c>
+      <c r="AH99">
+        <v>1.67</v>
+      </c>
+      <c r="AI99">
+        <v>1.82</v>
+      </c>
+      <c r="AJ99">
+        <v>1.88</v>
+      </c>
+      <c r="AK99">
+        <v>1.51</v>
+      </c>
+      <c r="AL99">
+        <v>1.31</v>
+      </c>
+      <c r="AM99">
+        <v>1.38</v>
+      </c>
+      <c r="AN99">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO99">
+        <v>0.89</v>
+      </c>
+      <c r="AP99">
+        <v>0.5</v>
+      </c>
+      <c r="AQ99">
+        <v>1.1</v>
+      </c>
+      <c r="AR99">
+        <v>1.34</v>
+      </c>
+      <c r="AS99">
+        <v>1.31</v>
+      </c>
+      <c r="AT99">
+        <v>2.65</v>
+      </c>
+      <c r="AU99">
+        <v>6</v>
+      </c>
+      <c r="AV99">
+        <v>5</v>
+      </c>
+      <c r="AW99">
+        <v>17</v>
+      </c>
+      <c r="AX99">
+        <v>3</v>
+      </c>
+      <c r="AY99">
+        <v>23</v>
+      </c>
+      <c r="AZ99">
+        <v>8</v>
+      </c>
+      <c r="BA99">
+        <v>9</v>
+      </c>
+      <c r="BB99">
+        <v>1</v>
+      </c>
+      <c r="BC99">
+        <v>10</v>
+      </c>
+      <c r="BD99">
+        <v>0</v>
+      </c>
+      <c r="BE99">
+        <v>0</v>
+      </c>
+      <c r="BF99">
+        <v>0</v>
+      </c>
+      <c r="BG99">
+        <v>0</v>
+      </c>
+      <c r="BH99">
+        <v>0</v>
+      </c>
+      <c r="BI99">
+        <v>0</v>
+      </c>
+      <c r="BJ99">
+        <v>0</v>
+      </c>
+      <c r="BK99">
+        <v>0</v>
+      </c>
+      <c r="BL99">
+        <v>0</v>
+      </c>
+      <c r="BM99">
+        <v>0</v>
+      </c>
+      <c r="BN99">
+        <v>0</v>
+      </c>
+      <c r="BO99">
+        <v>0</v>
+      </c>
+      <c r="BP99">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="195">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -448,6 +448,12 @@
     <t>['63', '90+2']</t>
   </si>
   <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -587,6 +593,12 @@
   </si>
   <si>
     <t>['34']</t>
+  </si>
+  <si>
+    <t>['23', '52']</t>
+  </si>
+  <si>
+    <t>['57', '74']</t>
   </si>
 </sst>
 </file>
@@ -948,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP99"/>
+  <dimension ref="A1:BP101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1822,7 +1834,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2106,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -2440,7 +2452,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2724,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3264,7 +3276,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4088,7 +4100,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4375,7 +4387,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ17">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR17">
         <v>1.21</v>
@@ -4500,7 +4512,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4578,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ18">
         <v>0.7</v>
@@ -5118,7 +5130,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5324,7 +5336,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5608,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
         <v>0.2</v>
@@ -5736,7 +5748,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5817,7 +5829,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ24">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR24">
         <v>1.24</v>
@@ -5942,7 +5954,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6354,7 +6366,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6641,7 +6653,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ28">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -6766,7 +6778,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6844,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7178,7 +7190,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7874,7 +7886,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8414,7 +8426,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8495,7 +8507,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ37">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -8826,7 +8838,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -8904,7 +8916,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ39">
         <v>0.2</v>
@@ -9316,10 +9328,10 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ41">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR41">
         <v>2.19</v>
@@ -9444,7 +9456,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9728,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ43">
         <v>1.1</v>
@@ -9856,7 +9868,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -9937,7 +9949,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ44">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10062,7 +10074,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10474,7 +10486,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10555,7 +10567,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ47">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR47">
         <v>1.05</v>
@@ -10680,7 +10692,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10964,7 +10976,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
         <v>0.7</v>
@@ -11092,7 +11104,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11173,7 +11185,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ50">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11504,7 +11516,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11916,7 +11928,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12122,7 +12134,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12328,7 +12340,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12534,7 +12546,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12612,7 +12624,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57">
         <v>1.1</v>
@@ -12740,7 +12752,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12821,7 +12833,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ58">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR58">
         <v>1.46</v>
@@ -12946,7 +12958,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13024,7 +13036,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13152,7 +13164,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13233,7 +13245,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ60">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
         <v>1.4</v>
@@ -13358,7 +13370,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13564,7 +13576,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13770,7 +13782,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13851,7 +13863,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ63">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR63">
         <v>1.5</v>
@@ -13976,7 +13988,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14054,7 +14066,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
         <v>1.5</v>
@@ -14182,7 +14194,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -15006,7 +15018,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15212,7 +15224,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15290,10 +15302,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ70">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR70">
         <v>1.99</v>
@@ -15418,7 +15430,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15702,7 +15714,7 @@
         <v>0.57</v>
       </c>
       <c r="AP72">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>0.5</v>
@@ -16117,7 +16129,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ74">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR74">
         <v>1.87</v>
@@ -16242,7 +16254,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16448,7 +16460,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16732,7 +16744,7 @@
         <v>2.14</v>
       </c>
       <c r="AP77">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ77">
         <v>2.1</v>
@@ -16860,7 +16872,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17066,7 +17078,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17147,7 +17159,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ79">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR79">
         <v>1.42</v>
@@ -17353,7 +17365,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ80">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR80">
         <v>1.04</v>
@@ -17478,7 +17490,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17684,7 +17696,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -17762,10 +17774,10 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR82">
         <v>1.46</v>
@@ -18714,7 +18726,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18792,7 +18804,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ87">
         <v>0.5</v>
@@ -18920,7 +18932,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19001,7 +19013,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ88">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR88">
         <v>1.51</v>
@@ -19126,7 +19138,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19538,7 +19550,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19744,7 +19756,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19822,7 +19834,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ92">
         <v>1.5</v>
@@ -20568,7 +20580,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20774,7 +20786,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -20867,31 +20879,31 @@
         <v>2.62</v>
       </c>
       <c r="AU97">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AV97">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW97">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AX97">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AY97">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ97">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BA97">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB97">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC97">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD97">
         <v>0</v>
@@ -20980,7 +20992,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21186,7 +21198,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21342,6 +21354,418 @@
         <v>0</v>
       </c>
       <c r="BP99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7483772</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F100">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>74</v>
+      </c>
+      <c r="H100" t="s">
+        <v>73</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>2</v>
+      </c>
+      <c r="N100">
+        <v>3</v>
+      </c>
+      <c r="O100" t="s">
+        <v>144</v>
+      </c>
+      <c r="P100" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q100">
+        <v>2.65</v>
+      </c>
+      <c r="R100">
+        <v>2.21</v>
+      </c>
+      <c r="S100">
+        <v>3.65</v>
+      </c>
+      <c r="T100">
+        <v>1.33</v>
+      </c>
+      <c r="U100">
+        <v>3.14</v>
+      </c>
+      <c r="V100">
+        <v>2.5</v>
+      </c>
+      <c r="W100">
+        <v>1.47</v>
+      </c>
+      <c r="X100">
+        <v>6.2</v>
+      </c>
+      <c r="Y100">
+        <v>1.1</v>
+      </c>
+      <c r="Z100">
+        <v>2.1</v>
+      </c>
+      <c r="AA100">
+        <v>3.3</v>
+      </c>
+      <c r="AB100">
+        <v>2.87</v>
+      </c>
+      <c r="AC100">
+        <v>1.02</v>
+      </c>
+      <c r="AD100">
+        <v>10</v>
+      </c>
+      <c r="AE100">
+        <v>1.24</v>
+      </c>
+      <c r="AF100">
+        <v>3.75</v>
+      </c>
+      <c r="AG100">
+        <v>1.73</v>
+      </c>
+      <c r="AH100">
+        <v>1.91</v>
+      </c>
+      <c r="AI100">
+        <v>1.63</v>
+      </c>
+      <c r="AJ100">
+        <v>2.14</v>
+      </c>
+      <c r="AK100">
+        <v>1.33</v>
+      </c>
+      <c r="AL100">
+        <v>1.27</v>
+      </c>
+      <c r="AM100">
+        <v>1.65</v>
+      </c>
+      <c r="AN100">
+        <v>1.9</v>
+      </c>
+      <c r="AO100">
+        <v>1.44</v>
+      </c>
+      <c r="AP100">
+        <v>1.73</v>
+      </c>
+      <c r="AQ100">
+        <v>1.6</v>
+      </c>
+      <c r="AR100">
+        <v>2.09</v>
+      </c>
+      <c r="AS100">
+        <v>1.64</v>
+      </c>
+      <c r="AT100">
+        <v>3.73</v>
+      </c>
+      <c r="AU100">
+        <v>6</v>
+      </c>
+      <c r="AV100">
+        <v>4</v>
+      </c>
+      <c r="AW100">
+        <v>12</v>
+      </c>
+      <c r="AX100">
+        <v>2</v>
+      </c>
+      <c r="AY100">
+        <v>18</v>
+      </c>
+      <c r="AZ100">
+        <v>6</v>
+      </c>
+      <c r="BA100">
+        <v>9</v>
+      </c>
+      <c r="BB100">
+        <v>4</v>
+      </c>
+      <c r="BC100">
+        <v>13</v>
+      </c>
+      <c r="BD100">
+        <v>0</v>
+      </c>
+      <c r="BE100">
+        <v>0</v>
+      </c>
+      <c r="BF100">
+        <v>0</v>
+      </c>
+      <c r="BG100">
+        <v>0</v>
+      </c>
+      <c r="BH100">
+        <v>0</v>
+      </c>
+      <c r="BI100">
+        <v>0</v>
+      </c>
+      <c r="BJ100">
+        <v>0</v>
+      </c>
+      <c r="BK100">
+        <v>0</v>
+      </c>
+      <c r="BL100">
+        <v>0</v>
+      </c>
+      <c r="BM100">
+        <v>0</v>
+      </c>
+      <c r="BN100">
+        <v>0</v>
+      </c>
+      <c r="BO100">
+        <v>0</v>
+      </c>
+      <c r="BP100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7483769</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45696.5625</v>
+      </c>
+      <c r="F101">
+        <v>20</v>
+      </c>
+      <c r="G101" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" t="s">
+        <v>70</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <v>2</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101" t="s">
+        <v>145</v>
+      </c>
+      <c r="P101" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q101">
+        <v>4.33</v>
+      </c>
+      <c r="R101">
+        <v>2.1</v>
+      </c>
+      <c r="S101">
+        <v>2.5</v>
+      </c>
+      <c r="T101">
+        <v>1.44</v>
+      </c>
+      <c r="U101">
+        <v>2.63</v>
+      </c>
+      <c r="V101">
+        <v>3</v>
+      </c>
+      <c r="W101">
+        <v>1.36</v>
+      </c>
+      <c r="X101">
+        <v>7.5</v>
+      </c>
+      <c r="Y101">
+        <v>1.07</v>
+      </c>
+      <c r="Z101">
+        <v>3.8</v>
+      </c>
+      <c r="AA101">
+        <v>3.3</v>
+      </c>
+      <c r="AB101">
+        <v>1.8</v>
+      </c>
+      <c r="AC101">
+        <v>0</v>
+      </c>
+      <c r="AD101">
+        <v>0</v>
+      </c>
+      <c r="AE101">
+        <v>0</v>
+      </c>
+      <c r="AF101">
+        <v>0</v>
+      </c>
+      <c r="AG101">
+        <v>1.95</v>
+      </c>
+      <c r="AH101">
+        <v>1.73</v>
+      </c>
+      <c r="AI101">
+        <v>1.83</v>
+      </c>
+      <c r="AJ101">
+        <v>1.83</v>
+      </c>
+      <c r="AK101">
+        <v>0</v>
+      </c>
+      <c r="AL101">
+        <v>0</v>
+      </c>
+      <c r="AM101">
+        <v>0</v>
+      </c>
+      <c r="AN101">
+        <v>1.67</v>
+      </c>
+      <c r="AO101">
+        <v>2.33</v>
+      </c>
+      <c r="AP101">
+        <v>1.5</v>
+      </c>
+      <c r="AQ101">
+        <v>2.4</v>
+      </c>
+      <c r="AR101">
+        <v>1.43</v>
+      </c>
+      <c r="AS101">
+        <v>1.66</v>
+      </c>
+      <c r="AT101">
+        <v>3.09</v>
+      </c>
+      <c r="AU101">
+        <v>5</v>
+      </c>
+      <c r="AV101">
+        <v>11</v>
+      </c>
+      <c r="AW101">
+        <v>2</v>
+      </c>
+      <c r="AX101">
+        <v>7</v>
+      </c>
+      <c r="AY101">
+        <v>7</v>
+      </c>
+      <c r="AZ101">
+        <v>18</v>
+      </c>
+      <c r="BA101">
+        <v>1</v>
+      </c>
+      <c r="BB101">
+        <v>4</v>
+      </c>
+      <c r="BC101">
+        <v>5</v>
+      </c>
+      <c r="BD101">
+        <v>0</v>
+      </c>
+      <c r="BE101">
+        <v>0</v>
+      </c>
+      <c r="BF101">
+        <v>0</v>
+      </c>
+      <c r="BG101">
+        <v>0</v>
+      </c>
+      <c r="BH101">
+        <v>0</v>
+      </c>
+      <c r="BI101">
+        <v>0</v>
+      </c>
+      <c r="BJ101">
+        <v>0</v>
+      </c>
+      <c r="BK101">
+        <v>0</v>
+      </c>
+      <c r="BL101">
+        <v>0</v>
+      </c>
+      <c r="BM101">
+        <v>0</v>
+      </c>
+      <c r="BN101">
+        <v>0</v>
+      </c>
+      <c r="BO101">
+        <v>0</v>
+      </c>
+      <c r="BP101">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="197">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -454,6 +454,9 @@
     <t>['13']</t>
   </si>
   <si>
+    <t>['31', '39']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -599,6 +602,9 @@
   </si>
   <si>
     <t>['57', '74']</t>
+  </si>
+  <si>
+    <t>['5', '59', '80']</t>
   </si>
 </sst>
 </file>
@@ -960,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP101"/>
+  <dimension ref="A1:BP102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1834,7 +1840,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -1912,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ5">
         <v>0.5</v>
@@ -2121,7 +2127,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2452,7 +2458,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3276,7 +3282,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3766,10 +3772,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR14">
         <v>1.88</v>
@@ -4100,7 +4106,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4512,7 +4518,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4796,7 +4802,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ19">
         <v>1.1</v>
@@ -5130,7 +5136,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5336,7 +5342,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5417,7 +5423,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5748,7 +5754,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5954,7 +5960,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6366,7 +6372,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6650,7 +6656,7 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ28">
         <v>2.4</v>
@@ -6778,7 +6784,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7190,7 +7196,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7477,7 +7483,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -7680,7 +7686,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8426,7 +8432,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8838,7 +8844,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9122,7 +9128,7 @@
         <v>2.25</v>
       </c>
       <c r="AP40">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ40">
         <v>2.1</v>
@@ -9456,7 +9462,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9537,7 +9543,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR42">
         <v>2.18</v>
@@ -9868,7 +9874,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10074,7 +10080,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10486,7 +10492,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10692,7 +10698,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11104,7 +11110,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11516,7 +11522,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11803,7 +11809,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ53">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR53">
         <v>1.07</v>
@@ -11928,7 +11934,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12006,7 +12012,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12134,7 +12140,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12340,7 +12346,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12546,7 +12552,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12752,7 +12758,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12958,7 +12964,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13164,7 +13170,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13370,7 +13376,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13576,7 +13582,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13782,7 +13788,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13988,7 +13994,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14069,7 +14075,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR64">
         <v>1.37</v>
@@ -14194,7 +14200,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14890,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ68">
         <v>0.7</v>
@@ -15018,7 +15024,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15224,7 +15230,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15430,7 +15436,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15923,7 +15929,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16254,7 +16260,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16460,7 +16466,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16872,7 +16878,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17078,7 +17084,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17490,7 +17496,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17571,7 +17577,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -17696,7 +17702,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18726,7 +18732,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18932,7 +18938,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19138,7 +19144,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19422,7 +19428,7 @@
         <v>0.13</v>
       </c>
       <c r="AP90">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ90">
         <v>0.2</v>
@@ -19550,7 +19556,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19756,7 +19762,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19837,7 +19843,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ92">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20040,7 +20046,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP93">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ93">
         <v>0.5</v>
@@ -20580,7 +20586,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20786,7 +20792,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -20992,7 +20998,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21198,7 +21204,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21404,7 +21410,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21610,7 +21616,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21766,6 +21772,212 @@
         <v>0</v>
       </c>
       <c r="BP101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7483773</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F102">
+        <v>21</v>
+      </c>
+      <c r="G102" t="s">
+        <v>73</v>
+      </c>
+      <c r="H102" t="s">
+        <v>78</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>3</v>
+      </c>
+      <c r="L102">
+        <v>2</v>
+      </c>
+      <c r="M102">
+        <v>3</v>
+      </c>
+      <c r="N102">
+        <v>5</v>
+      </c>
+      <c r="O102" t="s">
+        <v>146</v>
+      </c>
+      <c r="P102" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q102">
+        <v>2.34</v>
+      </c>
+      <c r="R102">
+        <v>2.09</v>
+      </c>
+      <c r="S102">
+        <v>5.2</v>
+      </c>
+      <c r="T102">
+        <v>1.46</v>
+      </c>
+      <c r="U102">
+        <v>2.55</v>
+      </c>
+      <c r="V102">
+        <v>3.1</v>
+      </c>
+      <c r="W102">
+        <v>1.33</v>
+      </c>
+      <c r="X102">
+        <v>8.1</v>
+      </c>
+      <c r="Y102">
+        <v>1.06</v>
+      </c>
+      <c r="Z102">
+        <v>1.76</v>
+      </c>
+      <c r="AA102">
+        <v>3.51</v>
+      </c>
+      <c r="AB102">
+        <v>4.6</v>
+      </c>
+      <c r="AC102">
+        <v>1.02</v>
+      </c>
+      <c r="AD102">
+        <v>8.1</v>
+      </c>
+      <c r="AE102">
+        <v>1.37</v>
+      </c>
+      <c r="AF102">
+        <v>2.95</v>
+      </c>
+      <c r="AG102">
+        <v>2</v>
+      </c>
+      <c r="AH102">
+        <v>1.67</v>
+      </c>
+      <c r="AI102">
+        <v>2</v>
+      </c>
+      <c r="AJ102">
+        <v>1.72</v>
+      </c>
+      <c r="AK102">
+        <v>1.19</v>
+      </c>
+      <c r="AL102">
+        <v>1.26</v>
+      </c>
+      <c r="AM102">
+        <v>1.95</v>
+      </c>
+      <c r="AN102">
+        <v>2.3</v>
+      </c>
+      <c r="AO102">
+        <v>1.5</v>
+      </c>
+      <c r="AP102">
+        <v>2.09</v>
+      </c>
+      <c r="AQ102">
+        <v>1.64</v>
+      </c>
+      <c r="AR102">
+        <v>1.84</v>
+      </c>
+      <c r="AS102">
+        <v>1.51</v>
+      </c>
+      <c r="AT102">
+        <v>3.35</v>
+      </c>
+      <c r="AU102">
+        <v>8</v>
+      </c>
+      <c r="AV102">
+        <v>6</v>
+      </c>
+      <c r="AW102">
+        <v>9</v>
+      </c>
+      <c r="AX102">
+        <v>10</v>
+      </c>
+      <c r="AY102">
+        <v>17</v>
+      </c>
+      <c r="AZ102">
+        <v>16</v>
+      </c>
+      <c r="BA102">
+        <v>5</v>
+      </c>
+      <c r="BB102">
+        <v>5</v>
+      </c>
+      <c r="BC102">
+        <v>10</v>
+      </c>
+      <c r="BD102">
+        <v>0</v>
+      </c>
+      <c r="BE102">
+        <v>0</v>
+      </c>
+      <c r="BF102">
+        <v>0</v>
+      </c>
+      <c r="BG102">
+        <v>0</v>
+      </c>
+      <c r="BH102">
+        <v>0</v>
+      </c>
+      <c r="BI102">
+        <v>0</v>
+      </c>
+      <c r="BJ102">
+        <v>0</v>
+      </c>
+      <c r="BK102">
+        <v>0</v>
+      </c>
+      <c r="BL102">
+        <v>0</v>
+      </c>
+      <c r="BM102">
+        <v>0</v>
+      </c>
+      <c r="BN102">
+        <v>0</v>
+      </c>
+      <c r="BO102">
+        <v>0</v>
+      </c>
+      <c r="BP102">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="198">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>['31', '39']</t>
+  </si>
+  <si>
+    <t>['22', '51', '77']</t>
   </si>
   <si>
     <t>['83']</t>
@@ -966,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP102"/>
+  <dimension ref="A1:BP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1300,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1712,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ4">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1840,7 +1843,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2458,7 +2461,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3282,7 +3285,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3566,10 +3569,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR13">
         <v>1.72</v>
@@ -3978,10 +3981,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ15">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR15">
         <v>1.3</v>
@@ -4106,7 +4109,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4518,7 +4521,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5136,7 +5139,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5342,7 +5345,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5420,7 +5423,7 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22">
         <v>1.64</v>
@@ -5629,7 +5632,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR23">
         <v>0.7</v>
@@ -5754,7 +5757,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5960,7 +5963,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6038,10 +6041,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR25">
         <v>1.83</v>
@@ -6244,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ26">
         <v>0.7</v>
@@ -6372,7 +6375,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6784,7 +6787,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7071,7 +7074,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ30">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR30">
         <v>1.03</v>
@@ -7196,7 +7199,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7895,7 +7898,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -8098,7 +8101,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ35">
         <v>1.1</v>
@@ -8304,7 +8307,7 @@
         <v>1.2</v>
       </c>
       <c r="AP36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8432,7 +8435,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8844,7 +8847,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -8925,7 +8928,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ39">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR39">
         <v>2.18</v>
@@ -9462,7 +9465,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9540,7 +9543,7 @@
         <v>1.25</v>
       </c>
       <c r="AP42">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ42">
         <v>1.64</v>
@@ -9874,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10080,7 +10083,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10161,7 +10164,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ45">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR45">
         <v>1.07</v>
@@ -10492,7 +10495,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10698,7 +10701,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10779,7 +10782,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR48">
         <v>1.28</v>
@@ -11110,7 +11113,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11397,7 +11400,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ51">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR51">
         <v>1.32</v>
@@ -11522,7 +11525,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11600,7 +11603,7 @@
         <v>0.2</v>
       </c>
       <c r="AP52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ52">
         <v>0.5</v>
@@ -11934,7 +11937,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12015,7 +12018,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12140,7 +12143,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12218,7 +12221,7 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ55">
         <v>2.1</v>
@@ -12346,7 +12349,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12552,7 +12555,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12758,7 +12761,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12964,7 +12967,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13170,7 +13173,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13376,7 +13379,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13582,7 +13585,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13663,7 +13666,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ62">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -13788,7 +13791,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13866,7 +13869,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ63">
         <v>1.6</v>
@@ -13994,7 +13997,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14200,7 +14203,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14281,7 +14284,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14484,7 +14487,7 @@
         <v>0.67</v>
       </c>
       <c r="AP66">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ66">
         <v>0.5</v>
@@ -15024,7 +15027,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15230,7 +15233,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15436,7 +15439,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16132,7 +16135,7 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ74">
         <v>1.6</v>
@@ -16260,7 +16263,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16466,7 +16469,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16547,7 +16550,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR76">
         <v>1.07</v>
@@ -16878,7 +16881,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -16959,7 +16962,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ78">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR78">
         <v>1.13</v>
@@ -17084,7 +17087,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17162,7 +17165,7 @@
         <v>2.43</v>
       </c>
       <c r="AP79">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ79">
         <v>2.4</v>
@@ -17496,7 +17499,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17702,7 +17705,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18195,7 +18198,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR84">
         <v>1.41</v>
@@ -18398,7 +18401,7 @@
         <v>0.86</v>
       </c>
       <c r="AP85">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ85">
         <v>0.7</v>
@@ -18732,7 +18735,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18938,7 +18941,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19144,7 +19147,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19431,7 +19434,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ90">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR90">
         <v>1.64</v>
@@ -19556,7 +19559,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19634,7 +19637,7 @@
         <v>1.88</v>
       </c>
       <c r="AP91">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ91">
         <v>2.1</v>
@@ -19762,7 +19765,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20252,7 +20255,7 @@
         <v>1.22</v>
       </c>
       <c r="AP94">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20458,10 +20461,10 @@
         <v>0.11</v>
       </c>
       <c r="AP95">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -20586,7 +20589,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20792,7 +20795,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -20998,7 +21001,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21204,7 +21207,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21410,7 +21413,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21616,7 +21619,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21822,7 +21825,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -21979,6 +21982,418 @@
       </c>
       <c r="BP102">
         <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7483774</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F103">
+        <v>21</v>
+      </c>
+      <c r="G103" t="s">
+        <v>72</v>
+      </c>
+      <c r="H103" t="s">
+        <v>74</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
+        <v>81</v>
+      </c>
+      <c r="P103" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q103">
+        <v>4.52</v>
+      </c>
+      <c r="R103">
+        <v>2.28</v>
+      </c>
+      <c r="S103">
+        <v>2.43</v>
+      </c>
+      <c r="T103">
+        <v>1.35</v>
+      </c>
+      <c r="U103">
+        <v>3.06</v>
+      </c>
+      <c r="V103">
+        <v>2.77</v>
+      </c>
+      <c r="W103">
+        <v>1.41</v>
+      </c>
+      <c r="X103">
+        <v>6</v>
+      </c>
+      <c r="Y103">
+        <v>1.09</v>
+      </c>
+      <c r="Z103">
+        <v>3.6</v>
+      </c>
+      <c r="AA103">
+        <v>3.55</v>
+      </c>
+      <c r="AB103">
+        <v>1.96</v>
+      </c>
+      <c r="AC103">
+        <v>1.02</v>
+      </c>
+      <c r="AD103">
+        <v>10</v>
+      </c>
+      <c r="AE103">
+        <v>1.25</v>
+      </c>
+      <c r="AF103">
+        <v>3.6</v>
+      </c>
+      <c r="AG103">
+        <v>1.75</v>
+      </c>
+      <c r="AH103">
+        <v>1.91</v>
+      </c>
+      <c r="AI103">
+        <v>1.73</v>
+      </c>
+      <c r="AJ103">
+        <v>2</v>
+      </c>
+      <c r="AK103">
+        <v>2</v>
+      </c>
+      <c r="AL103">
+        <v>1.29</v>
+      </c>
+      <c r="AM103">
+        <v>1.22</v>
+      </c>
+      <c r="AN103">
+        <v>1.4</v>
+      </c>
+      <c r="AO103">
+        <v>1.33</v>
+      </c>
+      <c r="AP103">
+        <v>1.36</v>
+      </c>
+      <c r="AQ103">
+        <v>1.3</v>
+      </c>
+      <c r="AR103">
+        <v>1.45</v>
+      </c>
+      <c r="AS103">
+        <v>1.63</v>
+      </c>
+      <c r="AT103">
+        <v>3.08</v>
+      </c>
+      <c r="AU103">
+        <v>7</v>
+      </c>
+      <c r="AV103">
+        <v>4</v>
+      </c>
+      <c r="AW103">
+        <v>6</v>
+      </c>
+      <c r="AX103">
+        <v>11</v>
+      </c>
+      <c r="AY103">
+        <v>13</v>
+      </c>
+      <c r="AZ103">
+        <v>15</v>
+      </c>
+      <c r="BA103">
+        <v>6</v>
+      </c>
+      <c r="BB103">
+        <v>4</v>
+      </c>
+      <c r="BC103">
+        <v>10</v>
+      </c>
+      <c r="BD103">
+        <v>3.02</v>
+      </c>
+      <c r="BE103">
+        <v>8.6</v>
+      </c>
+      <c r="BF103">
+        <v>1.49</v>
+      </c>
+      <c r="BG103">
+        <v>1.19</v>
+      </c>
+      <c r="BH103">
+        <v>3.75</v>
+      </c>
+      <c r="BI103">
+        <v>1.39</v>
+      </c>
+      <c r="BJ103">
+        <v>2.59</v>
+      </c>
+      <c r="BK103">
+        <v>1.7</v>
+      </c>
+      <c r="BL103">
+        <v>1.98</v>
+      </c>
+      <c r="BM103">
+        <v>2.14</v>
+      </c>
+      <c r="BN103">
+        <v>1.57</v>
+      </c>
+      <c r="BO103">
+        <v>2.83</v>
+      </c>
+      <c r="BP103">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7483776</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45704.5625</v>
+      </c>
+      <c r="F104">
+        <v>21</v>
+      </c>
+      <c r="G104" t="s">
+        <v>70</v>
+      </c>
+      <c r="H104" t="s">
+        <v>75</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>3</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>3</v>
+      </c>
+      <c r="O104" t="s">
+        <v>147</v>
+      </c>
+      <c r="P104" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q104">
+        <v>1.73</v>
+      </c>
+      <c r="R104">
+        <v>2.4</v>
+      </c>
+      <c r="S104">
+        <v>8.5</v>
+      </c>
+      <c r="T104">
+        <v>1.33</v>
+      </c>
+      <c r="U104">
+        <v>3.25</v>
+      </c>
+      <c r="V104">
+        <v>2.63</v>
+      </c>
+      <c r="W104">
+        <v>1.44</v>
+      </c>
+      <c r="X104">
+        <v>6</v>
+      </c>
+      <c r="Y104">
+        <v>1.11</v>
+      </c>
+      <c r="Z104">
+        <v>1.28</v>
+      </c>
+      <c r="AA104">
+        <v>5.5</v>
+      </c>
+      <c r="AB104">
+        <v>9.1</v>
+      </c>
+      <c r="AC104">
+        <v>1.03</v>
+      </c>
+      <c r="AD104">
+        <v>10</v>
+      </c>
+      <c r="AE104">
+        <v>1.22</v>
+      </c>
+      <c r="AF104">
+        <v>4</v>
+      </c>
+      <c r="AG104">
+        <v>1.79</v>
+      </c>
+      <c r="AH104">
+        <v>1.95</v>
+      </c>
+      <c r="AI104">
+        <v>2.25</v>
+      </c>
+      <c r="AJ104">
+        <v>1.57</v>
+      </c>
+      <c r="AK104">
+        <v>1.04</v>
+      </c>
+      <c r="AL104">
+        <v>1.11</v>
+      </c>
+      <c r="AM104">
+        <v>3.6</v>
+      </c>
+      <c r="AN104">
+        <v>2.1</v>
+      </c>
+      <c r="AO104">
+        <v>0.2</v>
+      </c>
+      <c r="AP104">
+        <v>2.18</v>
+      </c>
+      <c r="AQ104">
+        <v>0.18</v>
+      </c>
+      <c r="AR104">
+        <v>1.82</v>
+      </c>
+      <c r="AS104">
+        <v>1.33</v>
+      </c>
+      <c r="AT104">
+        <v>3.15</v>
+      </c>
+      <c r="AU104">
+        <v>8</v>
+      </c>
+      <c r="AV104">
+        <v>3</v>
+      </c>
+      <c r="AW104">
+        <v>2</v>
+      </c>
+      <c r="AX104">
+        <v>6</v>
+      </c>
+      <c r="AY104">
+        <v>10</v>
+      </c>
+      <c r="AZ104">
+        <v>9</v>
+      </c>
+      <c r="BA104">
+        <v>4</v>
+      </c>
+      <c r="BB104">
+        <v>3</v>
+      </c>
+      <c r="BC104">
+        <v>7</v>
+      </c>
+      <c r="BD104">
+        <v>1.02</v>
+      </c>
+      <c r="BE104">
+        <v>14.75</v>
+      </c>
+      <c r="BF104">
+        <v>14.5</v>
+      </c>
+      <c r="BG104">
+        <v>1.19</v>
+      </c>
+      <c r="BH104">
+        <v>3.74</v>
+      </c>
+      <c r="BI104">
+        <v>1.39</v>
+      </c>
+      <c r="BJ104">
+        <v>2.59</v>
+      </c>
+      <c r="BK104">
+        <v>1.71</v>
+      </c>
+      <c r="BL104">
+        <v>1.97</v>
+      </c>
+      <c r="BM104">
+        <v>2.14</v>
+      </c>
+      <c r="BN104">
+        <v>1.57</v>
+      </c>
+      <c r="BO104">
+        <v>2.83</v>
+      </c>
+      <c r="BP104">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="199">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>['22', '51', '77']</t>
+  </si>
+  <si>
+    <t>['42']</t>
   </si>
   <si>
     <t>['83']</t>
@@ -969,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP104"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1509,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ3">
         <v>2.1</v>
@@ -1843,7 +1846,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -1924,7 +1927,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2461,7 +2464,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3157,10 +3160,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR11">
         <v>1.27</v>
@@ -3285,7 +3288,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4109,7 +4112,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4521,7 +4524,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5139,7 +5142,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5220,7 +5223,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR21">
         <v>1.05</v>
@@ -5345,7 +5348,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5757,7 +5760,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5835,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24">
         <v>1.6</v>
@@ -5963,7 +5966,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6375,7 +6378,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6787,7 +6790,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7199,7 +7202,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7280,7 +7283,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR31">
         <v>1.26</v>
@@ -7483,7 +7486,7 @@
         <v>1.33</v>
       </c>
       <c r="AP32">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ32">
         <v>1.64</v>
@@ -8435,7 +8438,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8513,7 +8516,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37">
         <v>2.4</v>
@@ -8722,7 +8725,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ38">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR38">
         <v>1.19</v>
@@ -8847,7 +8850,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9465,7 +9468,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9877,7 +9880,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10083,7 +10086,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10495,7 +10498,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10701,7 +10704,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11113,7 +11116,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11397,7 +11400,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51">
         <v>0.18</v>
@@ -11525,7 +11528,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11606,7 +11609,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ52">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -11937,7 +11940,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12143,7 +12146,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12349,7 +12352,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12555,7 +12558,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12761,7 +12764,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12967,7 +12970,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13173,7 +13176,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13379,7 +13382,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13585,7 +13588,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13791,7 +13794,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13997,7 +14000,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14203,7 +14206,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14281,7 +14284,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ65">
         <v>1.3</v>
@@ -14490,7 +14493,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR66">
         <v>1.87</v>
@@ -15027,7 +15030,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15233,7 +15236,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15439,7 +15442,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15726,7 +15729,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR72">
         <v>1.36</v>
@@ -16263,7 +16266,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16341,7 +16344,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ75">
         <v>1.1</v>
@@ -16469,7 +16472,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16881,7 +16884,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17087,7 +17090,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17499,7 +17502,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17705,7 +17708,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18735,7 +18738,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18816,7 +18819,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ87">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -18941,7 +18944,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19147,7 +19150,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19225,7 +19228,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19559,7 +19562,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19765,7 +19768,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20052,7 +20055,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ93">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20589,7 +20592,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20667,7 +20670,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ96">
         <v>2.1</v>
@@ -20795,7 +20798,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -21001,7 +21004,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21207,7 +21210,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21413,7 +21416,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21619,7 +21622,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21825,7 +21828,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22394,6 +22397,212 @@
       </c>
       <c r="BP104">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7483775</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45705.5625</v>
+      </c>
+      <c r="F105">
+        <v>21</v>
+      </c>
+      <c r="G105" t="s">
+        <v>71</v>
+      </c>
+      <c r="H105" t="s">
+        <v>76</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>148</v>
+      </c>
+      <c r="P105" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q105">
+        <v>2.7</v>
+      </c>
+      <c r="R105">
+        <v>2.03</v>
+      </c>
+      <c r="S105">
+        <v>4.1</v>
+      </c>
+      <c r="T105">
+        <v>1.48</v>
+      </c>
+      <c r="U105">
+        <v>2.5</v>
+      </c>
+      <c r="V105">
+        <v>3.2</v>
+      </c>
+      <c r="W105">
+        <v>1.31</v>
+      </c>
+      <c r="X105">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y105">
+        <v>1.05</v>
+      </c>
+      <c r="Z105">
+        <v>2.11</v>
+      </c>
+      <c r="AA105">
+        <v>3.23</v>
+      </c>
+      <c r="AB105">
+        <v>3.47</v>
+      </c>
+      <c r="AC105">
+        <v>1.01</v>
+      </c>
+      <c r="AD105">
+        <v>8.5</v>
+      </c>
+      <c r="AE105">
+        <v>1.37</v>
+      </c>
+      <c r="AF105">
+        <v>2.95</v>
+      </c>
+      <c r="AG105">
+        <v>2.05</v>
+      </c>
+      <c r="AH105">
+        <v>1.61</v>
+      </c>
+      <c r="AI105">
+        <v>1.89</v>
+      </c>
+      <c r="AJ105">
+        <v>1.82</v>
+      </c>
+      <c r="AK105">
+        <v>1.29</v>
+      </c>
+      <c r="AL105">
+        <v>1.3</v>
+      </c>
+      <c r="AM105">
+        <v>1.66</v>
+      </c>
+      <c r="AN105">
+        <v>1.2</v>
+      </c>
+      <c r="AO105">
+        <v>0.5</v>
+      </c>
+      <c r="AP105">
+        <v>1.36</v>
+      </c>
+      <c r="AQ105">
+        <v>0.45</v>
+      </c>
+      <c r="AR105">
+        <v>1.39</v>
+      </c>
+      <c r="AS105">
+        <v>1.18</v>
+      </c>
+      <c r="AT105">
+        <v>2.57</v>
+      </c>
+      <c r="AU105">
+        <v>4</v>
+      </c>
+      <c r="AV105">
+        <v>5</v>
+      </c>
+      <c r="AW105">
+        <v>2</v>
+      </c>
+      <c r="AX105">
+        <v>13</v>
+      </c>
+      <c r="AY105">
+        <v>6</v>
+      </c>
+      <c r="AZ105">
+        <v>18</v>
+      </c>
+      <c r="BA105">
+        <v>1</v>
+      </c>
+      <c r="BB105">
+        <v>8</v>
+      </c>
+      <c r="BC105">
+        <v>9</v>
+      </c>
+      <c r="BD105">
+        <v>1.66</v>
+      </c>
+      <c r="BE105">
+        <v>8.1</v>
+      </c>
+      <c r="BF105">
+        <v>2.55</v>
+      </c>
+      <c r="BG105">
+        <v>1.33</v>
+      </c>
+      <c r="BH105">
+        <v>3</v>
+      </c>
+      <c r="BI105">
+        <v>1.58</v>
+      </c>
+      <c r="BJ105">
+        <v>2.23</v>
+      </c>
+      <c r="BK105">
+        <v>1.96</v>
+      </c>
+      <c r="BL105">
+        <v>1.75</v>
+      </c>
+      <c r="BM105">
+        <v>2.5</v>
+      </c>
+      <c r="BN105">
+        <v>1.47</v>
+      </c>
+      <c r="BO105">
+        <v>3.3</v>
+      </c>
+      <c r="BP105">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="201">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -463,6 +463,9 @@
     <t>['42']</t>
   </si>
   <si>
+    <t>['13', '16']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -611,6 +614,9 @@
   </si>
   <si>
     <t>['5', '59', '80']</t>
+  </si>
+  <si>
+    <t>['25', '33']</t>
   </si>
 </sst>
 </file>
@@ -972,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1846,7 +1852,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2336,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ7">
         <v>0.7</v>
@@ -2464,7 +2470,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3288,7 +3294,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4112,7 +4118,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4190,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4524,7 +4530,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5142,7 +5148,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5348,7 +5354,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5760,7 +5766,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5966,7 +5972,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6378,7 +6384,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6790,7 +6796,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7202,7 +7208,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7280,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ31">
         <v>0.45</v>
@@ -8438,7 +8444,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8850,7 +8856,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9468,7 +9474,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9880,7 +9886,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -9958,7 +9964,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ44">
         <v>1.6</v>
@@ -10086,7 +10092,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10370,7 +10376,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ46">
         <v>1.1</v>
@@ -10498,7 +10504,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10704,7 +10710,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11116,7 +11122,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11528,7 +11534,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11940,7 +11946,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12146,7 +12152,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12352,7 +12358,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12558,7 +12564,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12764,7 +12770,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12842,7 +12848,7 @@
         <v>2.2</v>
       </c>
       <c r="AP58">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ58">
         <v>2.4</v>
@@ -12970,7 +12976,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13176,7 +13182,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13382,7 +13388,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13588,7 +13594,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13794,7 +13800,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14000,7 +14006,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14206,7 +14212,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -15030,7 +15036,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15236,7 +15242,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15442,7 +15448,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15520,7 +15526,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ71">
         <v>2.1</v>
@@ -15932,7 +15938,7 @@
         <v>0.86</v>
       </c>
       <c r="AP73">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ73">
         <v>1.64</v>
@@ -16266,7 +16272,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16472,7 +16478,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16884,7 +16890,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17090,7 +17096,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17502,7 +17508,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17708,7 +17714,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18198,7 +18204,7 @@
         <v>1.38</v>
       </c>
       <c r="AP84">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ84">
         <v>1.3</v>
@@ -18738,7 +18744,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18944,7 +18950,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19150,7 +19156,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19562,7 +19568,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19768,7 +19774,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20592,7 +20598,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20798,7 +20804,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -21004,7 +21010,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21082,7 +21088,7 @@
         <v>0.78</v>
       </c>
       <c r="AP98">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ98">
         <v>0.7</v>
@@ -21210,7 +21216,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21416,7 +21422,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21622,7 +21628,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21828,7 +21834,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22603,6 +22609,212 @@
       </c>
       <c r="BP105">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7483779</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45709.5625</v>
+      </c>
+      <c r="F106">
+        <v>22</v>
+      </c>
+      <c r="G106" t="s">
+        <v>75</v>
+      </c>
+      <c r="H106" t="s">
+        <v>79</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+      <c r="J106">
+        <v>2</v>
+      </c>
+      <c r="K106">
+        <v>4</v>
+      </c>
+      <c r="L106">
+        <v>2</v>
+      </c>
+      <c r="M106">
+        <v>2</v>
+      </c>
+      <c r="N106">
+        <v>4</v>
+      </c>
+      <c r="O106" t="s">
+        <v>149</v>
+      </c>
+      <c r="P106" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q106">
+        <v>0</v>
+      </c>
+      <c r="R106">
+        <v>0</v>
+      </c>
+      <c r="S106">
+        <v>0</v>
+      </c>
+      <c r="T106">
+        <v>0</v>
+      </c>
+      <c r="U106">
+        <v>0</v>
+      </c>
+      <c r="V106">
+        <v>0</v>
+      </c>
+      <c r="W106">
+        <v>0</v>
+      </c>
+      <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106">
+        <v>0</v>
+      </c>
+      <c r="Z106">
+        <v>2.37</v>
+      </c>
+      <c r="AA106">
+        <v>2.94</v>
+      </c>
+      <c r="AB106">
+        <v>3.25</v>
+      </c>
+      <c r="AC106">
+        <v>0</v>
+      </c>
+      <c r="AD106">
+        <v>0</v>
+      </c>
+      <c r="AE106">
+        <v>0</v>
+      </c>
+      <c r="AF106">
+        <v>0</v>
+      </c>
+      <c r="AG106">
+        <v>2.41</v>
+      </c>
+      <c r="AH106">
+        <v>1.5</v>
+      </c>
+      <c r="AI106">
+        <v>0</v>
+      </c>
+      <c r="AJ106">
+        <v>0</v>
+      </c>
+      <c r="AK106">
+        <v>0</v>
+      </c>
+      <c r="AL106">
+        <v>0</v>
+      </c>
+      <c r="AM106">
+        <v>0</v>
+      </c>
+      <c r="AN106">
+        <v>1.1</v>
+      </c>
+      <c r="AO106">
+        <v>1</v>
+      </c>
+      <c r="AP106">
+        <v>1.09</v>
+      </c>
+      <c r="AQ106">
+        <v>1</v>
+      </c>
+      <c r="AR106">
+        <v>1.46</v>
+      </c>
+      <c r="AS106">
+        <v>1.27</v>
+      </c>
+      <c r="AT106">
+        <v>2.73</v>
+      </c>
+      <c r="AU106">
+        <v>-1</v>
+      </c>
+      <c r="AV106">
+        <v>-1</v>
+      </c>
+      <c r="AW106">
+        <v>-1</v>
+      </c>
+      <c r="AX106">
+        <v>-1</v>
+      </c>
+      <c r="AY106">
+        <v>-1</v>
+      </c>
+      <c r="AZ106">
+        <v>-1</v>
+      </c>
+      <c r="BA106">
+        <v>-1</v>
+      </c>
+      <c r="BB106">
+        <v>-1</v>
+      </c>
+      <c r="BC106">
+        <v>-1</v>
+      </c>
+      <c r="BD106">
+        <v>0</v>
+      </c>
+      <c r="BE106">
+        <v>0</v>
+      </c>
+      <c r="BF106">
+        <v>0</v>
+      </c>
+      <c r="BG106">
+        <v>0</v>
+      </c>
+      <c r="BH106">
+        <v>0</v>
+      </c>
+      <c r="BI106">
+        <v>0</v>
+      </c>
+      <c r="BJ106">
+        <v>0</v>
+      </c>
+      <c r="BK106">
+        <v>0</v>
+      </c>
+      <c r="BL106">
+        <v>0</v>
+      </c>
+      <c r="BM106">
+        <v>0</v>
+      </c>
+      <c r="BN106">
+        <v>0</v>
+      </c>
+      <c r="BO106">
+        <v>0</v>
+      </c>
+      <c r="BP106">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="204">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -466,6 +466,12 @@
     <t>['13', '16']</t>
   </si>
   <si>
+    <t>['36', '68']</t>
+  </si>
+  <si>
+    <t>['11', '44']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -617,6 +623,9 @@
   </si>
   <si>
     <t>['25', '33']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
 </sst>
 </file>
@@ -978,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1521,7 +1530,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ3">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1852,7 +1861,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -1930,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ5">
         <v>0.45</v>
@@ -2470,7 +2479,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2551,7 +2560,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ8">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2960,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3294,7 +3303,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3375,7 +3384,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ12">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3784,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ14">
         <v>1.64</v>
@@ -4118,7 +4127,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4530,7 +4539,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4814,10 +4823,10 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.75</v>
@@ -5020,10 +5029,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ20">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5148,7 +5157,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5354,7 +5363,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5766,7 +5775,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5972,7 +5981,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6384,7 +6393,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6465,7 +6474,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ27">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR27">
         <v>0.98</v>
@@ -6668,7 +6677,7 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ28">
         <v>2.4</v>
@@ -6796,7 +6805,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7080,7 +7089,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ30">
         <v>0.18</v>
@@ -7208,7 +7217,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7698,7 +7707,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8113,7 +8122,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ35">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>2.01</v>
@@ -8444,7 +8453,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8728,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ38">
         <v>0.45</v>
@@ -8856,7 +8865,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9140,10 +9149,10 @@
         <v>2.25</v>
       </c>
       <c r="AP40">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ40">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9474,7 +9483,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9761,7 +9770,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ43">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>1.26</v>
@@ -9886,7 +9895,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10092,7 +10101,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10379,7 +10388,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ46">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.5</v>
@@ -10504,7 +10513,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10710,7 +10719,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10788,7 +10797,7 @@
         <v>1.25</v>
       </c>
       <c r="AP48">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ48">
         <v>1.3</v>
@@ -11122,7 +11131,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11534,7 +11543,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11946,7 +11955,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12024,7 +12033,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ54">
         <v>1.3</v>
@@ -12152,7 +12161,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12233,7 +12242,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ55">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR55">
         <v>1.92</v>
@@ -12358,7 +12367,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12564,7 +12573,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12645,7 +12654,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>2.09</v>
@@ -12770,7 +12779,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12976,7 +12985,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13182,7 +13191,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13260,7 +13269,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ60">
         <v>1.6</v>
@@ -13388,7 +13397,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13594,7 +13603,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13800,7 +13809,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14006,7 +14015,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14212,7 +14221,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14908,7 +14917,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ68">
         <v>0.7</v>
@@ -15036,7 +15045,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15114,10 +15123,10 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ69">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -15242,7 +15251,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15448,7 +15457,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15529,7 +15538,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ71">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -16272,7 +16281,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16353,7 +16362,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ75">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.44</v>
@@ -16478,7 +16487,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16765,7 +16774,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ77">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR77">
         <v>2</v>
@@ -16890,7 +16899,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17096,7 +17105,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17508,7 +17517,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17714,7 +17723,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18001,7 +18010,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ83">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.05</v>
@@ -18616,7 +18625,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ86">
         <v>0.7</v>
@@ -18744,7 +18753,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18950,7 +18959,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19028,7 +19037,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ88">
         <v>2.4</v>
@@ -19156,7 +19165,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19440,7 +19449,7 @@
         <v>0.13</v>
       </c>
       <c r="AP90">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ90">
         <v>0.18</v>
@@ -19568,7 +19577,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19649,7 +19658,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ91">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR91">
         <v>1.34</v>
@@ -19774,7 +19783,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20058,7 +20067,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP93">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ93">
         <v>0.45</v>
@@ -20598,7 +20607,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20679,7 +20688,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ96">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -20804,7 +20813,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -20882,7 +20891,7 @@
         <v>1.1</v>
       </c>
       <c r="AP97">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21010,7 +21019,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21216,7 +21225,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21297,7 +21306,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ99">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21422,7 +21431,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21628,7 +21637,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21834,7 +21843,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -21912,7 +21921,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ102">
         <v>1.64</v>
@@ -22658,7 +22667,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22751,31 +22760,31 @@
         <v>2.73</v>
       </c>
       <c r="AU106">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV106">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW106">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX106">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AY106">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AZ106">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BA106">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB106">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BC106">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BD106">
         <v>0</v>
@@ -22815,6 +22824,418 @@
       </c>
       <c r="BP106">
         <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7483778</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45710.375</v>
+      </c>
+      <c r="F107">
+        <v>22</v>
+      </c>
+      <c r="G107" t="s">
+        <v>78</v>
+      </c>
+      <c r="H107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>3</v>
+      </c>
+      <c r="O107" t="s">
+        <v>150</v>
+      </c>
+      <c r="P107" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q107">
+        <v>2.82</v>
+      </c>
+      <c r="R107">
+        <v>2.01</v>
+      </c>
+      <c r="S107">
+        <v>3.78</v>
+      </c>
+      <c r="T107">
+        <v>1.44</v>
+      </c>
+      <c r="U107">
+        <v>2.62</v>
+      </c>
+      <c r="V107">
+        <v>3.1</v>
+      </c>
+      <c r="W107">
+        <v>1.33</v>
+      </c>
+      <c r="X107">
+        <v>8.5</v>
+      </c>
+      <c r="Y107">
+        <v>1.05</v>
+      </c>
+      <c r="Z107">
+        <v>2.24</v>
+      </c>
+      <c r="AA107">
+        <v>3.3</v>
+      </c>
+      <c r="AB107">
+        <v>3.12</v>
+      </c>
+      <c r="AC107">
+        <v>1.03</v>
+      </c>
+      <c r="AD107">
+        <v>7.7</v>
+      </c>
+      <c r="AE107">
+        <v>1.33</v>
+      </c>
+      <c r="AF107">
+        <v>2.83</v>
+      </c>
+      <c r="AG107">
+        <v>1.94</v>
+      </c>
+      <c r="AH107">
+        <v>1.8</v>
+      </c>
+      <c r="AI107">
+        <v>1.83</v>
+      </c>
+      <c r="AJ107">
+        <v>1.83</v>
+      </c>
+      <c r="AK107">
+        <v>1.31</v>
+      </c>
+      <c r="AL107">
+        <v>1.29</v>
+      </c>
+      <c r="AM107">
+        <v>1.57</v>
+      </c>
+      <c r="AN107">
+        <v>2.1</v>
+      </c>
+      <c r="AO107">
+        <v>2.1</v>
+      </c>
+      <c r="AP107">
+        <v>2.18</v>
+      </c>
+      <c r="AQ107">
+        <v>1.91</v>
+      </c>
+      <c r="AR107">
+        <v>1.54</v>
+      </c>
+      <c r="AS107">
+        <v>1.36</v>
+      </c>
+      <c r="AT107">
+        <v>2.9</v>
+      </c>
+      <c r="AU107">
+        <v>4</v>
+      </c>
+      <c r="AV107">
+        <v>3</v>
+      </c>
+      <c r="AW107">
+        <v>3</v>
+      </c>
+      <c r="AX107">
+        <v>6</v>
+      </c>
+      <c r="AY107">
+        <v>7</v>
+      </c>
+      <c r="AZ107">
+        <v>9</v>
+      </c>
+      <c r="BA107">
+        <v>1</v>
+      </c>
+      <c r="BB107">
+        <v>7</v>
+      </c>
+      <c r="BC107">
+        <v>8</v>
+      </c>
+      <c r="BD107">
+        <v>1.72</v>
+      </c>
+      <c r="BE107">
+        <v>7.7</v>
+      </c>
+      <c r="BF107">
+        <v>2.46</v>
+      </c>
+      <c r="BG107">
+        <v>1.46</v>
+      </c>
+      <c r="BH107">
+        <v>2.38</v>
+      </c>
+      <c r="BI107">
+        <v>1.84</v>
+      </c>
+      <c r="BJ107">
+        <v>1.82</v>
+      </c>
+      <c r="BK107">
+        <v>2.41</v>
+      </c>
+      <c r="BL107">
+        <v>1.45</v>
+      </c>
+      <c r="BM107">
+        <v>3.34</v>
+      </c>
+      <c r="BN107">
+        <v>1.24</v>
+      </c>
+      <c r="BO107">
+        <v>4.33</v>
+      </c>
+      <c r="BP107">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7483782</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F108">
+        <v>22</v>
+      </c>
+      <c r="G108" t="s">
+        <v>73</v>
+      </c>
+      <c r="H108" t="s">
+        <v>72</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>2</v>
+      </c>
+      <c r="O108" t="s">
+        <v>151</v>
+      </c>
+      <c r="P108" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q108">
+        <v>2.03</v>
+      </c>
+      <c r="R108">
+        <v>2.24</v>
+      </c>
+      <c r="S108">
+        <v>5.6</v>
+      </c>
+      <c r="T108">
+        <v>1.33</v>
+      </c>
+      <c r="U108">
+        <v>3.08</v>
+      </c>
+      <c r="V108">
+        <v>2.66</v>
+      </c>
+      <c r="W108">
+        <v>1.43</v>
+      </c>
+      <c r="X108">
+        <v>6.3</v>
+      </c>
+      <c r="Y108">
+        <v>1.1</v>
+      </c>
+      <c r="Z108">
+        <v>1.63</v>
+      </c>
+      <c r="AA108">
+        <v>3.87</v>
+      </c>
+      <c r="AB108">
+        <v>5.1</v>
+      </c>
+      <c r="AC108">
+        <v>1.01</v>
+      </c>
+      <c r="AD108">
+        <v>11</v>
+      </c>
+      <c r="AE108">
+        <v>1.21</v>
+      </c>
+      <c r="AF108">
+        <v>3.58</v>
+      </c>
+      <c r="AG108">
+        <v>1.8</v>
+      </c>
+      <c r="AH108">
+        <v>1.94</v>
+      </c>
+      <c r="AI108">
+        <v>1.83</v>
+      </c>
+      <c r="AJ108">
+        <v>1.83</v>
+      </c>
+      <c r="AK108">
+        <v>1.1</v>
+      </c>
+      <c r="AL108">
+        <v>1.19</v>
+      </c>
+      <c r="AM108">
+        <v>2.38</v>
+      </c>
+      <c r="AN108">
+        <v>2.09</v>
+      </c>
+      <c r="AO108">
+        <v>1.1</v>
+      </c>
+      <c r="AP108">
+        <v>2.17</v>
+      </c>
+      <c r="AQ108">
+        <v>1</v>
+      </c>
+      <c r="AR108">
+        <v>1.88</v>
+      </c>
+      <c r="AS108">
+        <v>1.32</v>
+      </c>
+      <c r="AT108">
+        <v>3.2</v>
+      </c>
+      <c r="AU108">
+        <v>7</v>
+      </c>
+      <c r="AV108">
+        <v>4</v>
+      </c>
+      <c r="AW108">
+        <v>8</v>
+      </c>
+      <c r="AX108">
+        <v>4</v>
+      </c>
+      <c r="AY108">
+        <v>15</v>
+      </c>
+      <c r="AZ108">
+        <v>8</v>
+      </c>
+      <c r="BA108">
+        <v>9</v>
+      </c>
+      <c r="BB108">
+        <v>5</v>
+      </c>
+      <c r="BC108">
+        <v>14</v>
+      </c>
+      <c r="BD108">
+        <v>1.33</v>
+      </c>
+      <c r="BE108">
+        <v>9.1</v>
+      </c>
+      <c r="BF108">
+        <v>3.9</v>
+      </c>
+      <c r="BG108">
+        <v>1.25</v>
+      </c>
+      <c r="BH108">
+        <v>3.28</v>
+      </c>
+      <c r="BI108">
+        <v>1.47</v>
+      </c>
+      <c r="BJ108">
+        <v>2.35</v>
+      </c>
+      <c r="BK108">
+        <v>1.83</v>
+      </c>
+      <c r="BL108">
+        <v>1.83</v>
+      </c>
+      <c r="BM108">
+        <v>2.35</v>
+      </c>
+      <c r="BN108">
+        <v>1.47</v>
+      </c>
+      <c r="BO108">
+        <v>3.14</v>
+      </c>
+      <c r="BP108">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="206">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -472,6 +472,9 @@
     <t>['11', '44']</t>
   </si>
   <si>
+    <t>['7', '11', '16', '21', '58', '71', '75', '78', '90+2']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -626,6 +629,9 @@
   </si>
   <si>
     <t>['9']</t>
+  </si>
+  <si>
+    <t>['31']</t>
   </si>
 </sst>
 </file>
@@ -987,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP108"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1861,7 +1867,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2145,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ6">
         <v>1.64</v>
@@ -2354,7 +2360,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ7">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2479,7 +2485,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3303,7 +3309,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4127,7 +4133,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4539,7 +4545,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4617,10 +4623,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ18">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR18">
         <v>2.23</v>
@@ -5157,7 +5163,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5363,7 +5369,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5775,7 +5781,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5981,7 +5987,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6268,7 +6274,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ26">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR26">
         <v>1.62</v>
@@ -6393,7 +6399,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6805,7 +6811,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6883,7 +6889,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7217,7 +7223,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -8453,7 +8459,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8865,7 +8871,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -8943,7 +8949,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ39">
         <v>0.18</v>
@@ -9355,7 +9361,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ41">
         <v>1.6</v>
@@ -9483,7 +9489,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9895,7 +9901,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10101,7 +10107,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10513,7 +10519,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10719,7 +10725,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11006,7 +11012,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR49">
         <v>1.31</v>
@@ -11131,7 +11137,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11543,7 +11549,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11955,7 +11961,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12161,7 +12167,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12367,7 +12373,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12448,7 +12454,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ56">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12573,7 +12579,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12651,7 +12657,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -12779,7 +12785,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12985,7 +12991,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13191,7 +13197,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13397,7 +13403,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13478,7 +13484,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ61">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR61">
         <v>1.2</v>
@@ -13603,7 +13609,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13809,7 +13815,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14015,7 +14021,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14221,7 +14227,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14920,7 +14926,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ68">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR68">
         <v>1.5</v>
@@ -15045,7 +15051,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15251,7 +15257,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15329,7 +15335,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ70">
         <v>2.4</v>
@@ -15457,7 +15463,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16281,7 +16287,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16487,7 +16493,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16771,7 +16777,7 @@
         <v>2.14</v>
       </c>
       <c r="AP77">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ77">
         <v>1.91</v>
@@ -16899,7 +16905,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17105,7 +17111,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17517,7 +17523,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17723,7 +17729,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18422,7 +18428,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ85">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR85">
         <v>1.72</v>
@@ -18628,7 +18634,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ86">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR86">
         <v>1.46</v>
@@ -18753,7 +18759,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18831,7 +18837,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ87">
         <v>0.45</v>
@@ -18959,7 +18965,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19165,7 +19171,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19577,7 +19583,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19783,7 +19789,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19861,7 +19867,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ92">
         <v>1.64</v>
@@ -20607,7 +20613,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20813,7 +20819,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -21019,7 +21025,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21100,7 +21106,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ98">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21225,7 +21231,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21431,7 +21437,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21509,7 +21515,7 @@
         <v>1.44</v>
       </c>
       <c r="AP100">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ100">
         <v>1.6</v>
@@ -21637,7 +21643,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21843,7 +21849,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22667,7 +22673,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22873,7 +22879,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23236,6 +23242,212 @@
       </c>
       <c r="BP108">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7483781</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45711.5625</v>
+      </c>
+      <c r="F109">
+        <v>22</v>
+      </c>
+      <c r="G109" t="s">
+        <v>74</v>
+      </c>
+      <c r="H109" t="s">
+        <v>71</v>
+      </c>
+      <c r="I109">
+        <v>4</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>5</v>
+      </c>
+      <c r="L109">
+        <v>9</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>10</v>
+      </c>
+      <c r="O109" t="s">
+        <v>152</v>
+      </c>
+      <c r="P109" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q109">
+        <v>2.2</v>
+      </c>
+      <c r="R109">
+        <v>2.2</v>
+      </c>
+      <c r="S109">
+        <v>5</v>
+      </c>
+      <c r="T109">
+        <v>1.36</v>
+      </c>
+      <c r="U109">
+        <v>3</v>
+      </c>
+      <c r="V109">
+        <v>2.75</v>
+      </c>
+      <c r="W109">
+        <v>1.4</v>
+      </c>
+      <c r="X109">
+        <v>6.5</v>
+      </c>
+      <c r="Y109">
+        <v>1.1</v>
+      </c>
+      <c r="Z109">
+        <v>1.51</v>
+      </c>
+      <c r="AA109">
+        <v>4.33</v>
+      </c>
+      <c r="AB109">
+        <v>5.6</v>
+      </c>
+      <c r="AC109">
+        <v>1.01</v>
+      </c>
+      <c r="AD109">
+        <v>12.4</v>
+      </c>
+      <c r="AE109">
+        <v>1.22</v>
+      </c>
+      <c r="AF109">
+        <v>3.5</v>
+      </c>
+      <c r="AG109">
+        <v>1.67</v>
+      </c>
+      <c r="AH109">
+        <v>2</v>
+      </c>
+      <c r="AI109">
+        <v>1.83</v>
+      </c>
+      <c r="AJ109">
+        <v>1.83</v>
+      </c>
+      <c r="AK109">
+        <v>1.16</v>
+      </c>
+      <c r="AL109">
+        <v>1.22</v>
+      </c>
+      <c r="AM109">
+        <v>2.17</v>
+      </c>
+      <c r="AN109">
+        <v>1.73</v>
+      </c>
+      <c r="AO109">
+        <v>0.7</v>
+      </c>
+      <c r="AP109">
+        <v>1.83</v>
+      </c>
+      <c r="AQ109">
+        <v>0.64</v>
+      </c>
+      <c r="AR109">
+        <v>2.1</v>
+      </c>
+      <c r="AS109">
+        <v>1.31</v>
+      </c>
+      <c r="AT109">
+        <v>3.41</v>
+      </c>
+      <c r="AU109">
+        <v>12</v>
+      </c>
+      <c r="AV109">
+        <v>6</v>
+      </c>
+      <c r="AW109">
+        <v>5</v>
+      </c>
+      <c r="AX109">
+        <v>4</v>
+      </c>
+      <c r="AY109">
+        <v>17</v>
+      </c>
+      <c r="AZ109">
+        <v>10</v>
+      </c>
+      <c r="BA109">
+        <v>4</v>
+      </c>
+      <c r="BB109">
+        <v>4</v>
+      </c>
+      <c r="BC109">
+        <v>8</v>
+      </c>
+      <c r="BD109">
+        <v>1.27</v>
+      </c>
+      <c r="BE109">
+        <v>10.75</v>
+      </c>
+      <c r="BF109">
+        <v>4.2</v>
+      </c>
+      <c r="BG109">
+        <v>1.22</v>
+      </c>
+      <c r="BH109">
+        <v>3.8</v>
+      </c>
+      <c r="BI109">
+        <v>1.33</v>
+      </c>
+      <c r="BJ109">
+        <v>2.83</v>
+      </c>
+      <c r="BK109">
+        <v>1.59</v>
+      </c>
+      <c r="BL109">
+        <v>2.1</v>
+      </c>
+      <c r="BM109">
+        <v>2</v>
+      </c>
+      <c r="BN109">
+        <v>1.69</v>
+      </c>
+      <c r="BO109">
+        <v>2.56</v>
+      </c>
+      <c r="BP109">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="207">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -633,6 +633,9 @@
   <si>
     <t>['31']</t>
   </si>
+  <si>
+    <t>['20', '55', '64', '74']</t>
+  </si>
 </sst>
 </file>
 
@@ -993,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1533,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3">
         <v>1.91</v>
@@ -1742,7 +1745,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ4">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1948,7 +1951,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ5">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2769,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ9">
         <v>2.4</v>
@@ -3181,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ11">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR11">
         <v>1.27</v>
@@ -3387,7 +3390,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ12">
         <v>1.91</v>
@@ -4008,7 +4011,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ15">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR15">
         <v>1.3</v>
@@ -5241,10 +5244,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR21">
         <v>1.05</v>
@@ -5653,10 +5656,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ23">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR23">
         <v>0.7</v>
@@ -5859,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR24">
         <v>1.24</v>
@@ -7098,7 +7101,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ30">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR30">
         <v>1.03</v>
@@ -7304,7 +7307,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ31">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR31">
         <v>1.26</v>
@@ -7507,7 +7510,7 @@
         <v>1.33</v>
       </c>
       <c r="AP32">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32">
         <v>1.64</v>
@@ -7919,7 +7922,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34">
         <v>1.3</v>
@@ -8537,7 +8540,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>2.4</v>
@@ -8746,7 +8749,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ38">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR38">
         <v>1.19</v>
@@ -8952,7 +8955,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR39">
         <v>2.18</v>
@@ -9364,7 +9367,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ41">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR41">
         <v>2.19</v>
@@ -9773,7 +9776,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -9982,7 +9985,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ44">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10597,7 +10600,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ47">
         <v>2.4</v>
@@ -11009,7 +11012,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ49">
         <v>0.64</v>
@@ -11218,7 +11221,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ50">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11421,10 +11424,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR51">
         <v>1.32</v>
@@ -11630,7 +11633,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ52">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -11833,7 +11836,7 @@
         <v>1.2</v>
       </c>
       <c r="AP53">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ53">
         <v>1.64</v>
@@ -12451,7 +12454,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ56">
         <v>0.64</v>
@@ -13069,7 +13072,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13278,7 +13281,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR60">
         <v>1.4</v>
@@ -13687,10 +13690,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ62">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -13896,7 +13899,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ63">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR63">
         <v>1.5</v>
@@ -14099,7 +14102,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ64">
         <v>1.64</v>
@@ -14305,7 +14308,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ65">
         <v>1.3</v>
@@ -14514,7 +14517,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ66">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR66">
         <v>1.87</v>
@@ -15747,10 +15750,10 @@
         <v>0.57</v>
       </c>
       <c r="AP72">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ72">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR72">
         <v>1.36</v>
@@ -16162,7 +16165,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ74">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR74">
         <v>1.87</v>
@@ -16365,7 +16368,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16571,7 +16574,7 @@
         <v>1.14</v>
       </c>
       <c r="AP76">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ76">
         <v>1.3</v>
@@ -16986,7 +16989,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ78">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR78">
         <v>1.13</v>
@@ -17395,10 +17398,10 @@
         <v>1.71</v>
       </c>
       <c r="AP80">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ80">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR80">
         <v>1.04</v>
@@ -17807,10 +17810,10 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ82">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR82">
         <v>1.46</v>
@@ -18013,7 +18016,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18840,7 +18843,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ87">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19249,7 +19252,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19458,7 +19461,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ90">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR90">
         <v>1.64</v>
@@ -20076,7 +20079,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ93">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20488,7 +20491,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ95">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -20691,7 +20694,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96">
         <v>1.91</v>
@@ -21518,7 +21521,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ100">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR100">
         <v>2.09</v>
@@ -21721,7 +21724,7 @@
         <v>2.33</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ101">
         <v>2.4</v>
@@ -22342,7 +22345,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ104">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR104">
         <v>1.82</v>
@@ -22545,10 +22548,10 @@
         <v>0.5</v>
       </c>
       <c r="AP105">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ105">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -23448,6 +23451,624 @@
       </c>
       <c r="BP109">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7483786</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45717.375</v>
+      </c>
+      <c r="F110">
+        <v>23</v>
+      </c>
+      <c r="G110" t="s">
+        <v>79</v>
+      </c>
+      <c r="H110" t="s">
+        <v>76</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>81</v>
+      </c>
+      <c r="P110" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110">
+        <v>0</v>
+      </c>
+      <c r="V110">
+        <v>0</v>
+      </c>
+      <c r="W110">
+        <v>0</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+      <c r="Z110">
+        <v>2.3</v>
+      </c>
+      <c r="AA110">
+        <v>3.19</v>
+      </c>
+      <c r="AB110">
+        <v>3.11</v>
+      </c>
+      <c r="AC110">
+        <v>0</v>
+      </c>
+      <c r="AD110">
+        <v>0</v>
+      </c>
+      <c r="AE110">
+        <v>0</v>
+      </c>
+      <c r="AF110">
+        <v>0</v>
+      </c>
+      <c r="AG110">
+        <v>1.99</v>
+      </c>
+      <c r="AH110">
+        <v>1.73</v>
+      </c>
+      <c r="AI110">
+        <v>0</v>
+      </c>
+      <c r="AJ110">
+        <v>0</v>
+      </c>
+      <c r="AK110">
+        <v>0</v>
+      </c>
+      <c r="AL110">
+        <v>0</v>
+      </c>
+      <c r="AM110">
+        <v>0</v>
+      </c>
+      <c r="AN110">
+        <v>1.44</v>
+      </c>
+      <c r="AO110">
+        <v>0.45</v>
+      </c>
+      <c r="AP110">
+        <v>1.3</v>
+      </c>
+      <c r="AQ110">
+        <v>0.67</v>
+      </c>
+      <c r="AR110">
+        <v>1.09</v>
+      </c>
+      <c r="AS110">
+        <v>1.25</v>
+      </c>
+      <c r="AT110">
+        <v>2.34</v>
+      </c>
+      <c r="AU110">
+        <v>-1</v>
+      </c>
+      <c r="AV110">
+        <v>-1</v>
+      </c>
+      <c r="AW110">
+        <v>-1</v>
+      </c>
+      <c r="AX110">
+        <v>-1</v>
+      </c>
+      <c r="AY110">
+        <v>-1</v>
+      </c>
+      <c r="AZ110">
+        <v>-1</v>
+      </c>
+      <c r="BA110">
+        <v>-1</v>
+      </c>
+      <c r="BB110">
+        <v>-1</v>
+      </c>
+      <c r="BC110">
+        <v>-1</v>
+      </c>
+      <c r="BD110">
+        <v>0</v>
+      </c>
+      <c r="BE110">
+        <v>0</v>
+      </c>
+      <c r="BF110">
+        <v>0</v>
+      </c>
+      <c r="BG110">
+        <v>0</v>
+      </c>
+      <c r="BH110">
+        <v>0</v>
+      </c>
+      <c r="BI110">
+        <v>0</v>
+      </c>
+      <c r="BJ110">
+        <v>0</v>
+      </c>
+      <c r="BK110">
+        <v>0</v>
+      </c>
+      <c r="BL110">
+        <v>0</v>
+      </c>
+      <c r="BM110">
+        <v>0</v>
+      </c>
+      <c r="BN110">
+        <v>0</v>
+      </c>
+      <c r="BO110">
+        <v>0</v>
+      </c>
+      <c r="BP110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7483784</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F111">
+        <v>23</v>
+      </c>
+      <c r="G111" t="s">
+        <v>71</v>
+      </c>
+      <c r="H111" t="s">
+        <v>73</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>4</v>
+      </c>
+      <c r="N111">
+        <v>4</v>
+      </c>
+      <c r="O111" t="s">
+        <v>81</v>
+      </c>
+      <c r="P111" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q111">
+        <v>5.2</v>
+      </c>
+      <c r="R111">
+        <v>2.27</v>
+      </c>
+      <c r="S111">
+        <v>2.13</v>
+      </c>
+      <c r="T111">
+        <v>1.35</v>
+      </c>
+      <c r="U111">
+        <v>2.98</v>
+      </c>
+      <c r="V111">
+        <v>2.55</v>
+      </c>
+      <c r="W111">
+        <v>1.45</v>
+      </c>
+      <c r="X111">
+        <v>6.5</v>
+      </c>
+      <c r="Y111">
+        <v>1.09</v>
+      </c>
+      <c r="Z111">
+        <v>5.1</v>
+      </c>
+      <c r="AA111">
+        <v>4.1</v>
+      </c>
+      <c r="AB111">
+        <v>1.59</v>
+      </c>
+      <c r="AC111">
+        <v>1</v>
+      </c>
+      <c r="AD111">
+        <v>9</v>
+      </c>
+      <c r="AE111">
+        <v>1.27</v>
+      </c>
+      <c r="AF111">
+        <v>3.55</v>
+      </c>
+      <c r="AG111">
+        <v>1.82</v>
+      </c>
+      <c r="AH111">
+        <v>1.92</v>
+      </c>
+      <c r="AI111">
+        <v>1.82</v>
+      </c>
+      <c r="AJ111">
+        <v>1.88</v>
+      </c>
+      <c r="AK111">
+        <v>2.14</v>
+      </c>
+      <c r="AL111">
+        <v>1.22</v>
+      </c>
+      <c r="AM111">
+        <v>1.17</v>
+      </c>
+      <c r="AN111">
+        <v>1.36</v>
+      </c>
+      <c r="AO111">
+        <v>1.6</v>
+      </c>
+      <c r="AP111">
+        <v>1.25</v>
+      </c>
+      <c r="AQ111">
+        <v>1.73</v>
+      </c>
+      <c r="AR111">
+        <v>1.34</v>
+      </c>
+      <c r="AS111">
+        <v>1.57</v>
+      </c>
+      <c r="AT111">
+        <v>2.91</v>
+      </c>
+      <c r="AU111">
+        <v>4</v>
+      </c>
+      <c r="AV111">
+        <v>9</v>
+      </c>
+      <c r="AW111">
+        <v>4</v>
+      </c>
+      <c r="AX111">
+        <v>8</v>
+      </c>
+      <c r="AY111">
+        <v>8</v>
+      </c>
+      <c r="AZ111">
+        <v>17</v>
+      </c>
+      <c r="BA111">
+        <v>4</v>
+      </c>
+      <c r="BB111">
+        <v>8</v>
+      </c>
+      <c r="BC111">
+        <v>12</v>
+      </c>
+      <c r="BD111">
+        <v>0</v>
+      </c>
+      <c r="BE111">
+        <v>0</v>
+      </c>
+      <c r="BF111">
+        <v>0</v>
+      </c>
+      <c r="BG111">
+        <v>0</v>
+      </c>
+      <c r="BH111">
+        <v>0</v>
+      </c>
+      <c r="BI111">
+        <v>0</v>
+      </c>
+      <c r="BJ111">
+        <v>0</v>
+      </c>
+      <c r="BK111">
+        <v>0</v>
+      </c>
+      <c r="BL111">
+        <v>0</v>
+      </c>
+      <c r="BM111">
+        <v>0</v>
+      </c>
+      <c r="BN111">
+        <v>0</v>
+      </c>
+      <c r="BO111">
+        <v>0</v>
+      </c>
+      <c r="BP111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7483787</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45717.5625</v>
+      </c>
+      <c r="F112">
+        <v>23</v>
+      </c>
+      <c r="G112" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" t="s">
+        <v>75</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112" t="s">
+        <v>81</v>
+      </c>
+      <c r="P112" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q112">
+        <v>2.37</v>
+      </c>
+      <c r="R112">
+        <v>2.16</v>
+      </c>
+      <c r="S112">
+        <v>4.6</v>
+      </c>
+      <c r="T112">
+        <v>1.4</v>
+      </c>
+      <c r="U112">
+        <v>2.77</v>
+      </c>
+      <c r="V112">
+        <v>2.75</v>
+      </c>
+      <c r="W112">
+        <v>1.4</v>
+      </c>
+      <c r="X112">
+        <v>7.3</v>
+      </c>
+      <c r="Y112">
+        <v>1.07</v>
+      </c>
+      <c r="Z112">
+        <v>1.8</v>
+      </c>
+      <c r="AA112">
+        <v>3.53</v>
+      </c>
+      <c r="AB112">
+        <v>4.3</v>
+      </c>
+      <c r="AC112">
+        <v>1.01</v>
+      </c>
+      <c r="AD112">
+        <v>8.4</v>
+      </c>
+      <c r="AE112">
+        <v>1.31</v>
+      </c>
+      <c r="AF112">
+        <v>3.3</v>
+      </c>
+      <c r="AG112">
+        <v>1.98</v>
+      </c>
+      <c r="AH112">
+        <v>1.77</v>
+      </c>
+      <c r="AI112">
+        <v>1.82</v>
+      </c>
+      <c r="AJ112">
+        <v>1.88</v>
+      </c>
+      <c r="AK112">
+        <v>1.22</v>
+      </c>
+      <c r="AL112">
+        <v>1.26</v>
+      </c>
+      <c r="AM112">
+        <v>1.88</v>
+      </c>
+      <c r="AN112">
+        <v>1.5</v>
+      </c>
+      <c r="AO112">
+        <v>0.18</v>
+      </c>
+      <c r="AP112">
+        <v>1.45</v>
+      </c>
+      <c r="AQ112">
+        <v>0.25</v>
+      </c>
+      <c r="AR112">
+        <v>1.41</v>
+      </c>
+      <c r="AS112">
+        <v>1.32</v>
+      </c>
+      <c r="AT112">
+        <v>2.73</v>
+      </c>
+      <c r="AU112">
+        <v>6</v>
+      </c>
+      <c r="AV112">
+        <v>3</v>
+      </c>
+      <c r="AW112">
+        <v>7</v>
+      </c>
+      <c r="AX112">
+        <v>1</v>
+      </c>
+      <c r="AY112">
+        <v>13</v>
+      </c>
+      <c r="AZ112">
+        <v>4</v>
+      </c>
+      <c r="BA112">
+        <v>9</v>
+      </c>
+      <c r="BB112">
+        <v>2</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>0</v>
+      </c>
+      <c r="BE112">
+        <v>0</v>
+      </c>
+      <c r="BF112">
+        <v>0</v>
+      </c>
+      <c r="BG112">
+        <v>0</v>
+      </c>
+      <c r="BH112">
+        <v>0</v>
+      </c>
+      <c r="BI112">
+        <v>0</v>
+      </c>
+      <c r="BJ112">
+        <v>0</v>
+      </c>
+      <c r="BK112">
+        <v>0</v>
+      </c>
+      <c r="BL112">
+        <v>0</v>
+      </c>
+      <c r="BM112">
+        <v>0</v>
+      </c>
+      <c r="BN112">
+        <v>0</v>
+      </c>
+      <c r="BO112">
+        <v>0</v>
+      </c>
+      <c r="BP112">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="209">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,12 @@
     <t>['7', '11', '16', '21', '58', '71', '75', '78', '90+2']</t>
   </si>
   <si>
+    <t>['40', '62']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -607,9 +613,6 @@
     <t>['71', '83']</t>
   </si>
   <si>
-    <t>['17']</t>
-  </si>
-  <si>
     <t>['44']</t>
   </si>
   <si>
@@ -635,6 +638,9 @@
   </si>
   <si>
     <t>['20', '55', '64', '74']</t>
+  </si>
+  <si>
+    <t>['33']</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1330,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1742,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0.25</v>
@@ -1870,7 +1876,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2157,7 +2163,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ6">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2488,7 +2494,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3312,7 +3318,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3596,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR13">
         <v>1.72</v>
@@ -3805,7 +3811,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ14">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR14">
         <v>1.88</v>
@@ -4008,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15">
         <v>0.25</v>
@@ -4136,7 +4142,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4548,7 +4554,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5166,7 +5172,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5372,7 +5378,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5450,10 +5456,10 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5784,7 +5790,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5990,7 +5996,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6068,10 +6074,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ25">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR25">
         <v>1.83</v>
@@ -6274,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
         <v>0.64</v>
@@ -6402,7 +6408,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6814,7 +6820,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7226,7 +7232,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7513,7 +7519,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ32">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -7925,7 +7931,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ34">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -8128,7 +8134,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8334,7 +8340,7 @@
         <v>1.2</v>
       </c>
       <c r="AP36">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8462,7 +8468,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8874,7 +8880,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9492,7 +9498,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9570,10 +9576,10 @@
         <v>1.25</v>
       </c>
       <c r="AP42">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ42">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR42">
         <v>2.18</v>
@@ -9904,7 +9910,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10110,7 +10116,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10191,7 +10197,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ45">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR45">
         <v>1.07</v>
@@ -10522,7 +10528,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10728,7 +10734,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10809,7 +10815,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ48">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR48">
         <v>1.28</v>
@@ -11140,7 +11146,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11552,7 +11558,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11630,7 +11636,7 @@
         <v>0.2</v>
       </c>
       <c r="AP52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ52">
         <v>0.67</v>
@@ -11839,7 +11845,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ53">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR53">
         <v>1.07</v>
@@ -11964,7 +11970,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12045,7 +12051,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ54">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12170,7 +12176,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12248,7 +12254,7 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ55">
         <v>1.91</v>
@@ -12376,7 +12382,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12582,7 +12588,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12788,7 +12794,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12994,7 +13000,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13200,7 +13206,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13406,7 +13412,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13612,7 +13618,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13818,7 +13824,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13896,7 +13902,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ63">
         <v>1.73</v>
@@ -14024,7 +14030,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14105,7 +14111,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ64">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR64">
         <v>1.37</v>
@@ -14230,7 +14236,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14311,7 +14317,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ65">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14514,7 +14520,7 @@
         <v>0.67</v>
       </c>
       <c r="AP66">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ66">
         <v>0.67</v>
@@ -15054,7 +15060,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15260,7 +15266,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15466,7 +15472,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15959,7 +15965,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ73">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16162,7 +16168,7 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ74">
         <v>1.73</v>
@@ -16290,7 +16296,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16496,7 +16502,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16577,7 +16583,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ76">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR76">
         <v>1.07</v>
@@ -16908,7 +16914,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17114,7 +17120,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17192,7 +17198,7 @@
         <v>2.43</v>
       </c>
       <c r="AP79">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ79">
         <v>2.4</v>
@@ -17526,7 +17532,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17607,7 +17613,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ81">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -17732,7 +17738,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18225,7 +18231,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ84">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR84">
         <v>1.41</v>
@@ -18428,7 +18434,7 @@
         <v>0.86</v>
       </c>
       <c r="AP85">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ85">
         <v>0.64</v>
@@ -18762,7 +18768,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18968,7 +18974,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19174,7 +19180,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19586,7 +19592,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19664,7 +19670,7 @@
         <v>1.88</v>
       </c>
       <c r="AP91">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ91">
         <v>1.91</v>
@@ -19792,7 +19798,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19873,7 +19879,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ92">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20282,7 +20288,7 @@
         <v>1.22</v>
       </c>
       <c r="AP94">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20488,7 +20494,7 @@
         <v>0.11</v>
       </c>
       <c r="AP95">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ95">
         <v>0.25</v>
@@ -20616,7 +20622,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20822,7 +20828,7 @@
         <v>142</v>
       </c>
       <c r="P97" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -21028,7 +21034,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21234,7 +21240,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21440,7 +21446,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21646,7 +21652,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21852,7 +21858,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -21933,7 +21939,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ102">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR102">
         <v>1.84</v>
@@ -22136,10 +22142,10 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ103">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22342,7 +22348,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ104">
         <v>0.25</v>
@@ -22676,7 +22682,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22882,7 +22888,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23294,7 +23300,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23706,7 +23712,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24069,6 +24075,418 @@
       </c>
       <c r="BP112">
         <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7483785</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F113">
+        <v>23</v>
+      </c>
+      <c r="G113" t="s">
+        <v>70</v>
+      </c>
+      <c r="H113" t="s">
+        <v>74</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113" t="s">
+        <v>153</v>
+      </c>
+      <c r="P113" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q113">
+        <v>2.6</v>
+      </c>
+      <c r="R113">
+        <v>2.2</v>
+      </c>
+      <c r="S113">
+        <v>3.75</v>
+      </c>
+      <c r="T113">
+        <v>1.36</v>
+      </c>
+      <c r="U113">
+        <v>3</v>
+      </c>
+      <c r="V113">
+        <v>2.75</v>
+      </c>
+      <c r="W113">
+        <v>1.4</v>
+      </c>
+      <c r="X113">
+        <v>6.5</v>
+      </c>
+      <c r="Y113">
+        <v>1.1</v>
+      </c>
+      <c r="Z113">
+        <v>1.99</v>
+      </c>
+      <c r="AA113">
+        <v>3.45</v>
+      </c>
+      <c r="AB113">
+        <v>3.59</v>
+      </c>
+      <c r="AC113">
+        <v>1.05</v>
+      </c>
+      <c r="AD113">
+        <v>8.5</v>
+      </c>
+      <c r="AE113">
+        <v>1.28</v>
+      </c>
+      <c r="AF113">
+        <v>3.55</v>
+      </c>
+      <c r="AG113">
+        <v>1.83</v>
+      </c>
+      <c r="AH113">
+        <v>1.91</v>
+      </c>
+      <c r="AI113">
+        <v>1.73</v>
+      </c>
+      <c r="AJ113">
+        <v>2</v>
+      </c>
+      <c r="AK113">
+        <v>1.28</v>
+      </c>
+      <c r="AL113">
+        <v>1.3</v>
+      </c>
+      <c r="AM113">
+        <v>1.75</v>
+      </c>
+      <c r="AN113">
+        <v>2.18</v>
+      </c>
+      <c r="AO113">
+        <v>1.3</v>
+      </c>
+      <c r="AP113">
+        <v>2.25</v>
+      </c>
+      <c r="AQ113">
+        <v>1.18</v>
+      </c>
+      <c r="AR113">
+        <v>1.82</v>
+      </c>
+      <c r="AS113">
+        <v>1.66</v>
+      </c>
+      <c r="AT113">
+        <v>3.48</v>
+      </c>
+      <c r="AU113">
+        <v>7</v>
+      </c>
+      <c r="AV113">
+        <v>3</v>
+      </c>
+      <c r="AW113">
+        <v>4</v>
+      </c>
+      <c r="AX113">
+        <v>3</v>
+      </c>
+      <c r="AY113">
+        <v>11</v>
+      </c>
+      <c r="AZ113">
+        <v>6</v>
+      </c>
+      <c r="BA113">
+        <v>8</v>
+      </c>
+      <c r="BB113">
+        <v>9</v>
+      </c>
+      <c r="BC113">
+        <v>17</v>
+      </c>
+      <c r="BD113">
+        <v>1.72</v>
+      </c>
+      <c r="BE113">
+        <v>7.4</v>
+      </c>
+      <c r="BF113">
+        <v>2.49</v>
+      </c>
+      <c r="BG113">
+        <v>1.23</v>
+      </c>
+      <c r="BH113">
+        <v>3.42</v>
+      </c>
+      <c r="BI113">
+        <v>1.45</v>
+      </c>
+      <c r="BJ113">
+        <v>2.41</v>
+      </c>
+      <c r="BK113">
+        <v>1.81</v>
+      </c>
+      <c r="BL113">
+        <v>1.85</v>
+      </c>
+      <c r="BM113">
+        <v>2.3</v>
+      </c>
+      <c r="BN113">
+        <v>1.49</v>
+      </c>
+      <c r="BO113">
+        <v>3.08</v>
+      </c>
+      <c r="BP113">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7483783</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45718.5625</v>
+      </c>
+      <c r="F114">
+        <v>23</v>
+      </c>
+      <c r="G114" t="s">
+        <v>72</v>
+      </c>
+      <c r="H114" t="s">
+        <v>78</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>154</v>
+      </c>
+      <c r="P114" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q114">
+        <v>3.8</v>
+      </c>
+      <c r="R114">
+        <v>2.06</v>
+      </c>
+      <c r="S114">
+        <v>2.8</v>
+      </c>
+      <c r="T114">
+        <v>1.46</v>
+      </c>
+      <c r="U114">
+        <v>2.55</v>
+      </c>
+      <c r="V114">
+        <v>3</v>
+      </c>
+      <c r="W114">
+        <v>1.36</v>
+      </c>
+      <c r="X114">
+        <v>8</v>
+      </c>
+      <c r="Y114">
+        <v>1.08</v>
+      </c>
+      <c r="Z114">
+        <v>3.23</v>
+      </c>
+      <c r="AA114">
+        <v>3.28</v>
+      </c>
+      <c r="AB114">
+        <v>2.2</v>
+      </c>
+      <c r="AC114">
+        <v>1</v>
+      </c>
+      <c r="AD114">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE114">
+        <v>1.34</v>
+      </c>
+      <c r="AF114">
+        <v>3.05</v>
+      </c>
+      <c r="AG114">
+        <v>1.95</v>
+      </c>
+      <c r="AH114">
+        <v>1.79</v>
+      </c>
+      <c r="AI114">
+        <v>1.81</v>
+      </c>
+      <c r="AJ114">
+        <v>1.89</v>
+      </c>
+      <c r="AK114">
+        <v>1.6</v>
+      </c>
+      <c r="AL114">
+        <v>1.3</v>
+      </c>
+      <c r="AM114">
+        <v>1.32</v>
+      </c>
+      <c r="AN114">
+        <v>1.36</v>
+      </c>
+      <c r="AO114">
+        <v>1.64</v>
+      </c>
+      <c r="AP114">
+        <v>1.33</v>
+      </c>
+      <c r="AQ114">
+        <v>1.58</v>
+      </c>
+      <c r="AR114">
+        <v>1.48</v>
+      </c>
+      <c r="AS114">
+        <v>1.55</v>
+      </c>
+      <c r="AT114">
+        <v>3.03</v>
+      </c>
+      <c r="AU114">
+        <v>7</v>
+      </c>
+      <c r="AV114">
+        <v>3</v>
+      </c>
+      <c r="AW114">
+        <v>9</v>
+      </c>
+      <c r="AX114">
+        <v>3</v>
+      </c>
+      <c r="AY114">
+        <v>16</v>
+      </c>
+      <c r="AZ114">
+        <v>6</v>
+      </c>
+      <c r="BA114">
+        <v>5</v>
+      </c>
+      <c r="BB114">
+        <v>1</v>
+      </c>
+      <c r="BC114">
+        <v>6</v>
+      </c>
+      <c r="BD114">
+        <v>2.21</v>
+      </c>
+      <c r="BE114">
+        <v>6.25</v>
+      </c>
+      <c r="BF114">
+        <v>1.98</v>
+      </c>
+      <c r="BG114">
+        <v>1.26</v>
+      </c>
+      <c r="BH114">
+        <v>3.22</v>
+      </c>
+      <c r="BI114">
+        <v>1.49</v>
+      </c>
+      <c r="BJ114">
+        <v>2.3</v>
+      </c>
+      <c r="BK114">
+        <v>1.86</v>
+      </c>
+      <c r="BL114">
+        <v>1.8</v>
+      </c>
+      <c r="BM114">
+        <v>2.41</v>
+      </c>
+      <c r="BN114">
+        <v>1.45</v>
+      </c>
+      <c r="BO114">
+        <v>3.28</v>
+      </c>
+      <c r="BP114">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="212">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -481,6 +481,12 @@
     <t>['17']</t>
   </si>
   <si>
+    <t>['45+5']</t>
+  </si>
+  <si>
+    <t>['10', '70', '79']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -641,6 +647,9 @@
   </si>
   <si>
     <t>['33']</t>
+  </si>
+  <si>
+    <t>['60']</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1545,7 +1554,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ3">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1876,7 +1885,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2494,7 +2503,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2572,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2781,7 +2790,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ9">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3318,7 +3327,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3396,10 +3405,10 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ12">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4142,7 +4151,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4426,10 +4435,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ17">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR17">
         <v>1.21</v>
@@ -4554,7 +4563,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5047,7 +5056,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ20">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5172,7 +5181,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5250,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21">
         <v>0.67</v>
@@ -5378,7 +5387,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5790,7 +5799,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5996,7 +6005,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6408,7 +6417,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6486,10 +6495,10 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ27">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR27">
         <v>0.98</v>
@@ -6695,7 +6704,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ28">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -6820,7 +6829,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7232,7 +7241,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -8468,7 +8477,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8549,7 +8558,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -8880,7 +8889,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9167,7 +9176,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ40">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9498,7 +9507,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9910,7 +9919,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10116,7 +10125,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10194,7 +10203,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ45">
         <v>1.18</v>
@@ -10528,7 +10537,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10606,10 +10615,10 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR47">
         <v>1.05</v>
@@ -10734,7 +10743,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11146,7 +11155,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11224,7 +11233,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ50">
         <v>1.73</v>
@@ -11558,7 +11567,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11842,7 +11851,7 @@
         <v>1.2</v>
       </c>
       <c r="AP53">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ53">
         <v>1.58</v>
@@ -11970,7 +11979,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12176,7 +12185,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12257,7 +12266,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ55">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR55">
         <v>1.92</v>
@@ -12382,7 +12391,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12460,7 +12469,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ56">
         <v>0.64</v>
@@ -12588,7 +12597,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12794,7 +12803,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12875,7 +12884,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ58">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR58">
         <v>1.46</v>
@@ -13000,7 +13009,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13206,7 +13215,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13412,7 +13421,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13490,7 +13499,7 @@
         <v>0.6</v>
       </c>
       <c r="AP61">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ61">
         <v>0.64</v>
@@ -13618,7 +13627,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13696,7 +13705,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62">
         <v>0.25</v>
@@ -13824,7 +13833,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14030,7 +14039,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14236,7 +14245,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14726,7 +14735,7 @@
         <v>1.29</v>
       </c>
       <c r="AP67">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15060,7 +15069,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15266,7 +15275,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15347,7 +15356,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ70">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR70">
         <v>1.99</v>
@@ -15472,7 +15481,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15553,7 +15562,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ71">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -16296,7 +16305,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16502,7 +16511,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16580,7 +16589,7 @@
         <v>1.14</v>
       </c>
       <c r="AP76">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ76">
         <v>1.18</v>
@@ -16789,7 +16798,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ77">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR77">
         <v>2</v>
@@ -16914,7 +16923,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -16992,7 +17001,7 @@
         <v>0.14</v>
       </c>
       <c r="AP78">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ78">
         <v>0.25</v>
@@ -17120,7 +17129,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17201,7 +17210,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ79">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR79">
         <v>1.42</v>
@@ -17404,7 +17413,7 @@
         <v>1.71</v>
       </c>
       <c r="AP80">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ80">
         <v>1.73</v>
@@ -17532,7 +17541,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17610,7 +17619,7 @@
         <v>1.13</v>
       </c>
       <c r="AP81">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ81">
         <v>1.58</v>
@@ -17738,7 +17747,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18022,7 +18031,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18768,7 +18777,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18974,7 +18983,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19055,7 +19064,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ88">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR88">
         <v>1.51</v>
@@ -19180,7 +19189,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19592,7 +19601,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19673,7 +19682,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ91">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR91">
         <v>1.34</v>
@@ -19798,7 +19807,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20622,7 +20631,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20703,7 +20712,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ96">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -21034,7 +21043,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21240,7 +21249,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21318,7 +21327,7 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -21446,7 +21455,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21652,7 +21661,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21733,7 +21742,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ101">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AR101">
         <v>1.43</v>
@@ -21858,7 +21867,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22682,7 +22691,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22888,7 +22897,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -22969,7 +22978,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ107">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23300,7 +23309,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23584,7 +23593,7 @@
         <v>0.45</v>
       </c>
       <c r="AP110">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ110">
         <v>0.67</v>
@@ -23712,7 +23721,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24330,7 +24339,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24487,6 +24496,418 @@
       </c>
       <c r="BP114">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7483777</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45721.45833333334</v>
+      </c>
+      <c r="F115">
+        <v>21</v>
+      </c>
+      <c r="G115" t="s">
+        <v>79</v>
+      </c>
+      <c r="H115" t="s">
+        <v>77</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>2</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>2</v>
+      </c>
+      <c r="O115" t="s">
+        <v>155</v>
+      </c>
+      <c r="P115" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q115">
+        <v>0</v>
+      </c>
+      <c r="R115">
+        <v>0</v>
+      </c>
+      <c r="S115">
+        <v>0</v>
+      </c>
+      <c r="T115">
+        <v>0</v>
+      </c>
+      <c r="U115">
+        <v>0</v>
+      </c>
+      <c r="V115">
+        <v>0</v>
+      </c>
+      <c r="W115">
+        <v>0</v>
+      </c>
+      <c r="X115">
+        <v>0</v>
+      </c>
+      <c r="Y115">
+        <v>0</v>
+      </c>
+      <c r="Z115">
+        <v>3.79</v>
+      </c>
+      <c r="AA115">
+        <v>3.06</v>
+      </c>
+      <c r="AB115">
+        <v>2.08</v>
+      </c>
+      <c r="AC115">
+        <v>0</v>
+      </c>
+      <c r="AD115">
+        <v>0</v>
+      </c>
+      <c r="AE115">
+        <v>0</v>
+      </c>
+      <c r="AF115">
+        <v>0</v>
+      </c>
+      <c r="AG115">
+        <v>2.3</v>
+      </c>
+      <c r="AH115">
+        <v>1.5</v>
+      </c>
+      <c r="AI115">
+        <v>0</v>
+      </c>
+      <c r="AJ115">
+        <v>0</v>
+      </c>
+      <c r="AK115">
+        <v>0</v>
+      </c>
+      <c r="AL115">
+        <v>0</v>
+      </c>
+      <c r="AM115">
+        <v>0</v>
+      </c>
+      <c r="AN115">
+        <v>1.3</v>
+      </c>
+      <c r="AO115">
+        <v>1.91</v>
+      </c>
+      <c r="AP115">
+        <v>1.27</v>
+      </c>
+      <c r="AQ115">
+        <v>1.83</v>
+      </c>
+      <c r="AR115">
+        <v>1.09</v>
+      </c>
+      <c r="AS115">
+        <v>1.35</v>
+      </c>
+      <c r="AT115">
+        <v>2.44</v>
+      </c>
+      <c r="AU115">
+        <v>-1</v>
+      </c>
+      <c r="AV115">
+        <v>-1</v>
+      </c>
+      <c r="AW115">
+        <v>-1</v>
+      </c>
+      <c r="AX115">
+        <v>-1</v>
+      </c>
+      <c r="AY115">
+        <v>-1</v>
+      </c>
+      <c r="AZ115">
+        <v>-1</v>
+      </c>
+      <c r="BA115">
+        <v>-1</v>
+      </c>
+      <c r="BB115">
+        <v>-1</v>
+      </c>
+      <c r="BC115">
+        <v>-1</v>
+      </c>
+      <c r="BD115">
+        <v>0</v>
+      </c>
+      <c r="BE115">
+        <v>0</v>
+      </c>
+      <c r="BF115">
+        <v>0</v>
+      </c>
+      <c r="BG115">
+        <v>0</v>
+      </c>
+      <c r="BH115">
+        <v>0</v>
+      </c>
+      <c r="BI115">
+        <v>0</v>
+      </c>
+      <c r="BJ115">
+        <v>0</v>
+      </c>
+      <c r="BK115">
+        <v>0</v>
+      </c>
+      <c r="BL115">
+        <v>0</v>
+      </c>
+      <c r="BM115">
+        <v>0</v>
+      </c>
+      <c r="BN115">
+        <v>0</v>
+      </c>
+      <c r="BO115">
+        <v>0</v>
+      </c>
+      <c r="BP115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7483780</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45721.5625</v>
+      </c>
+      <c r="F116">
+        <v>22</v>
+      </c>
+      <c r="G116" t="s">
+        <v>76</v>
+      </c>
+      <c r="H116" t="s">
+        <v>70</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>3</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>4</v>
+      </c>
+      <c r="O116" t="s">
+        <v>156</v>
+      </c>
+      <c r="P116" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q116">
+        <v>5.5</v>
+      </c>
+      <c r="R116">
+        <v>2.3</v>
+      </c>
+      <c r="S116">
+        <v>2</v>
+      </c>
+      <c r="T116">
+        <v>1.33</v>
+      </c>
+      <c r="U116">
+        <v>3.25</v>
+      </c>
+      <c r="V116">
+        <v>2.5</v>
+      </c>
+      <c r="W116">
+        <v>1.5</v>
+      </c>
+      <c r="X116">
+        <v>6</v>
+      </c>
+      <c r="Y116">
+        <v>1.11</v>
+      </c>
+      <c r="Z116">
+        <v>7.9</v>
+      </c>
+      <c r="AA116">
+        <v>4.5</v>
+      </c>
+      <c r="AB116">
+        <v>1.39</v>
+      </c>
+      <c r="AC116">
+        <v>1.03</v>
+      </c>
+      <c r="AD116">
+        <v>10</v>
+      </c>
+      <c r="AE116">
+        <v>1.23</v>
+      </c>
+      <c r="AF116">
+        <v>3.9</v>
+      </c>
+      <c r="AG116">
+        <v>1.77</v>
+      </c>
+      <c r="AH116">
+        <v>1.98</v>
+      </c>
+      <c r="AI116">
+        <v>1.83</v>
+      </c>
+      <c r="AJ116">
+        <v>1.83</v>
+      </c>
+      <c r="AK116">
+        <v>2.6</v>
+      </c>
+      <c r="AL116">
+        <v>1.17</v>
+      </c>
+      <c r="AM116">
+        <v>1.11</v>
+      </c>
+      <c r="AN116">
+        <v>0.5</v>
+      </c>
+      <c r="AO116">
+        <v>2.4</v>
+      </c>
+      <c r="AP116">
+        <v>0.73</v>
+      </c>
+      <c r="AQ116">
+        <v>2.18</v>
+      </c>
+      <c r="AR116">
+        <v>1.46</v>
+      </c>
+      <c r="AS116">
+        <v>1.77</v>
+      </c>
+      <c r="AT116">
+        <v>3.23</v>
+      </c>
+      <c r="AU116">
+        <v>5</v>
+      </c>
+      <c r="AV116">
+        <v>7</v>
+      </c>
+      <c r="AW116">
+        <v>5</v>
+      </c>
+      <c r="AX116">
+        <v>11</v>
+      </c>
+      <c r="AY116">
+        <v>10</v>
+      </c>
+      <c r="AZ116">
+        <v>18</v>
+      </c>
+      <c r="BA116">
+        <v>3</v>
+      </c>
+      <c r="BB116">
+        <v>15</v>
+      </c>
+      <c r="BC116">
+        <v>18</v>
+      </c>
+      <c r="BD116">
+        <v>4.05</v>
+      </c>
+      <c r="BE116">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF116">
+        <v>1.31</v>
+      </c>
+      <c r="BG116">
+        <v>1.23</v>
+      </c>
+      <c r="BH116">
+        <v>3.42</v>
+      </c>
+      <c r="BI116">
+        <v>1.44</v>
+      </c>
+      <c r="BJ116">
+        <v>2.43</v>
+      </c>
+      <c r="BK116">
+        <v>1.78</v>
+      </c>
+      <c r="BL116">
+        <v>1.88</v>
+      </c>
+      <c r="BM116">
+        <v>2.26</v>
+      </c>
+      <c r="BN116">
+        <v>1.51</v>
+      </c>
+      <c r="BO116">
+        <v>3.04</v>
+      </c>
+      <c r="BP116">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -24638,31 +24638,31 @@
         <v>2.44</v>
       </c>
       <c r="AU115">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV115">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW115">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX115">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AY115">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AZ115">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BA115">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB115">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC115">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD115">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -487,6 +487,15 @@
     <t>['10', '70', '79']</t>
   </si>
   <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['23', '26']</t>
+  </si>
+  <si>
+    <t>['36', '77']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -650,6 +659,9 @@
   </si>
   <si>
     <t>['60']</t>
+  </si>
+  <si>
+    <t>['21', '45+1', '90']</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1554,7 +1566,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ3">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1757,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ4">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1885,7 +1897,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2378,7 +2390,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ7">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2503,7 +2515,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2581,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2993,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3327,7 +3339,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3408,7 +3420,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ12">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3611,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ13">
         <v>1.18</v>
@@ -4026,7 +4038,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ15">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR15">
         <v>1.3</v>
@@ -4151,7 +4163,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4435,7 +4447,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ17">
         <v>2.18</v>
@@ -4563,7 +4575,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4644,7 +4656,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR18">
         <v>2.23</v>
@@ -5053,10 +5065,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ20">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5181,7 +5193,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5387,7 +5399,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5465,7 +5477,7 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22">
         <v>1.58</v>
@@ -5674,7 +5686,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ23">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR23">
         <v>0.7</v>
@@ -5799,7 +5811,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6005,7 +6017,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6289,10 +6301,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ26">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR26">
         <v>1.62</v>
@@ -6417,7 +6429,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6495,10 +6507,10 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ27">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR27">
         <v>0.98</v>
@@ -6829,7 +6841,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7113,10 +7125,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ30">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR30">
         <v>1.03</v>
@@ -7241,7 +7253,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -8349,7 +8361,7 @@
         <v>1.2</v>
       </c>
       <c r="AP36">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8477,7 +8489,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8761,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ38">
         <v>0.67</v>
@@ -8889,7 +8901,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -8970,7 +8982,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR39">
         <v>2.18</v>
@@ -9176,7 +9188,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ40">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9507,7 +9519,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9919,7 +9931,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10125,7 +10137,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10203,7 +10215,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ45">
         <v>1.18</v>
@@ -10537,7 +10549,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10743,7 +10755,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10821,7 +10833,7 @@
         <v>1.25</v>
       </c>
       <c r="AP48">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ48">
         <v>1.18</v>
@@ -11030,7 +11042,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ49">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR49">
         <v>1.31</v>
@@ -11155,7 +11167,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11233,7 +11245,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ50">
         <v>1.73</v>
@@ -11442,7 +11454,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR51">
         <v>1.32</v>
@@ -11567,7 +11579,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11645,7 +11657,7 @@
         <v>0.2</v>
       </c>
       <c r="AP52">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ52">
         <v>0.67</v>
@@ -11979,7 +11991,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12185,7 +12197,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12266,7 +12278,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ55">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR55">
         <v>1.92</v>
@@ -12391,7 +12403,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12472,7 +12484,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ56">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12597,7 +12609,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12803,7 +12815,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13009,7 +13021,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13215,7 +13227,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13293,7 +13305,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60">
         <v>1.73</v>
@@ -13421,7 +13433,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13499,10 +13511,10 @@
         <v>0.6</v>
       </c>
       <c r="AP61">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ61">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR61">
         <v>1.2</v>
@@ -13627,7 +13639,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13708,7 +13720,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ62">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -13833,7 +13845,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13911,7 +13923,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ63">
         <v>1.73</v>
@@ -14039,7 +14051,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14245,7 +14257,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14735,7 +14747,7 @@
         <v>1.29</v>
       </c>
       <c r="AP67">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -14944,7 +14956,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ68">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR68">
         <v>1.5</v>
@@ -15069,7 +15081,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15147,7 +15159,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ69">
         <v>1</v>
@@ -15275,7 +15287,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15481,7 +15493,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15562,7 +15574,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ71">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -16305,7 +16317,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16511,7 +16523,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16798,7 +16810,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ77">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR77">
         <v>2</v>
@@ -16923,7 +16935,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17001,10 +17013,10 @@
         <v>0.14</v>
       </c>
       <c r="AP78">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ78">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR78">
         <v>1.13</v>
@@ -17129,7 +17141,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17207,7 +17219,7 @@
         <v>2.43</v>
       </c>
       <c r="AP79">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ79">
         <v>2.18</v>
@@ -17541,7 +17553,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17619,7 +17631,7 @@
         <v>1.13</v>
       </c>
       <c r="AP81">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ81">
         <v>1.58</v>
@@ -17747,7 +17759,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18446,7 +18458,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ85">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR85">
         <v>1.72</v>
@@ -18649,10 +18661,10 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ86">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR86">
         <v>1.46</v>
@@ -18777,7 +18789,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18983,7 +18995,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19061,7 +19073,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ88">
         <v>2.18</v>
@@ -19189,7 +19201,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19476,7 +19488,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ90">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR90">
         <v>1.64</v>
@@ -19601,7 +19613,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19679,10 +19691,10 @@
         <v>1.88</v>
       </c>
       <c r="AP91">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ91">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR91">
         <v>1.34</v>
@@ -19807,7 +19819,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20503,10 +20515,10 @@
         <v>0.11</v>
       </c>
       <c r="AP95">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ95">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -20631,7 +20643,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20712,7 +20724,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ96">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -20915,7 +20927,7 @@
         <v>1.1</v>
       </c>
       <c r="AP97">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21043,7 +21055,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21124,7 +21136,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ98">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21249,7 +21261,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21327,7 +21339,7 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -21455,7 +21467,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21661,7 +21673,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21867,7 +21879,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22151,7 +22163,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ103">
         <v>1.18</v>
@@ -22360,7 +22372,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ104">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR104">
         <v>1.82</v>
@@ -22691,7 +22703,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22897,7 +22909,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -22975,10 +22987,10 @@
         <v>2.1</v>
       </c>
       <c r="AP107">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ107">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23309,7 +23321,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23390,7 +23402,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ109">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR109">
         <v>2.1</v>
@@ -23721,7 +23733,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24008,7 +24020,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ112">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR112">
         <v>1.41</v>
@@ -24339,7 +24351,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24417,7 +24429,7 @@
         <v>1.64</v>
       </c>
       <c r="AP114">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ114">
         <v>1.58</v>
@@ -24545,7 +24557,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24626,7 +24638,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ115">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR115">
         <v>1.09</v>
@@ -24751,7 +24763,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24829,7 +24841,7 @@
         <v>2.4</v>
       </c>
       <c r="AP116">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ116">
         <v>2.18</v>
@@ -24908,6 +24920,624 @@
       </c>
       <c r="BP116">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7483788</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45724.375</v>
+      </c>
+      <c r="F117">
+        <v>24</v>
+      </c>
+      <c r="G117" t="s">
+        <v>78</v>
+      </c>
+      <c r="H117" t="s">
+        <v>75</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>2</v>
+      </c>
+      <c r="O117" t="s">
+        <v>157</v>
+      </c>
+      <c r="P117" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q117">
+        <v>2.12</v>
+      </c>
+      <c r="R117">
+        <v>2.12</v>
+      </c>
+      <c r="S117">
+        <v>5.75</v>
+      </c>
+      <c r="T117">
+        <v>1.41</v>
+      </c>
+      <c r="U117">
+        <v>2.69</v>
+      </c>
+      <c r="V117">
+        <v>2.93</v>
+      </c>
+      <c r="W117">
+        <v>1.35</v>
+      </c>
+      <c r="X117">
+        <v>7.5</v>
+      </c>
+      <c r="Y117">
+        <v>1.07</v>
+      </c>
+      <c r="Z117">
+        <v>1.74</v>
+      </c>
+      <c r="AA117">
+        <v>3.56</v>
+      </c>
+      <c r="AB117">
+        <v>4.6</v>
+      </c>
+      <c r="AC117">
+        <v>1.02</v>
+      </c>
+      <c r="AD117">
+        <v>8.1</v>
+      </c>
+      <c r="AE117">
+        <v>1.3</v>
+      </c>
+      <c r="AF117">
+        <v>2.97</v>
+      </c>
+      <c r="AG117">
+        <v>1.98</v>
+      </c>
+      <c r="AH117">
+        <v>1.77</v>
+      </c>
+      <c r="AI117">
+        <v>1.98</v>
+      </c>
+      <c r="AJ117">
+        <v>1.7</v>
+      </c>
+      <c r="AK117">
+        <v>1.11</v>
+      </c>
+      <c r="AL117">
+        <v>1.22</v>
+      </c>
+      <c r="AM117">
+        <v>2.2</v>
+      </c>
+      <c r="AN117">
+        <v>2.18</v>
+      </c>
+      <c r="AO117">
+        <v>0.25</v>
+      </c>
+      <c r="AP117">
+        <v>2.08</v>
+      </c>
+      <c r="AQ117">
+        <v>0.31</v>
+      </c>
+      <c r="AR117">
+        <v>1.5</v>
+      </c>
+      <c r="AS117">
+        <v>1.29</v>
+      </c>
+      <c r="AT117">
+        <v>2.79</v>
+      </c>
+      <c r="AU117">
+        <v>6</v>
+      </c>
+      <c r="AV117">
+        <v>3</v>
+      </c>
+      <c r="AW117">
+        <v>10</v>
+      </c>
+      <c r="AX117">
+        <v>1</v>
+      </c>
+      <c r="AY117">
+        <v>16</v>
+      </c>
+      <c r="AZ117">
+        <v>4</v>
+      </c>
+      <c r="BA117">
+        <v>5</v>
+      </c>
+      <c r="BB117">
+        <v>1</v>
+      </c>
+      <c r="BC117">
+        <v>6</v>
+      </c>
+      <c r="BD117">
+        <v>0</v>
+      </c>
+      <c r="BE117">
+        <v>0</v>
+      </c>
+      <c r="BF117">
+        <v>0</v>
+      </c>
+      <c r="BG117">
+        <v>0</v>
+      </c>
+      <c r="BH117">
+        <v>0</v>
+      </c>
+      <c r="BI117">
+        <v>0</v>
+      </c>
+      <c r="BJ117">
+        <v>0</v>
+      </c>
+      <c r="BK117">
+        <v>0</v>
+      </c>
+      <c r="BL117">
+        <v>0</v>
+      </c>
+      <c r="BM117">
+        <v>0</v>
+      </c>
+      <c r="BN117">
+        <v>0</v>
+      </c>
+      <c r="BO117">
+        <v>0</v>
+      </c>
+      <c r="BP117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7483792</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F118">
+        <v>24</v>
+      </c>
+      <c r="G118" t="s">
+        <v>72</v>
+      </c>
+      <c r="H118" t="s">
+        <v>71</v>
+      </c>
+      <c r="I118">
+        <v>2</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>2</v>
+      </c>
+      <c r="L118">
+        <v>2</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>158</v>
+      </c>
+      <c r="P118" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q118">
+        <v>2.42</v>
+      </c>
+      <c r="R118">
+        <v>2.11</v>
+      </c>
+      <c r="S118">
+        <v>4.35</v>
+      </c>
+      <c r="T118">
+        <v>1.36</v>
+      </c>
+      <c r="U118">
+        <v>2.89</v>
+      </c>
+      <c r="V118">
+        <v>2.8</v>
+      </c>
+      <c r="W118">
+        <v>1.38</v>
+      </c>
+      <c r="X118">
+        <v>6.9</v>
+      </c>
+      <c r="Y118">
+        <v>1.08</v>
+      </c>
+      <c r="Z118">
+        <v>1.93</v>
+      </c>
+      <c r="AA118">
+        <v>3.36</v>
+      </c>
+      <c r="AB118">
+        <v>3.93</v>
+      </c>
+      <c r="AC118">
+        <v>1.01</v>
+      </c>
+      <c r="AD118">
+        <v>8.6</v>
+      </c>
+      <c r="AE118">
+        <v>1.24</v>
+      </c>
+      <c r="AF118">
+        <v>3.34</v>
+      </c>
+      <c r="AG118">
+        <v>2</v>
+      </c>
+      <c r="AH118">
+        <v>1.75</v>
+      </c>
+      <c r="AI118">
+        <v>1.75</v>
+      </c>
+      <c r="AJ118">
+        <v>1.92</v>
+      </c>
+      <c r="AK118">
+        <v>1.22</v>
+      </c>
+      <c r="AL118">
+        <v>1.25</v>
+      </c>
+      <c r="AM118">
+        <v>1.83</v>
+      </c>
+      <c r="AN118">
+        <v>1.33</v>
+      </c>
+      <c r="AO118">
+        <v>0.64</v>
+      </c>
+      <c r="AP118">
+        <v>1.46</v>
+      </c>
+      <c r="AQ118">
+        <v>0.58</v>
+      </c>
+      <c r="AR118">
+        <v>1.52</v>
+      </c>
+      <c r="AS118">
+        <v>1.31</v>
+      </c>
+      <c r="AT118">
+        <v>2.83</v>
+      </c>
+      <c r="AU118">
+        <v>5</v>
+      </c>
+      <c r="AV118">
+        <v>4</v>
+      </c>
+      <c r="AW118">
+        <v>8</v>
+      </c>
+      <c r="AX118">
+        <v>10</v>
+      </c>
+      <c r="AY118">
+        <v>13</v>
+      </c>
+      <c r="AZ118">
+        <v>14</v>
+      </c>
+      <c r="BA118">
+        <v>3</v>
+      </c>
+      <c r="BB118">
+        <v>10</v>
+      </c>
+      <c r="BC118">
+        <v>13</v>
+      </c>
+      <c r="BD118">
+        <v>0</v>
+      </c>
+      <c r="BE118">
+        <v>0</v>
+      </c>
+      <c r="BF118">
+        <v>0</v>
+      </c>
+      <c r="BG118">
+        <v>0</v>
+      </c>
+      <c r="BH118">
+        <v>0</v>
+      </c>
+      <c r="BI118">
+        <v>0</v>
+      </c>
+      <c r="BJ118">
+        <v>0</v>
+      </c>
+      <c r="BK118">
+        <v>0</v>
+      </c>
+      <c r="BL118">
+        <v>0</v>
+      </c>
+      <c r="BM118">
+        <v>0</v>
+      </c>
+      <c r="BN118">
+        <v>0</v>
+      </c>
+      <c r="BO118">
+        <v>0</v>
+      </c>
+      <c r="BP118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7483789</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45724.5625</v>
+      </c>
+      <c r="F119">
+        <v>24</v>
+      </c>
+      <c r="G119" t="s">
+        <v>76</v>
+      </c>
+      <c r="H119" t="s">
+        <v>77</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>2</v>
+      </c>
+      <c r="K119">
+        <v>3</v>
+      </c>
+      <c r="L119">
+        <v>2</v>
+      </c>
+      <c r="M119">
+        <v>3</v>
+      </c>
+      <c r="N119">
+        <v>5</v>
+      </c>
+      <c r="O119" t="s">
+        <v>159</v>
+      </c>
+      <c r="P119" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q119">
+        <v>3.75</v>
+      </c>
+      <c r="R119">
+        <v>2.05</v>
+      </c>
+      <c r="S119">
+        <v>2.75</v>
+      </c>
+      <c r="T119">
+        <v>1.44</v>
+      </c>
+      <c r="U119">
+        <v>2.63</v>
+      </c>
+      <c r="V119">
+        <v>3.25</v>
+      </c>
+      <c r="W119">
+        <v>1.33</v>
+      </c>
+      <c r="X119">
+        <v>7.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.07</v>
+      </c>
+      <c r="Z119">
+        <v>3.29</v>
+      </c>
+      <c r="AA119">
+        <v>3.34</v>
+      </c>
+      <c r="AB119">
+        <v>2.14</v>
+      </c>
+      <c r="AC119">
+        <v>0</v>
+      </c>
+      <c r="AD119">
+        <v>0</v>
+      </c>
+      <c r="AE119">
+        <v>0</v>
+      </c>
+      <c r="AF119">
+        <v>0</v>
+      </c>
+      <c r="AG119">
+        <v>2</v>
+      </c>
+      <c r="AH119">
+        <v>1.75</v>
+      </c>
+      <c r="AI119">
+        <v>1.83</v>
+      </c>
+      <c r="AJ119">
+        <v>1.83</v>
+      </c>
+      <c r="AK119">
+        <v>0</v>
+      </c>
+      <c r="AL119">
+        <v>0</v>
+      </c>
+      <c r="AM119">
+        <v>0</v>
+      </c>
+      <c r="AN119">
+        <v>0.73</v>
+      </c>
+      <c r="AO119">
+        <v>1.83</v>
+      </c>
+      <c r="AP119">
+        <v>0.67</v>
+      </c>
+      <c r="AQ119">
+        <v>1.92</v>
+      </c>
+      <c r="AR119">
+        <v>1.44</v>
+      </c>
+      <c r="AS119">
+        <v>1.42</v>
+      </c>
+      <c r="AT119">
+        <v>2.86</v>
+      </c>
+      <c r="AU119">
+        <v>3</v>
+      </c>
+      <c r="AV119">
+        <v>10</v>
+      </c>
+      <c r="AW119">
+        <v>6</v>
+      </c>
+      <c r="AX119">
+        <v>5</v>
+      </c>
+      <c r="AY119">
+        <v>9</v>
+      </c>
+      <c r="AZ119">
+        <v>15</v>
+      </c>
+      <c r="BA119">
+        <v>5</v>
+      </c>
+      <c r="BB119">
+        <v>10</v>
+      </c>
+      <c r="BC119">
+        <v>15</v>
+      </c>
+      <c r="BD119">
+        <v>0</v>
+      </c>
+      <c r="BE119">
+        <v>0</v>
+      </c>
+      <c r="BF119">
+        <v>0</v>
+      </c>
+      <c r="BG119">
+        <v>0</v>
+      </c>
+      <c r="BH119">
+        <v>0</v>
+      </c>
+      <c r="BI119">
+        <v>0</v>
+      </c>
+      <c r="BJ119">
+        <v>0</v>
+      </c>
+      <c r="BK119">
+        <v>0</v>
+      </c>
+      <c r="BL119">
+        <v>0</v>
+      </c>
+      <c r="BM119">
+        <v>0</v>
+      </c>
+      <c r="BN119">
+        <v>0</v>
+      </c>
+      <c r="BO119">
+        <v>0</v>
+      </c>
+      <c r="BP119">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="218">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,9 @@
     <t>['36', '77']</t>
   </si>
   <si>
+    <t>['27', '90+3']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -662,6 +665,9 @@
   </si>
   <si>
     <t>['21', '45+1', '90']</t>
+  </si>
+  <si>
+    <t>['55', '70']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1897,7 +1903,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -1975,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ5">
         <v>0.67</v>
@@ -2181,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ6">
         <v>1.58</v>
@@ -2515,7 +2521,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2802,7 +2808,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ9">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3339,7 +3345,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3829,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ14">
         <v>1.58</v>
@@ -4163,7 +4169,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4450,7 +4456,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ17">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>1.21</v>
@@ -4575,7 +4581,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4653,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ18">
         <v>0.58</v>
@@ -4859,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5193,7 +5199,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5399,7 +5405,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5811,7 +5817,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6017,7 +6023,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6429,7 +6435,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6713,10 +6719,10 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ28">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -6841,7 +6847,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6919,7 +6925,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7253,7 +7259,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7743,7 +7749,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8489,7 +8495,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8570,7 +8576,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -8901,7 +8907,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -8979,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ39">
         <v>0.31</v>
@@ -9185,7 +9191,7 @@
         <v>2.25</v>
       </c>
       <c r="AP40">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ40">
         <v>1.92</v>
@@ -9391,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ41">
         <v>1.73</v>
@@ -9519,7 +9525,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9931,7 +9937,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10137,7 +10143,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10549,7 +10555,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10630,7 +10636,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ47">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR47">
         <v>1.05</v>
@@ -10755,7 +10761,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11167,7 +11173,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11579,7 +11585,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11991,7 +11997,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12069,7 +12075,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ54">
         <v>1.18</v>
@@ -12197,7 +12203,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12403,7 +12409,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12609,7 +12615,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12687,7 +12693,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -12815,7 +12821,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12896,7 +12902,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ58">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR58">
         <v>1.46</v>
@@ -13021,7 +13027,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13227,7 +13233,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13433,7 +13439,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13639,7 +13645,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13845,7 +13851,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14051,7 +14057,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14257,7 +14263,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14953,7 +14959,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ68">
         <v>0.58</v>
@@ -15081,7 +15087,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15287,7 +15293,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15365,10 +15371,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ70">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR70">
         <v>1.99</v>
@@ -15493,7 +15499,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16317,7 +16323,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16523,7 +16529,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16807,7 +16813,7 @@
         <v>2.14</v>
       </c>
       <c r="AP77">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ77">
         <v>1.92</v>
@@ -16935,7 +16941,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17141,7 +17147,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17222,7 +17228,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ79">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR79">
         <v>1.42</v>
@@ -17553,7 +17559,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17759,7 +17765,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18789,7 +18795,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18867,7 +18873,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ87">
         <v>0.67</v>
@@ -18995,7 +19001,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19076,7 +19082,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ88">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR88">
         <v>1.51</v>
@@ -19201,7 +19207,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19485,7 +19491,7 @@
         <v>0.13</v>
       </c>
       <c r="AP90">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ90">
         <v>0.31</v>
@@ -19613,7 +19619,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19819,7 +19825,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19897,7 +19903,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ92">
         <v>1.58</v>
@@ -20103,7 +20109,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP93">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ93">
         <v>0.67</v>
@@ -20643,7 +20649,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21055,7 +21061,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21261,7 +21267,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21467,7 +21473,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21545,7 +21551,7 @@
         <v>1.44</v>
       </c>
       <c r="AP100">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ100">
         <v>1.73</v>
@@ -21673,7 +21679,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21754,7 +21760,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ101">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR101">
         <v>1.43</v>
@@ -21879,7 +21885,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -21957,7 +21963,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ102">
         <v>1.58</v>
@@ -22703,7 +22709,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22909,7 +22915,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23193,7 +23199,7 @@
         <v>1.1</v>
       </c>
       <c r="AP108">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23321,7 +23327,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23399,7 +23405,7 @@
         <v>0.7</v>
       </c>
       <c r="AP109">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109">
         <v>0.58</v>
@@ -23733,7 +23739,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24351,7 +24357,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24557,7 +24563,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24763,7 +24769,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24844,7 +24850,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ116">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR116">
         <v>1.46</v>
@@ -24969,7 +24975,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25381,7 +25387,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25537,6 +25543,418 @@
         <v>0</v>
       </c>
       <c r="BP119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7483791</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F120">
+        <v>24</v>
+      </c>
+      <c r="G120" t="s">
+        <v>73</v>
+      </c>
+      <c r="H120" t="s">
+        <v>70</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>1</v>
+      </c>
+      <c r="O120" t="s">
+        <v>104</v>
+      </c>
+      <c r="P120" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q120">
+        <v>2.88</v>
+      </c>
+      <c r="R120">
+        <v>2.05</v>
+      </c>
+      <c r="S120">
+        <v>3.75</v>
+      </c>
+      <c r="T120">
+        <v>1.44</v>
+      </c>
+      <c r="U120">
+        <v>2.63</v>
+      </c>
+      <c r="V120">
+        <v>3.25</v>
+      </c>
+      <c r="W120">
+        <v>1.33</v>
+      </c>
+      <c r="X120">
+        <v>7.5</v>
+      </c>
+      <c r="Y120">
+        <v>1.07</v>
+      </c>
+      <c r="Z120">
+        <v>2.23</v>
+      </c>
+      <c r="AA120">
+        <v>3.37</v>
+      </c>
+      <c r="AB120">
+        <v>3.08</v>
+      </c>
+      <c r="AC120">
+        <v>0</v>
+      </c>
+      <c r="AD120">
+        <v>0</v>
+      </c>
+      <c r="AE120">
+        <v>3.23</v>
+      </c>
+      <c r="AF120">
+        <v>1.32</v>
+      </c>
+      <c r="AG120">
+        <v>2.05</v>
+      </c>
+      <c r="AH120">
+        <v>1.65</v>
+      </c>
+      <c r="AI120">
+        <v>1.83</v>
+      </c>
+      <c r="AJ120">
+        <v>1.83</v>
+      </c>
+      <c r="AK120">
+        <v>0</v>
+      </c>
+      <c r="AL120">
+        <v>0</v>
+      </c>
+      <c r="AM120">
+        <v>0</v>
+      </c>
+      <c r="AN120">
+        <v>2.17</v>
+      </c>
+      <c r="AO120">
+        <v>2.18</v>
+      </c>
+      <c r="AP120">
+        <v>2.23</v>
+      </c>
+      <c r="AQ120">
+        <v>2</v>
+      </c>
+      <c r="AR120">
+        <v>1.91</v>
+      </c>
+      <c r="AS120">
+        <v>1.81</v>
+      </c>
+      <c r="AT120">
+        <v>3.72</v>
+      </c>
+      <c r="AU120">
+        <v>5</v>
+      </c>
+      <c r="AV120">
+        <v>0</v>
+      </c>
+      <c r="AW120">
+        <v>5</v>
+      </c>
+      <c r="AX120">
+        <v>5</v>
+      </c>
+      <c r="AY120">
+        <v>10</v>
+      </c>
+      <c r="AZ120">
+        <v>5</v>
+      </c>
+      <c r="BA120">
+        <v>8</v>
+      </c>
+      <c r="BB120">
+        <v>3</v>
+      </c>
+      <c r="BC120">
+        <v>11</v>
+      </c>
+      <c r="BD120">
+        <v>0</v>
+      </c>
+      <c r="BE120">
+        <v>0</v>
+      </c>
+      <c r="BF120">
+        <v>0</v>
+      </c>
+      <c r="BG120">
+        <v>0</v>
+      </c>
+      <c r="BH120">
+        <v>0</v>
+      </c>
+      <c r="BI120">
+        <v>0</v>
+      </c>
+      <c r="BJ120">
+        <v>0</v>
+      </c>
+      <c r="BK120">
+        <v>0</v>
+      </c>
+      <c r="BL120">
+        <v>0</v>
+      </c>
+      <c r="BM120">
+        <v>0</v>
+      </c>
+      <c r="BN120">
+        <v>0</v>
+      </c>
+      <c r="BO120">
+        <v>0</v>
+      </c>
+      <c r="BP120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7483790</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45725.5625</v>
+      </c>
+      <c r="F121">
+        <v>24</v>
+      </c>
+      <c r="G121" t="s">
+        <v>74</v>
+      </c>
+      <c r="H121" t="s">
+        <v>79</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>4</v>
+      </c>
+      <c r="O121" t="s">
+        <v>160</v>
+      </c>
+      <c r="P121" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q121">
+        <v>0</v>
+      </c>
+      <c r="R121">
+        <v>0</v>
+      </c>
+      <c r="S121">
+        <v>0</v>
+      </c>
+      <c r="T121">
+        <v>0</v>
+      </c>
+      <c r="U121">
+        <v>0</v>
+      </c>
+      <c r="V121">
+        <v>0</v>
+      </c>
+      <c r="W121">
+        <v>0</v>
+      </c>
+      <c r="X121">
+        <v>0</v>
+      </c>
+      <c r="Y121">
+        <v>0</v>
+      </c>
+      <c r="Z121">
+        <v>1.28</v>
+      </c>
+      <c r="AA121">
+        <v>5.3</v>
+      </c>
+      <c r="AB121">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC121">
+        <v>0</v>
+      </c>
+      <c r="AD121">
+        <v>0</v>
+      </c>
+      <c r="AE121">
+        <v>0</v>
+      </c>
+      <c r="AF121">
+        <v>0</v>
+      </c>
+      <c r="AG121">
+        <v>1.6</v>
+      </c>
+      <c r="AH121">
+        <v>2.1</v>
+      </c>
+      <c r="AI121">
+        <v>0</v>
+      </c>
+      <c r="AJ121">
+        <v>0</v>
+      </c>
+      <c r="AK121">
+        <v>0</v>
+      </c>
+      <c r="AL121">
+        <v>0</v>
+      </c>
+      <c r="AM121">
+        <v>0</v>
+      </c>
+      <c r="AN121">
+        <v>1.83</v>
+      </c>
+      <c r="AO121">
+        <v>1</v>
+      </c>
+      <c r="AP121">
+        <v>1.77</v>
+      </c>
+      <c r="AQ121">
+        <v>1</v>
+      </c>
+      <c r="AR121">
+        <v>2.13</v>
+      </c>
+      <c r="AS121">
+        <v>1.26</v>
+      </c>
+      <c r="AT121">
+        <v>3.39</v>
+      </c>
+      <c r="AU121">
+        <v>-1</v>
+      </c>
+      <c r="AV121">
+        <v>-1</v>
+      </c>
+      <c r="AW121">
+        <v>-1</v>
+      </c>
+      <c r="AX121">
+        <v>-1</v>
+      </c>
+      <c r="AY121">
+        <v>-1</v>
+      </c>
+      <c r="AZ121">
+        <v>-1</v>
+      </c>
+      <c r="BA121">
+        <v>-1</v>
+      </c>
+      <c r="BB121">
+        <v>-1</v>
+      </c>
+      <c r="BC121">
+        <v>-1</v>
+      </c>
+      <c r="BD121">
+        <v>0</v>
+      </c>
+      <c r="BE121">
+        <v>0</v>
+      </c>
+      <c r="BF121">
+        <v>0</v>
+      </c>
+      <c r="BG121">
+        <v>0</v>
+      </c>
+      <c r="BH121">
+        <v>0</v>
+      </c>
+      <c r="BI121">
+        <v>0</v>
+      </c>
+      <c r="BJ121">
+        <v>0</v>
+      </c>
+      <c r="BK121">
+        <v>0</v>
+      </c>
+      <c r="BL121">
+        <v>0</v>
+      </c>
+      <c r="BM121">
+        <v>0</v>
+      </c>
+      <c r="BN121">
+        <v>0</v>
+      </c>
+      <c r="BO121">
+        <v>0</v>
+      </c>
+      <c r="BP121">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -497,6 +497,9 @@
   </si>
   <si>
     <t>['27', '90+3']</t>
+  </si>
+  <si>
+    <t>['39', '66']</t>
   </si>
   <si>
     <t>['83']</t>
@@ -1029,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1569,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3">
         <v>1.92</v>
@@ -1903,7 +1906,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2190,7 +2193,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ6">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2521,7 +2524,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3217,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ11">
         <v>0.67</v>
@@ -3345,7 +3348,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3838,7 +3841,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ14">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR14">
         <v>1.88</v>
@@ -4169,7 +4172,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4581,7 +4584,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5199,7 +5202,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5405,7 +5408,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5486,7 +5489,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ22">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5817,7 +5820,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5895,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24">
         <v>1.73</v>
@@ -6023,7 +6026,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6435,7 +6438,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6847,7 +6850,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7259,7 +7262,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7543,10 +7546,10 @@
         <v>1.33</v>
       </c>
       <c r="AP32">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -8495,7 +8498,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8573,7 +8576,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
         <v>2</v>
@@ -8907,7 +8910,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9525,7 +9528,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9606,7 +9609,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ42">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR42">
         <v>2.18</v>
@@ -9937,7 +9940,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10143,7 +10146,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10555,7 +10558,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10761,7 +10764,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11173,7 +11176,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11457,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ51">
         <v>0.31</v>
@@ -11585,7 +11588,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11872,7 +11875,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ53">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR53">
         <v>1.07</v>
@@ -11997,7 +12000,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12203,7 +12206,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12409,7 +12412,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12615,7 +12618,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12821,7 +12824,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13027,7 +13030,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13233,7 +13236,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13439,7 +13442,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13645,7 +13648,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13851,7 +13854,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14057,7 +14060,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14138,7 +14141,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ64">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR64">
         <v>1.37</v>
@@ -14263,7 +14266,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14341,7 +14344,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ65">
         <v>1.18</v>
@@ -15087,7 +15090,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15293,7 +15296,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15499,7 +15502,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15992,7 +15995,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ73">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16323,7 +16326,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16401,7 +16404,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16529,7 +16532,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16941,7 +16944,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17147,7 +17150,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17559,7 +17562,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17640,7 +17643,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ81">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -17765,7 +17768,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18795,7 +18798,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19001,7 +19004,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19207,7 +19210,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19285,7 +19288,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19619,7 +19622,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19825,7 +19828,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19906,7 +19909,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ92">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20649,7 +20652,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20727,7 +20730,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ96">
         <v>1.92</v>
@@ -21061,7 +21064,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21267,7 +21270,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21473,7 +21476,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21679,7 +21682,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21885,7 +21888,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -21966,7 +21969,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ102">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR102">
         <v>1.84</v>
@@ -22581,7 +22584,7 @@
         <v>0.5</v>
       </c>
       <c r="AP105">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ105">
         <v>0.67</v>
@@ -22709,7 +22712,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22915,7 +22918,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23327,7 +23330,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23739,7 +23742,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -23817,7 +23820,7 @@
         <v>1.6</v>
       </c>
       <c r="AP111">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ111">
         <v>1.73</v>
@@ -24357,7 +24360,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24438,7 +24441,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ114">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR114">
         <v>1.48</v>
@@ -24563,7 +24566,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24769,7 +24772,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24975,7 +24978,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25387,7 +25390,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25799,7 +25802,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -25892,31 +25895,31 @@
         <v>3.39</v>
       </c>
       <c r="AU121">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV121">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW121">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX121">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY121">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ121">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA121">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB121">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC121">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD121">
         <v>0</v>
@@ -25956,6 +25959,212 @@
       </c>
       <c r="BP121">
         <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7483793</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45727.5625</v>
+      </c>
+      <c r="F122">
+        <v>25</v>
+      </c>
+      <c r="G122" t="s">
+        <v>71</v>
+      </c>
+      <c r="H122" t="s">
+        <v>78</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>2</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122" t="s">
+        <v>161</v>
+      </c>
+      <c r="P122" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q122">
+        <v>4.2</v>
+      </c>
+      <c r="R122">
+        <v>2.05</v>
+      </c>
+      <c r="S122">
+        <v>2.5</v>
+      </c>
+      <c r="T122">
+        <v>1.42</v>
+      </c>
+      <c r="U122">
+        <v>2.6</v>
+      </c>
+      <c r="V122">
+        <v>2.95</v>
+      </c>
+      <c r="W122">
+        <v>1.34</v>
+      </c>
+      <c r="X122">
+        <v>7.75</v>
+      </c>
+      <c r="Y122">
+        <v>1.07</v>
+      </c>
+      <c r="Z122">
+        <v>4.1</v>
+      </c>
+      <c r="AA122">
+        <v>3.55</v>
+      </c>
+      <c r="AB122">
+        <v>1.84</v>
+      </c>
+      <c r="AC122">
+        <v>1.06</v>
+      </c>
+      <c r="AD122">
+        <v>8</v>
+      </c>
+      <c r="AE122">
+        <v>1.35</v>
+      </c>
+      <c r="AF122">
+        <v>3</v>
+      </c>
+      <c r="AG122">
+        <v>2</v>
+      </c>
+      <c r="AH122">
+        <v>1.67</v>
+      </c>
+      <c r="AI122">
+        <v>1.9</v>
+      </c>
+      <c r="AJ122">
+        <v>1.77</v>
+      </c>
+      <c r="AK122">
+        <v>1.83</v>
+      </c>
+      <c r="AL122">
+        <v>1.29</v>
+      </c>
+      <c r="AM122">
+        <v>1.24</v>
+      </c>
+      <c r="AN122">
+        <v>1.25</v>
+      </c>
+      <c r="AO122">
+        <v>1.58</v>
+      </c>
+      <c r="AP122">
+        <v>1.38</v>
+      </c>
+      <c r="AQ122">
+        <v>1.46</v>
+      </c>
+      <c r="AR122">
+        <v>1.32</v>
+      </c>
+      <c r="AS122">
+        <v>1.5</v>
+      </c>
+      <c r="AT122">
+        <v>2.82</v>
+      </c>
+      <c r="AU122">
+        <v>6</v>
+      </c>
+      <c r="AV122">
+        <v>7</v>
+      </c>
+      <c r="AW122">
+        <v>5</v>
+      </c>
+      <c r="AX122">
+        <v>8</v>
+      </c>
+      <c r="AY122">
+        <v>11</v>
+      </c>
+      <c r="AZ122">
+        <v>15</v>
+      </c>
+      <c r="BA122">
+        <v>2</v>
+      </c>
+      <c r="BB122">
+        <v>5</v>
+      </c>
+      <c r="BC122">
+        <v>7</v>
+      </c>
+      <c r="BD122">
+        <v>2.78</v>
+      </c>
+      <c r="BE122">
+        <v>8</v>
+      </c>
+      <c r="BF122">
+        <v>1.58</v>
+      </c>
+      <c r="BG122">
+        <v>1.4</v>
+      </c>
+      <c r="BH122">
+        <v>2.56</v>
+      </c>
+      <c r="BI122">
+        <v>1.74</v>
+      </c>
+      <c r="BJ122">
+        <v>1.93</v>
+      </c>
+      <c r="BK122">
+        <v>2.21</v>
+      </c>
+      <c r="BL122">
+        <v>1.53</v>
+      </c>
+      <c r="BM122">
+        <v>3.04</v>
+      </c>
+      <c r="BN122">
+        <v>1.29</v>
+      </c>
+      <c r="BO122">
+        <v>4.05</v>
+      </c>
+      <c r="BP122">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="222">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,12 @@
     <t>['39', '66']</t>
   </si>
   <si>
+    <t>['8', '82']</t>
+  </si>
+  <si>
+    <t>['35', '89']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -671,6 +677,9 @@
   </si>
   <si>
     <t>['55', '70']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1366,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1906,7 +1915,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2524,7 +2533,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2605,7 +2614,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3348,7 +3357,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3426,7 +3435,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ12">
         <v>1.92</v>
@@ -4044,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ15">
         <v>0.31</v>
@@ -4172,7 +4181,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4584,7 +4593,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4871,7 +4880,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR19">
         <v>1.75</v>
@@ -5202,7 +5211,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5280,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ21">
         <v>0.67</v>
@@ -5408,7 +5417,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5820,7 +5829,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5901,7 +5910,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ24">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR24">
         <v>1.24</v>
@@ -6026,7 +6035,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6104,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ25">
         <v>1.18</v>
@@ -6438,7 +6447,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6850,7 +6859,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7262,7 +7271,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -8164,10 +8173,10 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR35">
         <v>2.01</v>
@@ -8498,7 +8507,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8910,7 +8919,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9403,7 +9412,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ41">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR41">
         <v>2.19</v>
@@ -9528,7 +9537,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9606,7 +9615,7 @@
         <v>1.25</v>
       </c>
       <c r="AP42">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ42">
         <v>1.46</v>
@@ -9815,7 +9824,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR43">
         <v>1.26</v>
@@ -9940,7 +9949,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10021,7 +10030,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ44">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10146,7 +10155,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10433,7 +10442,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR46">
         <v>1.5</v>
@@ -10558,7 +10567,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10636,7 +10645,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ47">
         <v>2</v>
@@ -10764,7 +10773,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11176,7 +11185,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11257,7 +11266,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ50">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11588,7 +11597,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11872,7 +11881,7 @@
         <v>1.2</v>
       </c>
       <c r="AP53">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ53">
         <v>1.46</v>
@@ -12000,7 +12009,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12206,7 +12215,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12284,7 +12293,7 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ55">
         <v>1.92</v>
@@ -12412,7 +12421,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12490,7 +12499,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ56">
         <v>0.58</v>
@@ -12618,7 +12627,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12699,7 +12708,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
         <v>2.09</v>
@@ -12824,7 +12833,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13030,7 +13039,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13236,7 +13245,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13317,7 +13326,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR60">
         <v>1.4</v>
@@ -13442,7 +13451,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13648,7 +13657,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13726,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ62">
         <v>0.31</v>
@@ -13854,7 +13863,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13935,7 +13944,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ63">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR63">
         <v>1.5</v>
@@ -14060,7 +14069,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14266,7 +14275,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14550,7 +14559,7 @@
         <v>0.67</v>
       </c>
       <c r="AP66">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ66">
         <v>0.67</v>
@@ -15090,7 +15099,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15171,7 +15180,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -15296,7 +15305,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15502,7 +15511,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16198,10 +16207,10 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ74">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR74">
         <v>1.87</v>
@@ -16326,7 +16335,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16407,7 +16416,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR75">
         <v>1.44</v>
@@ -16532,7 +16541,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16610,7 +16619,7 @@
         <v>1.14</v>
       </c>
       <c r="AP76">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ76">
         <v>1.18</v>
@@ -16944,7 +16953,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17150,7 +17159,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17434,10 +17443,10 @@
         <v>1.71</v>
       </c>
       <c r="AP80">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ80">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR80">
         <v>1.04</v>
@@ -17562,7 +17571,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17768,7 +17777,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -17849,7 +17858,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ82">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR82">
         <v>1.46</v>
@@ -18052,10 +18061,10 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR83">
         <v>1.05</v>
@@ -18464,7 +18473,7 @@
         <v>0.86</v>
       </c>
       <c r="AP85">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ85">
         <v>0.58</v>
@@ -18798,7 +18807,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19004,7 +19013,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19210,7 +19219,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19622,7 +19631,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19828,7 +19837,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20318,7 +20327,7 @@
         <v>1.22</v>
       </c>
       <c r="AP94">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20652,7 +20661,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21064,7 +21073,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21270,7 +21279,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21351,7 +21360,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21476,7 +21485,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21557,7 +21566,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ100">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR100">
         <v>2.09</v>
@@ -21682,7 +21691,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21888,7 +21897,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22378,7 +22387,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ104">
         <v>0.31</v>
@@ -22712,7 +22721,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22918,7 +22927,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23205,7 +23214,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR108">
         <v>1.88</v>
@@ -23330,7 +23339,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23614,7 +23623,7 @@
         <v>0.45</v>
       </c>
       <c r="AP110">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
         <v>0.67</v>
@@ -23742,7 +23751,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -23823,7 +23832,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ111">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR111">
         <v>1.34</v>
@@ -24232,7 +24241,7 @@
         <v>1.3</v>
       </c>
       <c r="AP113">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ113">
         <v>1.18</v>
@@ -24360,7 +24369,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24566,7 +24575,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24644,7 +24653,7 @@
         <v>1.91</v>
       </c>
       <c r="AP115">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ115">
         <v>1.92</v>
@@ -24772,7 +24781,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24978,7 +24987,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25390,7 +25399,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25802,7 +25811,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26165,6 +26174,418 @@
       </c>
       <c r="BP122">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7483795</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45728.45833333334</v>
+      </c>
+      <c r="F123">
+        <v>25</v>
+      </c>
+      <c r="G123" t="s">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s">
+        <v>73</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>2</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>3</v>
+      </c>
+      <c r="O123" t="s">
+        <v>162</v>
+      </c>
+      <c r="P123" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q123">
+        <v>0</v>
+      </c>
+      <c r="R123">
+        <v>0</v>
+      </c>
+      <c r="S123">
+        <v>0</v>
+      </c>
+      <c r="T123">
+        <v>0</v>
+      </c>
+      <c r="U123">
+        <v>0</v>
+      </c>
+      <c r="V123">
+        <v>0</v>
+      </c>
+      <c r="W123">
+        <v>0</v>
+      </c>
+      <c r="X123">
+        <v>0</v>
+      </c>
+      <c r="Y123">
+        <v>0</v>
+      </c>
+      <c r="Z123">
+        <v>6</v>
+      </c>
+      <c r="AA123">
+        <v>3.78</v>
+      </c>
+      <c r="AB123">
+        <v>1.57</v>
+      </c>
+      <c r="AC123">
+        <v>0</v>
+      </c>
+      <c r="AD123">
+        <v>0</v>
+      </c>
+      <c r="AE123">
+        <v>0</v>
+      </c>
+      <c r="AF123">
+        <v>0</v>
+      </c>
+      <c r="AG123">
+        <v>1.83</v>
+      </c>
+      <c r="AH123">
+        <v>1.91</v>
+      </c>
+      <c r="AI123">
+        <v>0</v>
+      </c>
+      <c r="AJ123">
+        <v>0</v>
+      </c>
+      <c r="AK123">
+        <v>0</v>
+      </c>
+      <c r="AL123">
+        <v>0</v>
+      </c>
+      <c r="AM123">
+        <v>0</v>
+      </c>
+      <c r="AN123">
+        <v>1.27</v>
+      </c>
+      <c r="AO123">
+        <v>1.73</v>
+      </c>
+      <c r="AP123">
+        <v>1.42</v>
+      </c>
+      <c r="AQ123">
+        <v>1.58</v>
+      </c>
+      <c r="AR123">
+        <v>1.1</v>
+      </c>
+      <c r="AS123">
+        <v>1.64</v>
+      </c>
+      <c r="AT123">
+        <v>2.74</v>
+      </c>
+      <c r="AU123">
+        <v>-1</v>
+      </c>
+      <c r="AV123">
+        <v>-1</v>
+      </c>
+      <c r="AW123">
+        <v>-1</v>
+      </c>
+      <c r="AX123">
+        <v>-1</v>
+      </c>
+      <c r="AY123">
+        <v>-1</v>
+      </c>
+      <c r="AZ123">
+        <v>-1</v>
+      </c>
+      <c r="BA123">
+        <v>-1</v>
+      </c>
+      <c r="BB123">
+        <v>-1</v>
+      </c>
+      <c r="BC123">
+        <v>-1</v>
+      </c>
+      <c r="BD123">
+        <v>0</v>
+      </c>
+      <c r="BE123">
+        <v>0</v>
+      </c>
+      <c r="BF123">
+        <v>0</v>
+      </c>
+      <c r="BG123">
+        <v>0</v>
+      </c>
+      <c r="BH123">
+        <v>0</v>
+      </c>
+      <c r="BI123">
+        <v>0</v>
+      </c>
+      <c r="BJ123">
+        <v>0</v>
+      </c>
+      <c r="BK123">
+        <v>0</v>
+      </c>
+      <c r="BL123">
+        <v>0</v>
+      </c>
+      <c r="BM123">
+        <v>0</v>
+      </c>
+      <c r="BN123">
+        <v>0</v>
+      </c>
+      <c r="BO123">
+        <v>0</v>
+      </c>
+      <c r="BP123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7483794</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45728.5625</v>
+      </c>
+      <c r="F124">
+        <v>25</v>
+      </c>
+      <c r="G124" t="s">
+        <v>70</v>
+      </c>
+      <c r="H124" t="s">
+        <v>72</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>2</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>163</v>
+      </c>
+      <c r="P124" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q124">
+        <v>1.93</v>
+      </c>
+      <c r="R124">
+        <v>2.25</v>
+      </c>
+      <c r="S124">
+        <v>6.5</v>
+      </c>
+      <c r="T124">
+        <v>1.39</v>
+      </c>
+      <c r="U124">
+        <v>2.75</v>
+      </c>
+      <c r="V124">
+        <v>2.87</v>
+      </c>
+      <c r="W124">
+        <v>1.36</v>
+      </c>
+      <c r="X124">
+        <v>7.5</v>
+      </c>
+      <c r="Y124">
+        <v>1.07</v>
+      </c>
+      <c r="Z124">
+        <v>1.46</v>
+      </c>
+      <c r="AA124">
+        <v>4.2</v>
+      </c>
+      <c r="AB124">
+        <v>6.7</v>
+      </c>
+      <c r="AC124">
+        <v>1.05</v>
+      </c>
+      <c r="AD124">
+        <v>8.5</v>
+      </c>
+      <c r="AE124">
+        <v>1.33</v>
+      </c>
+      <c r="AF124">
+        <v>3.1</v>
+      </c>
+      <c r="AG124">
+        <v>1.91</v>
+      </c>
+      <c r="AH124">
+        <v>1.83</v>
+      </c>
+      <c r="AI124">
+        <v>2.3</v>
+      </c>
+      <c r="AJ124">
+        <v>1.53</v>
+      </c>
+      <c r="AK124">
+        <v>1.09</v>
+      </c>
+      <c r="AL124">
+        <v>1.2</v>
+      </c>
+      <c r="AM124">
+        <v>2.7</v>
+      </c>
+      <c r="AN124">
+        <v>2.25</v>
+      </c>
+      <c r="AO124">
+        <v>1</v>
+      </c>
+      <c r="AP124">
+        <v>2.31</v>
+      </c>
+      <c r="AQ124">
+        <v>0.92</v>
+      </c>
+      <c r="AR124">
+        <v>1.8</v>
+      </c>
+      <c r="AS124">
+        <v>1.32</v>
+      </c>
+      <c r="AT124">
+        <v>3.12</v>
+      </c>
+      <c r="AU124">
+        <v>7</v>
+      </c>
+      <c r="AV124">
+        <v>2</v>
+      </c>
+      <c r="AW124">
+        <v>8</v>
+      </c>
+      <c r="AX124">
+        <v>2</v>
+      </c>
+      <c r="AY124">
+        <v>15</v>
+      </c>
+      <c r="AZ124">
+        <v>4</v>
+      </c>
+      <c r="BA124">
+        <v>15</v>
+      </c>
+      <c r="BB124">
+        <v>1</v>
+      </c>
+      <c r="BC124">
+        <v>16</v>
+      </c>
+      <c r="BD124">
+        <v>1.21</v>
+      </c>
+      <c r="BE124">
+        <v>10.5</v>
+      </c>
+      <c r="BF124">
+        <v>5.1</v>
+      </c>
+      <c r="BG124">
+        <v>1.29</v>
+      </c>
+      <c r="BH124">
+        <v>3.3</v>
+      </c>
+      <c r="BI124">
+        <v>1.47</v>
+      </c>
+      <c r="BJ124">
+        <v>2.56</v>
+      </c>
+      <c r="BK124">
+        <v>1.85</v>
+      </c>
+      <c r="BL124">
+        <v>1.95</v>
+      </c>
+      <c r="BM124">
+        <v>2.29</v>
+      </c>
+      <c r="BN124">
+        <v>1.58</v>
+      </c>
+      <c r="BO124">
+        <v>2.9</v>
+      </c>
+      <c r="BP124">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="224">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,9 @@
     <t>['35', '89']</t>
   </si>
   <si>
+    <t>['4', '27', '84']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -680,6 +683,9 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['23', '48']</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP124"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1915,7 +1921,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -1996,7 +2002,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ5">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2405,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
         <v>0.58</v>
@@ -2533,7 +2539,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3232,7 +3238,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ11">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR11">
         <v>1.27</v>
@@ -3357,7 +3363,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4181,7 +4187,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4259,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4593,7 +4599,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5211,7 +5217,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5292,7 +5298,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ21">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR21">
         <v>1.05</v>
@@ -5417,7 +5423,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5829,7 +5835,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6035,7 +6041,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6447,7 +6453,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6859,7 +6865,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7271,7 +7277,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7349,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR31">
         <v>1.26</v>
@@ -8507,7 +8513,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8794,7 +8800,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ38">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR38">
         <v>1.19</v>
@@ -8919,7 +8925,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9537,7 +9543,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9949,7 +9955,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10027,7 +10033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ44">
         <v>1.58</v>
@@ -10155,7 +10161,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10439,7 +10445,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ46">
         <v>0.92</v>
@@ -10567,7 +10573,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10773,7 +10779,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11185,7 +11191,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11597,7 +11603,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11678,7 +11684,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ52">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -12009,7 +12015,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12215,7 +12221,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12421,7 +12427,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12627,7 +12633,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12833,7 +12839,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12911,7 +12917,7 @@
         <v>2.2</v>
       </c>
       <c r="AP58">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ58">
         <v>2</v>
@@ -13039,7 +13045,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13245,7 +13251,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13451,7 +13457,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13657,7 +13663,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13863,7 +13869,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14069,7 +14075,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14275,7 +14281,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14562,7 +14568,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ66">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR66">
         <v>1.87</v>
@@ -15099,7 +15105,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15305,7 +15311,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15511,7 +15517,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15589,7 +15595,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ71">
         <v>1.92</v>
@@ -15798,7 +15804,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ72">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR72">
         <v>1.36</v>
@@ -16001,7 +16007,7 @@
         <v>0.86</v>
       </c>
       <c r="AP73">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ73">
         <v>1.46</v>
@@ -16335,7 +16341,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16541,7 +16547,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16953,7 +16959,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17159,7 +17165,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17571,7 +17577,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17777,7 +17783,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18267,7 +18273,7 @@
         <v>1.38</v>
       </c>
       <c r="AP84">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ84">
         <v>1.18</v>
@@ -18807,7 +18813,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18888,7 +18894,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ87">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19013,7 +19019,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19219,7 +19225,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19631,7 +19637,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19837,7 +19843,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20124,7 +20130,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ93">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20661,7 +20667,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21073,7 +21079,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21151,7 +21157,7 @@
         <v>0.78</v>
       </c>
       <c r="AP98">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ98">
         <v>0.58</v>
@@ -21279,7 +21285,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21485,7 +21491,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21691,7 +21697,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21897,7 +21903,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22596,7 +22602,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ105">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -22721,7 +22727,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22799,7 +22805,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -22927,7 +22933,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23339,7 +23345,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23626,7 +23632,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR110">
         <v>1.09</v>
@@ -23751,7 +23757,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24369,7 +24375,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24575,7 +24581,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24781,7 +24787,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24987,7 +24993,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25399,7 +25405,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25811,7 +25817,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26223,7 +26229,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26586,6 +26592,212 @@
       </c>
       <c r="BP124">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7483797</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45729.47916666666</v>
+      </c>
+      <c r="F125">
+        <v>25</v>
+      </c>
+      <c r="G125" t="s">
+        <v>75</v>
+      </c>
+      <c r="H125" t="s">
+        <v>76</v>
+      </c>
+      <c r="I125">
+        <v>2</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+      <c r="K125">
+        <v>3</v>
+      </c>
+      <c r="L125">
+        <v>3</v>
+      </c>
+      <c r="M125">
+        <v>2</v>
+      </c>
+      <c r="N125">
+        <v>5</v>
+      </c>
+      <c r="O125" t="s">
+        <v>164</v>
+      </c>
+      <c r="P125" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q125">
+        <v>2.85</v>
+      </c>
+      <c r="R125">
+        <v>2.1</v>
+      </c>
+      <c r="S125">
+        <v>3.3</v>
+      </c>
+      <c r="T125">
+        <v>1.38</v>
+      </c>
+      <c r="U125">
+        <v>2.8</v>
+      </c>
+      <c r="V125">
+        <v>2.85</v>
+      </c>
+      <c r="W125">
+        <v>1.37</v>
+      </c>
+      <c r="X125">
+        <v>7.5</v>
+      </c>
+      <c r="Y125">
+        <v>1.08</v>
+      </c>
+      <c r="Z125">
+        <v>2.27</v>
+      </c>
+      <c r="AA125">
+        <v>3.58</v>
+      </c>
+      <c r="AB125">
+        <v>2.85</v>
+      </c>
+      <c r="AC125">
+        <v>1.05</v>
+      </c>
+      <c r="AD125">
+        <v>8.5</v>
+      </c>
+      <c r="AE125">
+        <v>1.3</v>
+      </c>
+      <c r="AF125">
+        <v>3.35</v>
+      </c>
+      <c r="AG125">
+        <v>1.92</v>
+      </c>
+      <c r="AH125">
+        <v>1.82</v>
+      </c>
+      <c r="AI125">
+        <v>1.77</v>
+      </c>
+      <c r="AJ125">
+        <v>1.9</v>
+      </c>
+      <c r="AK125">
+        <v>1.4</v>
+      </c>
+      <c r="AL125">
+        <v>1.28</v>
+      </c>
+      <c r="AM125">
+        <v>1.6</v>
+      </c>
+      <c r="AN125">
+        <v>1.09</v>
+      </c>
+      <c r="AO125">
+        <v>0.67</v>
+      </c>
+      <c r="AP125">
+        <v>1.25</v>
+      </c>
+      <c r="AQ125">
+        <v>0.62</v>
+      </c>
+      <c r="AR125">
+        <v>1.44</v>
+      </c>
+      <c r="AS125">
+        <v>1.25</v>
+      </c>
+      <c r="AT125">
+        <v>2.69</v>
+      </c>
+      <c r="AU125">
+        <v>8</v>
+      </c>
+      <c r="AV125">
+        <v>3</v>
+      </c>
+      <c r="AW125">
+        <v>7</v>
+      </c>
+      <c r="AX125">
+        <v>1</v>
+      </c>
+      <c r="AY125">
+        <v>15</v>
+      </c>
+      <c r="AZ125">
+        <v>4</v>
+      </c>
+      <c r="BA125">
+        <v>9</v>
+      </c>
+      <c r="BB125">
+        <v>1</v>
+      </c>
+      <c r="BC125">
+        <v>10</v>
+      </c>
+      <c r="BD125">
+        <v>1.86</v>
+      </c>
+      <c r="BE125">
+        <v>6.3</v>
+      </c>
+      <c r="BF125">
+        <v>2.38</v>
+      </c>
+      <c r="BG125">
+        <v>1.21</v>
+      </c>
+      <c r="BH125">
+        <v>3.58</v>
+      </c>
+      <c r="BI125">
+        <v>1.42</v>
+      </c>
+      <c r="BJ125">
+        <v>2.49</v>
+      </c>
+      <c r="BK125">
+        <v>1.75</v>
+      </c>
+      <c r="BL125">
+        <v>1.92</v>
+      </c>
+      <c r="BM125">
+        <v>2.21</v>
+      </c>
+      <c r="BN125">
+        <v>1.53</v>
+      </c>
+      <c r="BO125">
+        <v>2.97</v>
+      </c>
+      <c r="BP125">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -26322,31 +26322,31 @@
         <v>2.74</v>
       </c>
       <c r="AU123">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV123">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AW123">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AX123">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY123">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AZ123">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BA123">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB123">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC123">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD123">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -511,6 +511,9 @@
     <t>['4', '27', '84']</t>
   </si>
   <si>
+    <t>['8', '70', '79']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>['23', '48']</t>
+  </si>
+  <si>
+    <t>['67', '81', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1384,7 +1390,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1587,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3">
         <v>1.92</v>
@@ -1793,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ4">
         <v>0.31</v>
@@ -1921,7 +1927,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2539,7 +2545,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2826,7 +2832,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3032,7 +3038,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3235,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11">
         <v>0.62</v>
@@ -3363,7 +3369,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3647,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ13">
         <v>1.18</v>
@@ -4187,7 +4193,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4268,7 +4274,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR16">
         <v>1.76</v>
@@ -4474,7 +4480,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR17">
         <v>1.21</v>
@@ -4599,7 +4605,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5217,7 +5223,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5423,7 +5429,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5501,7 +5507,7 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ22">
         <v>1.46</v>
@@ -5835,7 +5841,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5913,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24">
         <v>1.58</v>
@@ -6041,7 +6047,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6325,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ26">
         <v>0.58</v>
@@ -6453,7 +6459,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6740,7 +6746,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -6865,7 +6871,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6946,7 +6952,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7277,7 +7283,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7561,7 +7567,7 @@
         <v>1.33</v>
       </c>
       <c r="AP32">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ32">
         <v>1.46</v>
@@ -7770,7 +7776,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8385,10 +8391,10 @@
         <v>1.2</v>
       </c>
       <c r="AP36">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR36">
         <v>1.75</v>
@@ -8513,7 +8519,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8591,10 +8597,10 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ37">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -8925,7 +8931,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9543,7 +9549,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9955,7 +9961,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10161,7 +10167,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10573,7 +10579,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10654,7 +10660,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR47">
         <v>1.05</v>
@@ -10779,7 +10785,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11191,7 +11197,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11475,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51">
         <v>0.31</v>
@@ -11603,7 +11609,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11681,7 +11687,7 @@
         <v>0.2</v>
       </c>
       <c r="AP52">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ52">
         <v>0.62</v>
@@ -12015,7 +12021,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12221,7 +12227,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12427,7 +12433,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12633,7 +12639,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12839,7 +12845,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12920,7 +12926,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ58">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR58">
         <v>1.46</v>
@@ -13045,7 +13051,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13126,7 +13132,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR59">
         <v>1.36</v>
@@ -13251,7 +13257,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13457,7 +13463,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13663,7 +13669,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13869,7 +13875,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13947,7 +13953,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ63">
         <v>1.58</v>
@@ -14075,7 +14081,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14281,7 +14287,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14359,7 +14365,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ65">
         <v>1.18</v>
@@ -14774,7 +14780,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR67">
         <v>1.12</v>
@@ -15105,7 +15111,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15311,7 +15317,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15392,7 +15398,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ70">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR70">
         <v>1.99</v>
@@ -15517,7 +15523,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16341,7 +16347,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16419,7 +16425,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ75">
         <v>0.92</v>
@@ -16547,7 +16553,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16959,7 +16965,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17165,7 +17171,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17243,10 +17249,10 @@
         <v>2.43</v>
       </c>
       <c r="AP79">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR79">
         <v>1.42</v>
@@ -17577,7 +17583,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17783,7 +17789,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18813,7 +18819,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19019,7 +19025,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19100,7 +19106,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ88">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR88">
         <v>1.51</v>
@@ -19225,7 +19231,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19303,10 +19309,10 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19637,7 +19643,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19715,7 +19721,7 @@
         <v>1.88</v>
       </c>
       <c r="AP91">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ91">
         <v>1.92</v>
@@ -19843,7 +19849,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20336,7 +20342,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR94">
         <v>1.81</v>
@@ -20539,7 +20545,7 @@
         <v>0.11</v>
       </c>
       <c r="AP95">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ95">
         <v>0.31</v>
@@ -20667,7 +20673,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20745,7 +20751,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ96">
         <v>1.92</v>
@@ -20954,7 +20960,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR97">
         <v>1.44</v>
@@ -21079,7 +21085,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21285,7 +21291,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21491,7 +21497,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21697,7 +21703,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21778,7 +21784,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ101">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR101">
         <v>1.43</v>
@@ -21903,7 +21909,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22187,7 +22193,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ103">
         <v>1.18</v>
@@ -22599,7 +22605,7 @@
         <v>0.5</v>
       </c>
       <c r="AP105">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ105">
         <v>0.62</v>
@@ -22727,7 +22733,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22808,7 +22814,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR106">
         <v>1.46</v>
@@ -22933,7 +22939,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23345,7 +23351,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23757,7 +23763,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -23835,7 +23841,7 @@
         <v>1.6</v>
       </c>
       <c r="AP111">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ111">
         <v>1.58</v>
@@ -24375,7 +24381,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24453,7 +24459,7 @@
         <v>1.64</v>
       </c>
       <c r="AP114">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ114">
         <v>1.46</v>
@@ -24581,7 +24587,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24787,7 +24793,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24868,7 +24874,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ116">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR116">
         <v>1.46</v>
@@ -24993,7 +24999,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25277,7 +25283,7 @@
         <v>0.64</v>
       </c>
       <c r="AP118">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ118">
         <v>0.58</v>
@@ -25405,7 +25411,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25692,7 +25698,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ120">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR120">
         <v>1.91</v>
@@ -25817,7 +25823,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -25898,7 +25904,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR121">
         <v>2.13</v>
@@ -26101,7 +26107,7 @@
         <v>1.58</v>
       </c>
       <c r="AP122">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ122">
         <v>1.46</v>
@@ -26229,7 +26235,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26641,7 +26647,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -26798,6 +26804,418 @@
       </c>
       <c r="BP125">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7483801</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F126">
+        <v>26</v>
+      </c>
+      <c r="G126" t="s">
+        <v>72</v>
+      </c>
+      <c r="H126" t="s">
+        <v>79</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>3</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>4</v>
+      </c>
+      <c r="O126" t="s">
+        <v>165</v>
+      </c>
+      <c r="P126" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126">
+        <v>0</v>
+      </c>
+      <c r="V126">
+        <v>0</v>
+      </c>
+      <c r="W126">
+        <v>0</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
+      </c>
+      <c r="Z126">
+        <v>2.03</v>
+      </c>
+      <c r="AA126">
+        <v>3.19</v>
+      </c>
+      <c r="AB126">
+        <v>3.79</v>
+      </c>
+      <c r="AC126">
+        <v>0</v>
+      </c>
+      <c r="AD126">
+        <v>0</v>
+      </c>
+      <c r="AE126">
+        <v>0</v>
+      </c>
+      <c r="AF126">
+        <v>0</v>
+      </c>
+      <c r="AG126">
+        <v>2.25</v>
+      </c>
+      <c r="AH126">
+        <v>1.53</v>
+      </c>
+      <c r="AI126">
+        <v>0</v>
+      </c>
+      <c r="AJ126">
+        <v>0</v>
+      </c>
+      <c r="AK126">
+        <v>0</v>
+      </c>
+      <c r="AL126">
+        <v>0</v>
+      </c>
+      <c r="AM126">
+        <v>0</v>
+      </c>
+      <c r="AN126">
+        <v>1.46</v>
+      </c>
+      <c r="AO126">
+        <v>1</v>
+      </c>
+      <c r="AP126">
+        <v>1.57</v>
+      </c>
+      <c r="AQ126">
+        <v>0.93</v>
+      </c>
+      <c r="AR126">
+        <v>1.52</v>
+      </c>
+      <c r="AS126">
+        <v>1.26</v>
+      </c>
+      <c r="AT126">
+        <v>2.78</v>
+      </c>
+      <c r="AU126">
+        <v>-1</v>
+      </c>
+      <c r="AV126">
+        <v>-1</v>
+      </c>
+      <c r="AW126">
+        <v>-1</v>
+      </c>
+      <c r="AX126">
+        <v>-1</v>
+      </c>
+      <c r="AY126">
+        <v>-1</v>
+      </c>
+      <c r="AZ126">
+        <v>-1</v>
+      </c>
+      <c r="BA126">
+        <v>-1</v>
+      </c>
+      <c r="BB126">
+        <v>-1</v>
+      </c>
+      <c r="BC126">
+        <v>-1</v>
+      </c>
+      <c r="BD126">
+        <v>0</v>
+      </c>
+      <c r="BE126">
+        <v>0</v>
+      </c>
+      <c r="BF126">
+        <v>0</v>
+      </c>
+      <c r="BG126">
+        <v>0</v>
+      </c>
+      <c r="BH126">
+        <v>0</v>
+      </c>
+      <c r="BI126">
+        <v>0</v>
+      </c>
+      <c r="BJ126">
+        <v>0</v>
+      </c>
+      <c r="BK126">
+        <v>0</v>
+      </c>
+      <c r="BL126">
+        <v>0</v>
+      </c>
+      <c r="BM126">
+        <v>0</v>
+      </c>
+      <c r="BN126">
+        <v>0</v>
+      </c>
+      <c r="BO126">
+        <v>0</v>
+      </c>
+      <c r="BP126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7483802</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45731.5625</v>
+      </c>
+      <c r="F127">
+        <v>26</v>
+      </c>
+      <c r="G127" t="s">
+        <v>71</v>
+      </c>
+      <c r="H127" t="s">
+        <v>70</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>3</v>
+      </c>
+      <c r="N127">
+        <v>3</v>
+      </c>
+      <c r="O127" t="s">
+        <v>81</v>
+      </c>
+      <c r="P127" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q127">
+        <v>6.5</v>
+      </c>
+      <c r="R127">
+        <v>2.2</v>
+      </c>
+      <c r="S127">
+        <v>2</v>
+      </c>
+      <c r="T127">
+        <v>1.4</v>
+      </c>
+      <c r="U127">
+        <v>2.75</v>
+      </c>
+      <c r="V127">
+        <v>2.75</v>
+      </c>
+      <c r="W127">
+        <v>1.4</v>
+      </c>
+      <c r="X127">
+        <v>7</v>
+      </c>
+      <c r="Y127">
+        <v>1.08</v>
+      </c>
+      <c r="Z127">
+        <v>6.7</v>
+      </c>
+      <c r="AA127">
+        <v>4.2</v>
+      </c>
+      <c r="AB127">
+        <v>1.46</v>
+      </c>
+      <c r="AC127">
+        <v>1.04</v>
+      </c>
+      <c r="AD127">
+        <v>9</v>
+      </c>
+      <c r="AE127">
+        <v>1.25</v>
+      </c>
+      <c r="AF127">
+        <v>3.65</v>
+      </c>
+      <c r="AG127">
+        <v>1.91</v>
+      </c>
+      <c r="AH127">
+        <v>1.83</v>
+      </c>
+      <c r="AI127">
+        <v>2.1</v>
+      </c>
+      <c r="AJ127">
+        <v>1.67</v>
+      </c>
+      <c r="AK127">
+        <v>2.6</v>
+      </c>
+      <c r="AL127">
+        <v>1.2</v>
+      </c>
+      <c r="AM127">
+        <v>1.11</v>
+      </c>
+      <c r="AN127">
+        <v>1.38</v>
+      </c>
+      <c r="AO127">
+        <v>2</v>
+      </c>
+      <c r="AP127">
+        <v>1.29</v>
+      </c>
+      <c r="AQ127">
+        <v>2.08</v>
+      </c>
+      <c r="AR127">
+        <v>1.33</v>
+      </c>
+      <c r="AS127">
+        <v>1.7</v>
+      </c>
+      <c r="AT127">
+        <v>3.03</v>
+      </c>
+      <c r="AU127">
+        <v>4</v>
+      </c>
+      <c r="AV127">
+        <v>15</v>
+      </c>
+      <c r="AW127">
+        <v>2</v>
+      </c>
+      <c r="AX127">
+        <v>11</v>
+      </c>
+      <c r="AY127">
+        <v>6</v>
+      </c>
+      <c r="AZ127">
+        <v>26</v>
+      </c>
+      <c r="BA127">
+        <v>4</v>
+      </c>
+      <c r="BB127">
+        <v>11</v>
+      </c>
+      <c r="BC127">
+        <v>15</v>
+      </c>
+      <c r="BD127">
+        <v>5.05</v>
+      </c>
+      <c r="BE127">
+        <v>10</v>
+      </c>
+      <c r="BF127">
+        <v>1.22</v>
+      </c>
+      <c r="BG127">
+        <v>1.31</v>
+      </c>
+      <c r="BH127">
+        <v>2.92</v>
+      </c>
+      <c r="BI127">
+        <v>1.57</v>
+      </c>
+      <c r="BJ127">
+        <v>2.14</v>
+      </c>
+      <c r="BK127">
+        <v>2</v>
+      </c>
+      <c r="BL127">
+        <v>1.69</v>
+      </c>
+      <c r="BM127">
+        <v>2.59</v>
+      </c>
+      <c r="BN127">
+        <v>1.39</v>
+      </c>
+      <c r="BO127">
+        <v>3.58</v>
+      </c>
+      <c r="BP127">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="230">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -514,6 +514,12 @@
     <t>['8', '70', '79']</t>
   </si>
   <si>
+    <t>['14', '20', '82']</t>
+  </si>
+  <si>
+    <t>['16', '66', '76', '83']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -692,6 +698,12 @@
   </si>
   <si>
     <t>['67', '81', '90+4']</t>
+  </si>
+  <si>
+    <t>['31', '33', '50']</t>
+  </si>
+  <si>
+    <t>['6', '19']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1596,7 +1608,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ3">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1927,7 +1939,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2005,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ5">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2545,7 +2557,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3035,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
         <v>0.93</v>
@@ -3244,7 +3256,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ11">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR11">
         <v>1.27</v>
@@ -3369,7 +3381,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3450,7 +3462,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ12">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3859,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ14">
         <v>1.46</v>
@@ -4193,7 +4205,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4605,7 +4617,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4889,7 +4901,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ19">
         <v>0.92</v>
@@ -5095,10 +5107,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5223,7 +5235,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5304,7 +5316,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ21">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR21">
         <v>1.05</v>
@@ -5429,7 +5441,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5841,7 +5853,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6047,7 +6059,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6459,7 +6471,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6540,7 +6552,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ27">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR27">
         <v>0.98</v>
@@ -6743,7 +6755,7 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ28">
         <v>2.08</v>
@@ -6871,7 +6883,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7155,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>0.31</v>
@@ -7283,7 +7295,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7364,7 +7376,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ31">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR31">
         <v>1.26</v>
@@ -7773,7 +7785,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ33">
         <v>0.93</v>
@@ -8519,7 +8531,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8803,10 +8815,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR38">
         <v>1.19</v>
@@ -8931,7 +8943,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9215,10 +9227,10 @@
         <v>2.25</v>
       </c>
       <c r="AP40">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ40">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9549,7 +9561,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9961,7 +9973,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10167,7 +10179,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10579,7 +10591,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10785,7 +10797,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10863,7 +10875,7 @@
         <v>1.25</v>
       </c>
       <c r="AP48">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>1.18</v>
@@ -11197,7 +11209,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11609,7 +11621,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11690,7 +11702,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ52">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -12021,7 +12033,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12099,7 +12111,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ54">
         <v>1.18</v>
@@ -12227,7 +12239,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12308,7 +12320,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ55">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR55">
         <v>1.92</v>
@@ -12433,7 +12445,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12639,7 +12651,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12845,7 +12857,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13051,7 +13063,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13257,7 +13269,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13335,7 +13347,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>1.58</v>
@@ -13463,7 +13475,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13669,7 +13681,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13875,7 +13887,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14081,7 +14093,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14287,7 +14299,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14574,7 +14586,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ66">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR66">
         <v>1.87</v>
@@ -14983,7 +14995,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ68">
         <v>0.58</v>
@@ -15111,7 +15123,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15189,7 +15201,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>0.92</v>
@@ -15317,7 +15329,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15523,7 +15535,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15604,7 +15616,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ71">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -15810,7 +15822,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ72">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR72">
         <v>1.36</v>
@@ -16347,7 +16359,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16553,7 +16565,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16840,7 +16852,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ77">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR77">
         <v>2</v>
@@ -16965,7 +16977,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17171,7 +17183,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17583,7 +17595,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17789,7 +17801,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18691,7 +18703,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ86">
         <v>0.58</v>
@@ -18819,7 +18831,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18900,7 +18912,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ87">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19025,7 +19037,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19103,7 +19115,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>2.08</v>
@@ -19231,7 +19243,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19515,7 +19527,7 @@
         <v>0.13</v>
       </c>
       <c r="AP90">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ90">
         <v>0.31</v>
@@ -19643,7 +19655,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19724,7 +19736,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ91">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR91">
         <v>1.34</v>
@@ -19849,7 +19861,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20133,10 +20145,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP93">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ93">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20673,7 +20685,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20754,7 +20766,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ96">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -20957,7 +20969,7 @@
         <v>1.1</v>
       </c>
       <c r="AP97">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>0.93</v>
@@ -21085,7 +21097,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21291,7 +21303,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21497,7 +21509,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21703,7 +21715,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21909,7 +21921,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -21987,7 +21999,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ102">
         <v>1.46</v>
@@ -22608,7 +22620,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ105">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -22733,7 +22745,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22939,7 +22951,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23017,10 +23029,10 @@
         <v>2.1</v>
       </c>
       <c r="AP107">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23223,7 +23235,7 @@
         <v>1.1</v>
       </c>
       <c r="AP108">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ108">
         <v>0.92</v>
@@ -23351,7 +23363,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23638,7 +23650,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR110">
         <v>1.09</v>
@@ -23763,7 +23775,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24381,7 +24393,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24587,7 +24599,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24668,7 +24680,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ115">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR115">
         <v>1.09</v>
@@ -24793,7 +24805,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24999,7 +25011,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25077,7 +25089,7 @@
         <v>0.25</v>
       </c>
       <c r="AP117">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>0.31</v>
@@ -25411,7 +25423,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25492,7 +25504,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ119">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR119">
         <v>1.44</v>
@@ -25695,7 +25707,7 @@
         <v>2.18</v>
       </c>
       <c r="AP120">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ120">
         <v>2.08</v>
@@ -25823,7 +25835,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26235,7 +26247,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26647,7 +26659,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -26728,7 +26740,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ125">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR125">
         <v>1.44</v>
@@ -27059,7 +27071,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27216,6 +27228,418 @@
       </c>
       <c r="BP127">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7483798</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F128">
+        <v>26</v>
+      </c>
+      <c r="G128" t="s">
+        <v>78</v>
+      </c>
+      <c r="H128" t="s">
+        <v>76</v>
+      </c>
+      <c r="I128">
+        <v>2</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128">
+        <v>4</v>
+      </c>
+      <c r="L128">
+        <v>3</v>
+      </c>
+      <c r="M128">
+        <v>3</v>
+      </c>
+      <c r="N128">
+        <v>6</v>
+      </c>
+      <c r="O128" t="s">
+        <v>166</v>
+      </c>
+      <c r="P128" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q128">
+        <v>2.2</v>
+      </c>
+      <c r="R128">
+        <v>2.15</v>
+      </c>
+      <c r="S128">
+        <v>5</v>
+      </c>
+      <c r="T128">
+        <v>1.38</v>
+      </c>
+      <c r="U128">
+        <v>2.8</v>
+      </c>
+      <c r="V128">
+        <v>2.8</v>
+      </c>
+      <c r="W128">
+        <v>1.38</v>
+      </c>
+      <c r="X128">
+        <v>6.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.07</v>
+      </c>
+      <c r="Z128">
+        <v>1.58</v>
+      </c>
+      <c r="AA128">
+        <v>3.89</v>
+      </c>
+      <c r="AB128">
+        <v>5.6</v>
+      </c>
+      <c r="AC128">
+        <v>1.05</v>
+      </c>
+      <c r="AD128">
+        <v>8.5</v>
+      </c>
+      <c r="AE128">
+        <v>1.3</v>
+      </c>
+      <c r="AF128">
+        <v>3.25</v>
+      </c>
+      <c r="AG128">
+        <v>1.95</v>
+      </c>
+      <c r="AH128">
+        <v>1.79</v>
+      </c>
+      <c r="AI128">
+        <v>1.85</v>
+      </c>
+      <c r="AJ128">
+        <v>1.77</v>
+      </c>
+      <c r="AK128">
+        <v>1.13</v>
+      </c>
+      <c r="AL128">
+        <v>1.22</v>
+      </c>
+      <c r="AM128">
+        <v>2.1</v>
+      </c>
+      <c r="AN128">
+        <v>2.08</v>
+      </c>
+      <c r="AO128">
+        <v>0.62</v>
+      </c>
+      <c r="AP128">
+        <v>2</v>
+      </c>
+      <c r="AQ128">
+        <v>0.64</v>
+      </c>
+      <c r="AR128">
+        <v>1.54</v>
+      </c>
+      <c r="AS128">
+        <v>1.21</v>
+      </c>
+      <c r="AT128">
+        <v>2.75</v>
+      </c>
+      <c r="AU128">
+        <v>11</v>
+      </c>
+      <c r="AV128">
+        <v>7</v>
+      </c>
+      <c r="AW128">
+        <v>9</v>
+      </c>
+      <c r="AX128">
+        <v>5</v>
+      </c>
+      <c r="AY128">
+        <v>20</v>
+      </c>
+      <c r="AZ128">
+        <v>12</v>
+      </c>
+      <c r="BA128">
+        <v>12</v>
+      </c>
+      <c r="BB128">
+        <v>3</v>
+      </c>
+      <c r="BC128">
+        <v>15</v>
+      </c>
+      <c r="BD128">
+        <v>1.34</v>
+      </c>
+      <c r="BE128">
+        <v>7.3</v>
+      </c>
+      <c r="BF128">
+        <v>4.25</v>
+      </c>
+      <c r="BG128">
+        <v>1.29</v>
+      </c>
+      <c r="BH128">
+        <v>3.3</v>
+      </c>
+      <c r="BI128">
+        <v>1.5</v>
+      </c>
+      <c r="BJ128">
+        <v>2.51</v>
+      </c>
+      <c r="BK128">
+        <v>1.79</v>
+      </c>
+      <c r="BL128">
+        <v>1.87</v>
+      </c>
+      <c r="BM128">
+        <v>2.33</v>
+      </c>
+      <c r="BN128">
+        <v>1.57</v>
+      </c>
+      <c r="BO128">
+        <v>3.1</v>
+      </c>
+      <c r="BP128">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7483800</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45732.5625</v>
+      </c>
+      <c r="F129">
+        <v>26</v>
+      </c>
+      <c r="G129" t="s">
+        <v>73</v>
+      </c>
+      <c r="H129" t="s">
+        <v>77</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>2</v>
+      </c>
+      <c r="K129">
+        <v>3</v>
+      </c>
+      <c r="L129">
+        <v>4</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>6</v>
+      </c>
+      <c r="O129" t="s">
+        <v>167</v>
+      </c>
+      <c r="P129" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q129">
+        <v>2.2</v>
+      </c>
+      <c r="R129">
+        <v>2.1</v>
+      </c>
+      <c r="S129">
+        <v>5</v>
+      </c>
+      <c r="T129">
+        <v>1.4</v>
+      </c>
+      <c r="U129">
+        <v>2.75</v>
+      </c>
+      <c r="V129">
+        <v>3</v>
+      </c>
+      <c r="W129">
+        <v>1.36</v>
+      </c>
+      <c r="X129">
+        <v>7</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
+        <v>1.63</v>
+      </c>
+      <c r="AA129">
+        <v>3.81</v>
+      </c>
+      <c r="AB129">
+        <v>5.2</v>
+      </c>
+      <c r="AC129">
+        <v>1.05</v>
+      </c>
+      <c r="AD129">
+        <v>8.5</v>
+      </c>
+      <c r="AE129">
+        <v>1.28</v>
+      </c>
+      <c r="AF129">
+        <v>3.5</v>
+      </c>
+      <c r="AG129">
+        <v>1.92</v>
+      </c>
+      <c r="AH129">
+        <v>1.82</v>
+      </c>
+      <c r="AI129">
+        <v>2</v>
+      </c>
+      <c r="AJ129">
+        <v>1.73</v>
+      </c>
+      <c r="AK129">
+        <v>1.16</v>
+      </c>
+      <c r="AL129">
+        <v>1.24</v>
+      </c>
+      <c r="AM129">
+        <v>2.2</v>
+      </c>
+      <c r="AN129">
+        <v>2.23</v>
+      </c>
+      <c r="AO129">
+        <v>1.92</v>
+      </c>
+      <c r="AP129">
+        <v>2.29</v>
+      </c>
+      <c r="AQ129">
+        <v>1.79</v>
+      </c>
+      <c r="AR129">
+        <v>1.87</v>
+      </c>
+      <c r="AS129">
+        <v>1.48</v>
+      </c>
+      <c r="AT129">
+        <v>3.35</v>
+      </c>
+      <c r="AU129">
+        <v>9</v>
+      </c>
+      <c r="AV129">
+        <v>6</v>
+      </c>
+      <c r="AW129">
+        <v>6</v>
+      </c>
+      <c r="AX129">
+        <v>9</v>
+      </c>
+      <c r="AY129">
+        <v>15</v>
+      </c>
+      <c r="AZ129">
+        <v>15</v>
+      </c>
+      <c r="BA129">
+        <v>7</v>
+      </c>
+      <c r="BB129">
+        <v>4</v>
+      </c>
+      <c r="BC129">
+        <v>11</v>
+      </c>
+      <c r="BD129">
+        <v>1.49</v>
+      </c>
+      <c r="BE129">
+        <v>8.1</v>
+      </c>
+      <c r="BF129">
+        <v>3.1</v>
+      </c>
+      <c r="BG129">
+        <v>1.51</v>
+      </c>
+      <c r="BH129">
+        <v>2.44</v>
+      </c>
+      <c r="BI129">
+        <v>1.83</v>
+      </c>
+      <c r="BJ129">
+        <v>1.83</v>
+      </c>
+      <c r="BK129">
+        <v>2.37</v>
+      </c>
+      <c r="BL129">
+        <v>1.54</v>
+      </c>
+      <c r="BM129">
+        <v>3</v>
+      </c>
+      <c r="BN129">
+        <v>1.33</v>
+      </c>
+      <c r="BO129">
+        <v>4</v>
+      </c>
+      <c r="BP129">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,9 @@
     <t>['16', '66', '76', '83']</t>
   </si>
   <si>
+    <t>['40', '87', '90+3']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -704,6 +707,9 @@
   </si>
   <si>
     <t>['6', '19']</t>
+  </si>
+  <si>
+    <t>['59', '68']</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP129"/>
+  <dimension ref="A1:BP130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1814,7 +1820,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ4">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1939,7 +1945,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2223,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
         <v>1.46</v>
@@ -2557,7 +2563,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3381,7 +3387,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4080,7 +4086,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ15">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR15">
         <v>1.3</v>
@@ -4205,7 +4211,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4617,7 +4623,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4695,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18">
         <v>0.58</v>
@@ -5235,7 +5241,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5441,7 +5447,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5728,7 +5734,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ23">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR23">
         <v>0.7</v>
@@ -5853,7 +5859,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6059,7 +6065,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6471,7 +6477,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6883,7 +6889,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6961,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ29">
         <v>0.93</v>
@@ -7170,7 +7176,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR30">
         <v>1.03</v>
@@ -7295,7 +7301,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -8531,7 +8537,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8943,7 +8949,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9021,10 +9027,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ39">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR39">
         <v>2.18</v>
@@ -9433,7 +9439,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ41">
         <v>1.58</v>
@@ -9561,7 +9567,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9973,7 +9979,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10179,7 +10185,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10591,7 +10597,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10797,7 +10803,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11209,7 +11215,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11496,7 +11502,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ51">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR51">
         <v>1.32</v>
@@ -11621,7 +11627,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -12033,7 +12039,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12239,7 +12245,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12445,7 +12451,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12651,7 +12657,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12729,7 +12735,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ57">
         <v>0.92</v>
@@ -12857,7 +12863,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13063,7 +13069,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13269,7 +13275,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13475,7 +13481,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13681,7 +13687,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13762,7 +13768,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ62">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -13887,7 +13893,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14093,7 +14099,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14299,7 +14305,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -15123,7 +15129,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15329,7 +15335,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15407,7 +15413,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ70">
         <v>2.08</v>
@@ -15535,7 +15541,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16359,7 +16365,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16565,7 +16571,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16849,7 +16855,7 @@
         <v>2.14</v>
       </c>
       <c r="AP77">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ77">
         <v>1.79</v>
@@ -16977,7 +16983,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17058,7 +17064,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ78">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR78">
         <v>1.13</v>
@@ -17183,7 +17189,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17595,7 +17601,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17801,7 +17807,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18831,7 +18837,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18909,7 +18915,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ87">
         <v>0.64</v>
@@ -19037,7 +19043,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19243,7 +19249,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19530,7 +19536,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ90">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR90">
         <v>1.64</v>
@@ -19655,7 +19661,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19861,7 +19867,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19939,7 +19945,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ92">
         <v>1.46</v>
@@ -20560,7 +20566,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ95">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -20685,7 +20691,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21097,7 +21103,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21303,7 +21309,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21509,7 +21515,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21587,7 +21593,7 @@
         <v>1.44</v>
       </c>
       <c r="AP100">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ100">
         <v>1.58</v>
@@ -21715,7 +21721,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21921,7 +21927,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22414,7 +22420,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ104">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR104">
         <v>1.82</v>
@@ -22745,7 +22751,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22951,7 +22957,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23363,7 +23369,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23441,7 +23447,7 @@
         <v>0.7</v>
       </c>
       <c r="AP109">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ109">
         <v>0.58</v>
@@ -23775,7 +23781,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24062,7 +24068,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ112">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR112">
         <v>1.41</v>
@@ -24393,7 +24399,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24599,7 +24605,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24805,7 +24811,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -25011,7 +25017,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25092,7 +25098,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR117">
         <v>1.5</v>
@@ -25423,7 +25429,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25835,7 +25841,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -25913,7 +25919,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ121">
         <v>0.93</v>
@@ -26247,7 +26253,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26659,7 +26665,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -26958,31 +26964,31 @@
         <v>2.78</v>
       </c>
       <c r="AU126">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV126">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW126">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AX126">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY126">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AZ126">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA126">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB126">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC126">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD126">
         <v>0</v>
@@ -27071,7 +27077,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27277,7 +27283,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27483,7 +27489,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27640,6 +27646,212 @@
       </c>
       <c r="BP129">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7483799</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45732.67708333334</v>
+      </c>
+      <c r="F130">
+        <v>26</v>
+      </c>
+      <c r="G130" t="s">
+        <v>74</v>
+      </c>
+      <c r="H130" t="s">
+        <v>75</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>3</v>
+      </c>
+      <c r="M130">
+        <v>2</v>
+      </c>
+      <c r="N130">
+        <v>5</v>
+      </c>
+      <c r="O130" t="s">
+        <v>168</v>
+      </c>
+      <c r="P130" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q130">
+        <v>1.8</v>
+      </c>
+      <c r="R130">
+        <v>2.5</v>
+      </c>
+      <c r="S130">
+        <v>6.5</v>
+      </c>
+      <c r="T130">
+        <v>1.3</v>
+      </c>
+      <c r="U130">
+        <v>3.4</v>
+      </c>
+      <c r="V130">
+        <v>2.38</v>
+      </c>
+      <c r="W130">
+        <v>1.53</v>
+      </c>
+      <c r="X130">
+        <v>5.5</v>
+      </c>
+      <c r="Y130">
+        <v>1.13</v>
+      </c>
+      <c r="Z130">
+        <v>1.37</v>
+      </c>
+      <c r="AA130">
+        <v>4.7</v>
+      </c>
+      <c r="AB130">
+        <v>8.1</v>
+      </c>
+      <c r="AC130">
+        <v>1.03</v>
+      </c>
+      <c r="AD130">
+        <v>10</v>
+      </c>
+      <c r="AE130">
+        <v>1.18</v>
+      </c>
+      <c r="AF130">
+        <v>4.5</v>
+      </c>
+      <c r="AG130">
+        <v>1.6</v>
+      </c>
+      <c r="AH130">
+        <v>2.15</v>
+      </c>
+      <c r="AI130">
+        <v>1.91</v>
+      </c>
+      <c r="AJ130">
+        <v>1.8</v>
+      </c>
+      <c r="AK130">
+        <v>1.09</v>
+      </c>
+      <c r="AL130">
+        <v>1.16</v>
+      </c>
+      <c r="AM130">
+        <v>3</v>
+      </c>
+      <c r="AN130">
+        <v>1.77</v>
+      </c>
+      <c r="AO130">
+        <v>0.31</v>
+      </c>
+      <c r="AP130">
+        <v>1.86</v>
+      </c>
+      <c r="AQ130">
+        <v>0.29</v>
+      </c>
+      <c r="AR130">
+        <v>2.1</v>
+      </c>
+      <c r="AS130">
+        <v>1.24</v>
+      </c>
+      <c r="AT130">
+        <v>3.34</v>
+      </c>
+      <c r="AU130">
+        <v>6</v>
+      </c>
+      <c r="AV130">
+        <v>5</v>
+      </c>
+      <c r="AW130">
+        <v>8</v>
+      </c>
+      <c r="AX130">
+        <v>4</v>
+      </c>
+      <c r="AY130">
+        <v>14</v>
+      </c>
+      <c r="AZ130">
+        <v>9</v>
+      </c>
+      <c r="BA130">
+        <v>4</v>
+      </c>
+      <c r="BB130">
+        <v>1</v>
+      </c>
+      <c r="BC130">
+        <v>5</v>
+      </c>
+      <c r="BD130">
+        <v>1.22</v>
+      </c>
+      <c r="BE130">
+        <v>10.75</v>
+      </c>
+      <c r="BF130">
+        <v>4.9</v>
+      </c>
+      <c r="BG130">
+        <v>1.17</v>
+      </c>
+      <c r="BH130">
+        <v>4.15</v>
+      </c>
+      <c r="BI130">
+        <v>1.36</v>
+      </c>
+      <c r="BJ130">
+        <v>2.92</v>
+      </c>
+      <c r="BK130">
+        <v>1.6</v>
+      </c>
+      <c r="BL130">
+        <v>2.25</v>
+      </c>
+      <c r="BM130">
+        <v>2</v>
+      </c>
+      <c r="BN130">
+        <v>1.8</v>
+      </c>
+      <c r="BO130">
+        <v>2.45</v>
+      </c>
+      <c r="BP130">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -521,6 +521,9 @@
   </si>
   <si>
     <t>['40', '87', '90+3']</t>
+  </si>
+  <si>
+    <t>['41']</t>
   </si>
   <si>
     <t>['83']</t>
@@ -1071,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP130"/>
+  <dimension ref="A1:BP132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1945,7 +1948,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2563,7 +2566,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2641,10 +2644,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ8">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2847,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9">
         <v>2.08</v>
@@ -3387,7 +3390,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3674,7 +3677,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ13">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>1.72</v>
@@ -4211,7 +4214,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4495,7 +4498,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ17">
         <v>2.08</v>
@@ -4623,7 +4626,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4910,7 +4913,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ19">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR19">
         <v>1.75</v>
@@ -5241,7 +5244,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5447,7 +5450,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5731,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ23">
         <v>0.29</v>
@@ -5859,7 +5862,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6065,7 +6068,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6146,7 +6149,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ25">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>1.83</v>
@@ -6477,7 +6480,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6555,7 +6558,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ27">
         <v>1.79</v>
@@ -6889,7 +6892,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7301,7 +7304,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7997,10 +8000,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ34">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -8206,7 +8209,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ35">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR35">
         <v>2.01</v>
@@ -8537,7 +8540,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8949,7 +8952,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9567,7 +9570,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9851,10 +9854,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ43">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR43">
         <v>1.26</v>
@@ -9979,7 +9982,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10185,7 +10188,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10263,10 +10266,10 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ45">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR45">
         <v>1.07</v>
@@ -10472,7 +10475,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ46">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR46">
         <v>1.5</v>
@@ -10597,7 +10600,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10803,7 +10806,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10884,7 +10887,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.28</v>
@@ -11087,7 +11090,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ49">
         <v>0.58</v>
@@ -11215,7 +11218,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11293,7 +11296,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ50">
         <v>1.58</v>
@@ -11627,7 +11630,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -12039,7 +12042,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12120,7 +12123,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12245,7 +12248,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12451,7 +12454,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12657,7 +12660,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12738,7 +12741,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ57">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR57">
         <v>2.09</v>
@@ -12863,7 +12866,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13069,7 +13072,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13147,7 +13150,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ59">
         <v>0.93</v>
@@ -13275,7 +13278,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13481,7 +13484,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13559,7 +13562,7 @@
         <v>0.6</v>
       </c>
       <c r="AP61">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ61">
         <v>0.58</v>
@@ -13687,7 +13690,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13893,7 +13896,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14099,7 +14102,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14177,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ64">
         <v>1.46</v>
@@ -14305,7 +14308,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14386,7 +14389,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ65">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14795,7 +14798,7 @@
         <v>1.29</v>
       </c>
       <c r="AP67">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ67">
         <v>0.93</v>
@@ -15129,7 +15132,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15210,7 +15213,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -15335,7 +15338,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15541,7 +15544,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15825,7 +15828,7 @@
         <v>0.57</v>
       </c>
       <c r="AP72">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ72">
         <v>0.64</v>
@@ -16365,7 +16368,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16446,7 +16449,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ75">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR75">
         <v>1.44</v>
@@ -16571,7 +16574,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16652,7 +16655,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ76">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
         <v>1.07</v>
@@ -16983,7 +16986,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17061,7 +17064,7 @@
         <v>0.14</v>
       </c>
       <c r="AP78">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ78">
         <v>0.29</v>
@@ -17189,7 +17192,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17601,7 +17604,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17679,7 +17682,7 @@
         <v>1.13</v>
       </c>
       <c r="AP81">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ81">
         <v>1.46</v>
@@ -17807,7 +17810,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -17885,7 +17888,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ82">
         <v>1.58</v>
@@ -18094,7 +18097,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ83">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR83">
         <v>1.05</v>
@@ -18300,7 +18303,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ84">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR84">
         <v>1.41</v>
@@ -18837,7 +18840,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19043,7 +19046,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19249,7 +19252,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19661,7 +19664,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19867,7 +19870,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20691,7 +20694,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21103,7 +21106,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21309,7 +21312,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21387,10 +21390,10 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ99">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21515,7 +21518,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21721,7 +21724,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21799,7 +21802,7 @@
         <v>2.33</v>
       </c>
       <c r="AP101">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ101">
         <v>2.08</v>
@@ -21927,7 +21930,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22214,7 +22217,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ103">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22751,7 +22754,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22957,7 +22960,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23244,7 +23247,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ108">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR108">
         <v>1.88</v>
@@ -23369,7 +23372,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23781,7 +23784,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24065,7 +24068,7 @@
         <v>0.18</v>
       </c>
       <c r="AP112">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ112">
         <v>0.29</v>
@@ -24274,7 +24277,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ113">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR113">
         <v>1.82</v>
@@ -24399,7 +24402,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24605,7 +24608,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24811,7 +24814,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24889,7 +24892,7 @@
         <v>2.4</v>
       </c>
       <c r="AP116">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ116">
         <v>2.08</v>
@@ -25017,7 +25020,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25429,7 +25432,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25507,7 +25510,7 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ119">
         <v>1.79</v>
@@ -25841,7 +25844,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26253,7 +26256,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26540,7 +26543,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -26665,7 +26668,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -27077,7 +27080,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27283,7 +27286,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27489,7 +27492,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27695,7 +27698,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q130">
         <v>1.8</v>
@@ -27852,6 +27855,418 @@
       </c>
       <c r="BP130">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7483805</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45745.5625</v>
+      </c>
+      <c r="F131">
+        <v>27</v>
+      </c>
+      <c r="G131" t="s">
+        <v>77</v>
+      </c>
+      <c r="H131" t="s">
+        <v>72</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>1</v>
+      </c>
+      <c r="O131" t="s">
+        <v>169</v>
+      </c>
+      <c r="P131" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q131">
+        <v>2.63</v>
+      </c>
+      <c r="R131">
+        <v>2.05</v>
+      </c>
+      <c r="S131">
+        <v>4</v>
+      </c>
+      <c r="T131">
+        <v>1.44</v>
+      </c>
+      <c r="U131">
+        <v>2.63</v>
+      </c>
+      <c r="V131">
+        <v>3.25</v>
+      </c>
+      <c r="W131">
+        <v>1.33</v>
+      </c>
+      <c r="X131">
+        <v>8</v>
+      </c>
+      <c r="Y131">
+        <v>1.06</v>
+      </c>
+      <c r="Z131">
+        <v>1.99</v>
+      </c>
+      <c r="AA131">
+        <v>3.32</v>
+      </c>
+      <c r="AB131">
+        <v>3.76</v>
+      </c>
+      <c r="AC131">
+        <v>0</v>
+      </c>
+      <c r="AD131">
+        <v>0</v>
+      </c>
+      <c r="AE131">
+        <v>1.77</v>
+      </c>
+      <c r="AF131">
+        <v>2.02</v>
+      </c>
+      <c r="AG131">
+        <v>2</v>
+      </c>
+      <c r="AH131">
+        <v>1.67</v>
+      </c>
+      <c r="AI131">
+        <v>1.91</v>
+      </c>
+      <c r="AJ131">
+        <v>1.8</v>
+      </c>
+      <c r="AK131">
+        <v>0</v>
+      </c>
+      <c r="AL131">
+        <v>0</v>
+      </c>
+      <c r="AM131">
+        <v>0</v>
+      </c>
+      <c r="AN131">
+        <v>1.45</v>
+      </c>
+      <c r="AO131">
+        <v>0.92</v>
+      </c>
+      <c r="AP131">
+        <v>1.58</v>
+      </c>
+      <c r="AQ131">
+        <v>0.85</v>
+      </c>
+      <c r="AR131">
+        <v>1.5</v>
+      </c>
+      <c r="AS131">
+        <v>1.26</v>
+      </c>
+      <c r="AT131">
+        <v>2.76</v>
+      </c>
+      <c r="AU131">
+        <v>6</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>8</v>
+      </c>
+      <c r="AX131">
+        <v>4</v>
+      </c>
+      <c r="AY131">
+        <v>14</v>
+      </c>
+      <c r="AZ131">
+        <v>8</v>
+      </c>
+      <c r="BA131">
+        <v>3</v>
+      </c>
+      <c r="BB131">
+        <v>7</v>
+      </c>
+      <c r="BC131">
+        <v>10</v>
+      </c>
+      <c r="BD131">
+        <v>0</v>
+      </c>
+      <c r="BE131">
+        <v>0</v>
+      </c>
+      <c r="BF131">
+        <v>0</v>
+      </c>
+      <c r="BG131">
+        <v>0</v>
+      </c>
+      <c r="BH131">
+        <v>0</v>
+      </c>
+      <c r="BI131">
+        <v>0</v>
+      </c>
+      <c r="BJ131">
+        <v>0</v>
+      </c>
+      <c r="BK131">
+        <v>0</v>
+      </c>
+      <c r="BL131">
+        <v>0</v>
+      </c>
+      <c r="BM131">
+        <v>0</v>
+      </c>
+      <c r="BN131">
+        <v>0</v>
+      </c>
+      <c r="BO131">
+        <v>0</v>
+      </c>
+      <c r="BP131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7483807</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45745.67708333334</v>
+      </c>
+      <c r="F132">
+        <v>27</v>
+      </c>
+      <c r="G132" t="s">
+        <v>76</v>
+      </c>
+      <c r="H132" t="s">
+        <v>74</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>81</v>
+      </c>
+      <c r="P132" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q132">
+        <v>5</v>
+      </c>
+      <c r="R132">
+        <v>2.38</v>
+      </c>
+      <c r="S132">
+        <v>2</v>
+      </c>
+      <c r="T132">
+        <v>1.3</v>
+      </c>
+      <c r="U132">
+        <v>3.4</v>
+      </c>
+      <c r="V132">
+        <v>2.5</v>
+      </c>
+      <c r="W132">
+        <v>1.5</v>
+      </c>
+      <c r="X132">
+        <v>5.5</v>
+      </c>
+      <c r="Y132">
+        <v>1.13</v>
+      </c>
+      <c r="Z132">
+        <v>5.4</v>
+      </c>
+      <c r="AA132">
+        <v>4.4</v>
+      </c>
+      <c r="AB132">
+        <v>1.52</v>
+      </c>
+      <c r="AC132">
+        <v>0</v>
+      </c>
+      <c r="AD132">
+        <v>0</v>
+      </c>
+      <c r="AE132">
+        <v>3.71</v>
+      </c>
+      <c r="AF132">
+        <v>1.26</v>
+      </c>
+      <c r="AG132">
+        <v>1.57</v>
+      </c>
+      <c r="AH132">
+        <v>2.15</v>
+      </c>
+      <c r="AI132">
+        <v>1.73</v>
+      </c>
+      <c r="AJ132">
+        <v>2</v>
+      </c>
+      <c r="AK132">
+        <v>0</v>
+      </c>
+      <c r="AL132">
+        <v>0</v>
+      </c>
+      <c r="AM132">
+        <v>0</v>
+      </c>
+      <c r="AN132">
+        <v>0.67</v>
+      </c>
+      <c r="AO132">
+        <v>1.18</v>
+      </c>
+      <c r="AP132">
+        <v>0.62</v>
+      </c>
+      <c r="AQ132">
+        <v>1.33</v>
+      </c>
+      <c r="AR132">
+        <v>1.42</v>
+      </c>
+      <c r="AS132">
+        <v>1.62</v>
+      </c>
+      <c r="AT132">
+        <v>3.04</v>
+      </c>
+      <c r="AU132">
+        <v>3</v>
+      </c>
+      <c r="AV132">
+        <v>6</v>
+      </c>
+      <c r="AW132">
+        <v>1</v>
+      </c>
+      <c r="AX132">
+        <v>13</v>
+      </c>
+      <c r="AY132">
+        <v>4</v>
+      </c>
+      <c r="AZ132">
+        <v>19</v>
+      </c>
+      <c r="BA132">
+        <v>4</v>
+      </c>
+      <c r="BB132">
+        <v>9</v>
+      </c>
+      <c r="BC132">
+        <v>13</v>
+      </c>
+      <c r="BD132">
+        <v>0</v>
+      </c>
+      <c r="BE132">
+        <v>0</v>
+      </c>
+      <c r="BF132">
+        <v>0</v>
+      </c>
+      <c r="BG132">
+        <v>0</v>
+      </c>
+      <c r="BH132">
+        <v>0</v>
+      </c>
+      <c r="BI132">
+        <v>0</v>
+      </c>
+      <c r="BJ132">
+        <v>0</v>
+      </c>
+      <c r="BK132">
+        <v>0</v>
+      </c>
+      <c r="BL132">
+        <v>0</v>
+      </c>
+      <c r="BM132">
+        <v>0</v>
+      </c>
+      <c r="BN132">
+        <v>0</v>
+      </c>
+      <c r="BO132">
+        <v>0</v>
+      </c>
+      <c r="BP132">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -524,6 +524,12 @@
   </si>
   <si>
     <t>['41']</t>
+  </si>
+  <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['5', '40', '73']</t>
   </si>
   <si>
     <t>['83']</t>
@@ -1074,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1408,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -1948,7 +1954,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2235,7 +2241,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2441,7 +2447,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2566,7 +2572,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3390,7 +3396,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3468,7 +3474,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12">
         <v>1.79</v>
@@ -3883,7 +3889,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ14">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
         <v>1.88</v>
@@ -4086,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ15">
         <v>0.29</v>
@@ -4214,7 +4220,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4626,7 +4632,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4707,7 +4713,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ18">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR18">
         <v>2.23</v>
@@ -5244,7 +5250,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5322,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ21">
         <v>0.64</v>
@@ -5450,7 +5456,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5531,7 +5537,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ22">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5862,7 +5868,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6068,7 +6074,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6146,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ25">
         <v>1.33</v>
@@ -6355,7 +6361,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ26">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR26">
         <v>1.62</v>
@@ -6480,7 +6486,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6892,7 +6898,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7304,7 +7310,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7591,7 +7597,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ32">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -8206,7 +8212,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ35">
         <v>0.85</v>
@@ -8540,7 +8546,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8952,7 +8958,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9570,7 +9576,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9648,10 +9654,10 @@
         <v>1.25</v>
       </c>
       <c r="AP42">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ42">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR42">
         <v>2.18</v>
@@ -9982,7 +9988,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10188,7 +10194,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10600,7 +10606,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10678,7 +10684,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ47">
         <v>2.08</v>
@@ -10806,7 +10812,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11093,7 +11099,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ49">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR49">
         <v>1.31</v>
@@ -11218,7 +11224,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11630,7 +11636,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11914,10 +11920,10 @@
         <v>1.2</v>
       </c>
       <c r="AP53">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ53">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR53">
         <v>1.07</v>
@@ -12042,7 +12048,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12248,7 +12254,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12326,7 +12332,7 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ55">
         <v>1.79</v>
@@ -12454,7 +12460,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12532,10 +12538,10 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ56">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12660,7 +12666,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12866,7 +12872,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13072,7 +13078,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13278,7 +13284,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13484,7 +13490,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13565,7 +13571,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ61">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR61">
         <v>1.2</v>
@@ -13690,7 +13696,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13768,7 +13774,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ62">
         <v>0.29</v>
@@ -13896,7 +13902,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14102,7 +14108,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14183,7 +14189,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ64">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR64">
         <v>1.37</v>
@@ -14308,7 +14314,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14592,7 +14598,7 @@
         <v>0.67</v>
       </c>
       <c r="AP66">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ66">
         <v>0.64</v>
@@ -15007,7 +15013,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ68">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR68">
         <v>1.5</v>
@@ -15132,7 +15138,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15338,7 +15344,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15544,7 +15550,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16037,7 +16043,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ73">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16240,7 +16246,7 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ74">
         <v>1.58</v>
@@ -16368,7 +16374,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16574,7 +16580,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16652,7 +16658,7 @@
         <v>1.14</v>
       </c>
       <c r="AP76">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ76">
         <v>1.33</v>
@@ -16986,7 +16992,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17192,7 +17198,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17476,7 +17482,7 @@
         <v>1.71</v>
       </c>
       <c r="AP80">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ80">
         <v>1.58</v>
@@ -17604,7 +17610,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17685,7 +17691,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ81">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -17810,7 +17816,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18094,7 +18100,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ83">
         <v>0.85</v>
@@ -18506,10 +18512,10 @@
         <v>0.86</v>
       </c>
       <c r="AP85">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ85">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR85">
         <v>1.72</v>
@@ -18715,7 +18721,7 @@
         <v>2</v>
       </c>
       <c r="AQ86">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR86">
         <v>1.46</v>
@@ -18840,7 +18846,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19046,7 +19052,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19252,7 +19258,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19664,7 +19670,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19870,7 +19876,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19951,7 +19957,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ92">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20360,7 +20366,7 @@
         <v>1.22</v>
       </c>
       <c r="AP94">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20694,7 +20700,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21106,7 +21112,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21187,7 +21193,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ98">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21312,7 +21318,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21518,7 +21524,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21724,7 +21730,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21930,7 +21936,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22011,7 +22017,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ102">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR102">
         <v>1.84</v>
@@ -22420,7 +22426,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ104">
         <v>0.29</v>
@@ -22754,7 +22760,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22960,7 +22966,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23372,7 +23378,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23453,7 +23459,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR109">
         <v>2.1</v>
@@ -23656,7 +23662,7 @@
         <v>0.45</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ110">
         <v>0.64</v>
@@ -23784,7 +23790,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24274,7 +24280,7 @@
         <v>1.3</v>
       </c>
       <c r="AP113">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ113">
         <v>1.33</v>
@@ -24402,7 +24408,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24483,7 +24489,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ114">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR114">
         <v>1.48</v>
@@ -24608,7 +24614,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24686,7 +24692,7 @@
         <v>1.91</v>
       </c>
       <c r="AP115">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ115">
         <v>1.79</v>
@@ -24814,7 +24820,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -25020,7 +25026,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25307,7 +25313,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ118">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR118">
         <v>1.52</v>
@@ -25432,7 +25438,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25844,7 +25850,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26131,7 +26137,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ122">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR122">
         <v>1.32</v>
@@ -26256,7 +26262,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26334,7 +26340,7 @@
         <v>1.73</v>
       </c>
       <c r="AP123">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ123">
         <v>1.58</v>
@@ -26540,7 +26546,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ124">
         <v>0.85</v>
@@ -26668,7 +26674,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -27080,7 +27086,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27286,7 +27292,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27492,7 +27498,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27698,7 +27704,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q130">
         <v>1.8</v>
@@ -28266,6 +28272,418 @@
         <v>0</v>
       </c>
       <c r="BP132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7483804</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F133">
+        <v>27</v>
+      </c>
+      <c r="G133" t="s">
+        <v>79</v>
+      </c>
+      <c r="H133" t="s">
+        <v>71</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>170</v>
+      </c>
+      <c r="P133" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+      <c r="S133">
+        <v>0</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133">
+        <v>0</v>
+      </c>
+      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>0</v>
+      </c>
+      <c r="Z133">
+        <v>2.24</v>
+      </c>
+      <c r="AA133">
+        <v>3.21</v>
+      </c>
+      <c r="AB133">
+        <v>3.2</v>
+      </c>
+      <c r="AC133">
+        <v>0</v>
+      </c>
+      <c r="AD133">
+        <v>0</v>
+      </c>
+      <c r="AE133">
+        <v>0</v>
+      </c>
+      <c r="AF133">
+        <v>0</v>
+      </c>
+      <c r="AG133">
+        <v>2.2</v>
+      </c>
+      <c r="AH133">
+        <v>1.55</v>
+      </c>
+      <c r="AI133">
+        <v>0</v>
+      </c>
+      <c r="AJ133">
+        <v>0</v>
+      </c>
+      <c r="AK133">
+        <v>0</v>
+      </c>
+      <c r="AL133">
+        <v>0</v>
+      </c>
+      <c r="AM133">
+        <v>0</v>
+      </c>
+      <c r="AN133">
+        <v>1.42</v>
+      </c>
+      <c r="AO133">
+        <v>0.58</v>
+      </c>
+      <c r="AP133">
+        <v>1.38</v>
+      </c>
+      <c r="AQ133">
+        <v>0.62</v>
+      </c>
+      <c r="AR133">
+        <v>1.12</v>
+      </c>
+      <c r="AS133">
+        <v>1.35</v>
+      </c>
+      <c r="AT133">
+        <v>2.47</v>
+      </c>
+      <c r="AU133">
+        <v>-1</v>
+      </c>
+      <c r="AV133">
+        <v>-1</v>
+      </c>
+      <c r="AW133">
+        <v>-1</v>
+      </c>
+      <c r="AX133">
+        <v>-1</v>
+      </c>
+      <c r="AY133">
+        <v>-1</v>
+      </c>
+      <c r="AZ133">
+        <v>-1</v>
+      </c>
+      <c r="BA133">
+        <v>-1</v>
+      </c>
+      <c r="BB133">
+        <v>-1</v>
+      </c>
+      <c r="BC133">
+        <v>-1</v>
+      </c>
+      <c r="BD133">
+        <v>0</v>
+      </c>
+      <c r="BE133">
+        <v>0</v>
+      </c>
+      <c r="BF133">
+        <v>0</v>
+      </c>
+      <c r="BG133">
+        <v>0</v>
+      </c>
+      <c r="BH133">
+        <v>0</v>
+      </c>
+      <c r="BI133">
+        <v>0</v>
+      </c>
+      <c r="BJ133">
+        <v>0</v>
+      </c>
+      <c r="BK133">
+        <v>0</v>
+      </c>
+      <c r="BL133">
+        <v>0</v>
+      </c>
+      <c r="BM133">
+        <v>0</v>
+      </c>
+      <c r="BN133">
+        <v>0</v>
+      </c>
+      <c r="BO133">
+        <v>0</v>
+      </c>
+      <c r="BP133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7483803</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45746.52083333334</v>
+      </c>
+      <c r="F134">
+        <v>27</v>
+      </c>
+      <c r="G134" t="s">
+        <v>70</v>
+      </c>
+      <c r="H134" t="s">
+        <v>78</v>
+      </c>
+      <c r="I134">
+        <v>2</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>2</v>
+      </c>
+      <c r="L134">
+        <v>3</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>3</v>
+      </c>
+      <c r="O134" t="s">
+        <v>171</v>
+      </c>
+      <c r="P134" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q134">
+        <v>2.2</v>
+      </c>
+      <c r="R134">
+        <v>2.05</v>
+      </c>
+      <c r="S134">
+        <v>6</v>
+      </c>
+      <c r="T134">
+        <v>1.5</v>
+      </c>
+      <c r="U134">
+        <v>2.5</v>
+      </c>
+      <c r="V134">
+        <v>3.4</v>
+      </c>
+      <c r="W134">
+        <v>1.3</v>
+      </c>
+      <c r="X134">
+        <v>8</v>
+      </c>
+      <c r="Y134">
+        <v>1.06</v>
+      </c>
+      <c r="Z134">
+        <v>1.57</v>
+      </c>
+      <c r="AA134">
+        <v>3.7</v>
+      </c>
+      <c r="AB134">
+        <v>6.2</v>
+      </c>
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
+        <v>0</v>
+      </c>
+      <c r="AF134">
+        <v>0</v>
+      </c>
+      <c r="AG134">
+        <v>2.15</v>
+      </c>
+      <c r="AH134">
+        <v>1.57</v>
+      </c>
+      <c r="AI134">
+        <v>2.25</v>
+      </c>
+      <c r="AJ134">
+        <v>1.57</v>
+      </c>
+      <c r="AK134">
+        <v>0</v>
+      </c>
+      <c r="AL134">
+        <v>0</v>
+      </c>
+      <c r="AM134">
+        <v>0</v>
+      </c>
+      <c r="AN134">
+        <v>2.31</v>
+      </c>
+      <c r="AO134">
+        <v>1.46</v>
+      </c>
+      <c r="AP134">
+        <v>2.36</v>
+      </c>
+      <c r="AQ134">
+        <v>1.36</v>
+      </c>
+      <c r="AR134">
+        <v>1.81</v>
+      </c>
+      <c r="AS134">
+        <v>1.53</v>
+      </c>
+      <c r="AT134">
+        <v>3.34</v>
+      </c>
+      <c r="AU134">
+        <v>8</v>
+      </c>
+      <c r="AV134">
+        <v>2</v>
+      </c>
+      <c r="AW134">
+        <v>4</v>
+      </c>
+      <c r="AX134">
+        <v>1</v>
+      </c>
+      <c r="AY134">
+        <v>12</v>
+      </c>
+      <c r="AZ134">
+        <v>3</v>
+      </c>
+      <c r="BA134">
+        <v>5</v>
+      </c>
+      <c r="BB134">
+        <v>3</v>
+      </c>
+      <c r="BC134">
+        <v>8</v>
+      </c>
+      <c r="BD134">
+        <v>0</v>
+      </c>
+      <c r="BE134">
+        <v>0</v>
+      </c>
+      <c r="BF134">
+        <v>0</v>
+      </c>
+      <c r="BG134">
+        <v>0</v>
+      </c>
+      <c r="BH134">
+        <v>0</v>
+      </c>
+      <c r="BI134">
+        <v>0</v>
+      </c>
+      <c r="BJ134">
+        <v>0</v>
+      </c>
+      <c r="BK134">
+        <v>0</v>
+      </c>
+      <c r="BL134">
+        <v>0</v>
+      </c>
+      <c r="BM134">
+        <v>0</v>
+      </c>
+      <c r="BN134">
+        <v>0</v>
+      </c>
+      <c r="BO134">
+        <v>0</v>
+      </c>
+      <c r="BP134">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -28415,31 +28415,31 @@
         <v>2.47</v>
       </c>
       <c r="AU133">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AV133">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW133">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AX133">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY133">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AZ133">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BA133">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB133">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC133">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD133">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,6 +532,12 @@
     <t>['5', '40', '73']</t>
   </si>
   <si>
+    <t>['31', '53', '72', '90+10']</t>
+  </si>
+  <si>
+    <t>['43', '76', '86']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -719,6 +725,12 @@
   </si>
   <si>
     <t>['59', '68']</t>
+  </si>
+  <si>
+    <t>['40', '90+9']</t>
+  </si>
+  <si>
+    <t>['72']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1954,7 +1966,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2444,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2572,7 +2584,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2653,7 +2665,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ8">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2856,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ9">
         <v>2.08</v>
@@ -3396,7 +3408,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4220,7 +4232,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4298,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ16">
         <v>0.93</v>
@@ -4632,7 +4644,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -4713,7 +4725,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ18">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR18">
         <v>2.23</v>
@@ -4919,7 +4931,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ19">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR19">
         <v>1.75</v>
@@ -5250,7 +5262,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5456,7 +5468,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5740,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ23">
         <v>0.29</v>
@@ -5868,7 +5880,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6074,7 +6086,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6361,7 +6373,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ26">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR26">
         <v>1.62</v>
@@ -6486,7 +6498,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6898,7 +6910,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7310,7 +7322,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7388,7 +7400,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ31">
         <v>0.64</v>
@@ -8006,7 +8018,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8215,7 +8227,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ35">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR35">
         <v>2.01</v>
@@ -8546,7 +8558,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8958,7 +8970,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9576,7 +9588,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9860,10 +9872,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ43">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR43">
         <v>1.26</v>
@@ -9988,7 +10000,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10066,7 +10078,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44">
         <v>1.58</v>
@@ -10194,7 +10206,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10478,10 +10490,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ46">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR46">
         <v>1.5</v>
@@ -10606,7 +10618,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10812,7 +10824,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11096,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ49">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR49">
         <v>1.31</v>
@@ -11224,7 +11236,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11636,7 +11648,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -12048,7 +12060,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12254,7 +12266,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12460,7 +12472,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12541,7 +12553,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ56">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12666,7 +12678,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12747,7 +12759,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ57">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR57">
         <v>2.09</v>
@@ -12872,7 +12884,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12950,7 +12962,7 @@
         <v>2.2</v>
       </c>
       <c r="AP58">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ58">
         <v>2.08</v>
@@ -13078,7 +13090,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13156,7 +13168,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ59">
         <v>0.93</v>
@@ -13284,7 +13296,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13490,7 +13502,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13571,7 +13583,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ61">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR61">
         <v>1.2</v>
@@ -13696,7 +13708,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13902,7 +13914,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14108,7 +14120,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14186,7 +14198,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ64">
         <v>1.36</v>
@@ -14314,7 +14326,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -15013,7 +15025,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ68">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR68">
         <v>1.5</v>
@@ -15138,7 +15150,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15219,7 +15231,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -15344,7 +15356,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15550,7 +15562,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15628,7 +15640,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71">
         <v>1.79</v>
@@ -15834,7 +15846,7 @@
         <v>0.57</v>
       </c>
       <c r="AP72">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ72">
         <v>0.64</v>
@@ -16040,7 +16052,7 @@
         <v>0.86</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ73">
         <v>1.36</v>
@@ -16374,7 +16386,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16455,7 +16467,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ75">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR75">
         <v>1.44</v>
@@ -16580,7 +16592,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16992,7 +17004,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17198,7 +17210,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17610,7 +17622,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17816,7 +17828,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -17894,7 +17906,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ82">
         <v>1.58</v>
@@ -18103,7 +18115,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ83">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR83">
         <v>1.05</v>
@@ -18306,7 +18318,7 @@
         <v>1.38</v>
       </c>
       <c r="AP84">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -18515,7 +18527,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ85">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR85">
         <v>1.72</v>
@@ -18721,7 +18733,7 @@
         <v>2</v>
       </c>
       <c r="AQ86">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR86">
         <v>1.46</v>
@@ -18846,7 +18858,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19052,7 +19064,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19258,7 +19270,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19670,7 +19682,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19876,7 +19888,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20700,7 +20712,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21112,7 +21124,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21190,10 +21202,10 @@
         <v>0.78</v>
       </c>
       <c r="AP98">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21318,7 +21330,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21399,7 +21411,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ99">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21524,7 +21536,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21730,7 +21742,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21808,7 +21820,7 @@
         <v>2.33</v>
       </c>
       <c r="AP101">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ101">
         <v>2.08</v>
@@ -21936,7 +21948,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22760,7 +22772,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22838,7 +22850,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ106">
         <v>0.93</v>
@@ -22966,7 +22978,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23253,7 +23265,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ108">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR108">
         <v>1.88</v>
@@ -23378,7 +23390,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23459,7 +23471,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR109">
         <v>2.1</v>
@@ -23790,7 +23802,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24074,7 +24086,7 @@
         <v>0.18</v>
       </c>
       <c r="AP112">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ112">
         <v>0.29</v>
@@ -24408,7 +24420,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24614,7 +24626,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24820,7 +24832,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -25026,7 +25038,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25313,7 +25325,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ118">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR118">
         <v>1.52</v>
@@ -25438,7 +25450,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25850,7 +25862,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26262,7 +26274,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26549,7 +26561,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ124">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -26674,7 +26686,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -26752,7 +26764,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ125">
         <v>0.64</v>
@@ -27086,7 +27098,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27292,7 +27304,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27498,7 +27510,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27704,7 +27716,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q130">
         <v>1.8</v>
@@ -27988,10 +28000,10 @@
         <v>0.92</v>
       </c>
       <c r="AP131">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ131">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR131">
         <v>1.5</v>
@@ -28403,7 +28415,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ133">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR133">
         <v>1.12</v>
@@ -28685,6 +28697,418 @@
       </c>
       <c r="BP134">
         <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7483873</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45752.52083333334</v>
+      </c>
+      <c r="F135">
+        <v>28</v>
+      </c>
+      <c r="G135" t="s">
+        <v>75</v>
+      </c>
+      <c r="H135" t="s">
+        <v>72</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>2</v>
+      </c>
+      <c r="L135">
+        <v>4</v>
+      </c>
+      <c r="M135">
+        <v>2</v>
+      </c>
+      <c r="N135">
+        <v>6</v>
+      </c>
+      <c r="O135" t="s">
+        <v>172</v>
+      </c>
+      <c r="P135" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q135">
+        <v>3.1</v>
+      </c>
+      <c r="R135">
+        <v>2.05</v>
+      </c>
+      <c r="S135">
+        <v>3.4</v>
+      </c>
+      <c r="T135">
+        <v>1.44</v>
+      </c>
+      <c r="U135">
+        <v>2.63</v>
+      </c>
+      <c r="V135">
+        <v>3.25</v>
+      </c>
+      <c r="W135">
+        <v>1.33</v>
+      </c>
+      <c r="X135">
+        <v>7.5</v>
+      </c>
+      <c r="Y135">
+        <v>1.07</v>
+      </c>
+      <c r="Z135">
+        <v>2.61</v>
+      </c>
+      <c r="AA135">
+        <v>3.13</v>
+      </c>
+      <c r="AB135">
+        <v>2.72</v>
+      </c>
+      <c r="AC135">
+        <v>1.02</v>
+      </c>
+      <c r="AD135">
+        <v>7.9</v>
+      </c>
+      <c r="AE135">
+        <v>1.35</v>
+      </c>
+      <c r="AF135">
+        <v>3.17</v>
+      </c>
+      <c r="AG135">
+        <v>2.05</v>
+      </c>
+      <c r="AH135">
+        <v>1.61</v>
+      </c>
+      <c r="AI135">
+        <v>1.83</v>
+      </c>
+      <c r="AJ135">
+        <v>1.83</v>
+      </c>
+      <c r="AK135">
+        <v>1.48</v>
+      </c>
+      <c r="AL135">
+        <v>1.36</v>
+      </c>
+      <c r="AM135">
+        <v>1.46</v>
+      </c>
+      <c r="AN135">
+        <v>1.25</v>
+      </c>
+      <c r="AO135">
+        <v>0.85</v>
+      </c>
+      <c r="AP135">
+        <v>1.38</v>
+      </c>
+      <c r="AQ135">
+        <v>0.79</v>
+      </c>
+      <c r="AR135">
+        <v>1.51</v>
+      </c>
+      <c r="AS135">
+        <v>1.26</v>
+      </c>
+      <c r="AT135">
+        <v>2.77</v>
+      </c>
+      <c r="AU135">
+        <v>8</v>
+      </c>
+      <c r="AV135">
+        <v>9</v>
+      </c>
+      <c r="AW135">
+        <v>8</v>
+      </c>
+      <c r="AX135">
+        <v>3</v>
+      </c>
+      <c r="AY135">
+        <v>16</v>
+      </c>
+      <c r="AZ135">
+        <v>12</v>
+      </c>
+      <c r="BA135">
+        <v>5</v>
+      </c>
+      <c r="BB135">
+        <v>5</v>
+      </c>
+      <c r="BC135">
+        <v>10</v>
+      </c>
+      <c r="BD135">
+        <v>1.98</v>
+      </c>
+      <c r="BE135">
+        <v>6.15</v>
+      </c>
+      <c r="BF135">
+        <v>2.22</v>
+      </c>
+      <c r="BG135">
+        <v>1.28</v>
+      </c>
+      <c r="BH135">
+        <v>3.08</v>
+      </c>
+      <c r="BI135">
+        <v>1.57</v>
+      </c>
+      <c r="BJ135">
+        <v>2.34</v>
+      </c>
+      <c r="BK135">
+        <v>1.95</v>
+      </c>
+      <c r="BL135">
+        <v>1.85</v>
+      </c>
+      <c r="BM135">
+        <v>2.47</v>
+      </c>
+      <c r="BN135">
+        <v>1.51</v>
+      </c>
+      <c r="BO135">
+        <v>3.42</v>
+      </c>
+      <c r="BP135">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7483810</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45752.63541666666</v>
+      </c>
+      <c r="F136">
+        <v>28</v>
+      </c>
+      <c r="G136" t="s">
+        <v>77</v>
+      </c>
+      <c r="H136" t="s">
+        <v>71</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>3</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>4</v>
+      </c>
+      <c r="O136" t="s">
+        <v>173</v>
+      </c>
+      <c r="P136" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q136">
+        <v>2.25</v>
+      </c>
+      <c r="R136">
+        <v>2.2</v>
+      </c>
+      <c r="S136">
+        <v>4.75</v>
+      </c>
+      <c r="T136">
+        <v>1.36</v>
+      </c>
+      <c r="U136">
+        <v>3</v>
+      </c>
+      <c r="V136">
+        <v>2.63</v>
+      </c>
+      <c r="W136">
+        <v>1.44</v>
+      </c>
+      <c r="X136">
+        <v>6.5</v>
+      </c>
+      <c r="Y136">
+        <v>1.1</v>
+      </c>
+      <c r="Z136">
+        <v>1.66</v>
+      </c>
+      <c r="AA136">
+        <v>3.89</v>
+      </c>
+      <c r="AB136">
+        <v>4.75</v>
+      </c>
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>1.27</v>
+      </c>
+      <c r="AF136">
+        <v>3.72</v>
+      </c>
+      <c r="AG136">
+        <v>1.77</v>
+      </c>
+      <c r="AH136">
+        <v>1.98</v>
+      </c>
+      <c r="AI136">
+        <v>1.8</v>
+      </c>
+      <c r="AJ136">
+        <v>1.91</v>
+      </c>
+      <c r="AK136">
+        <v>1.2</v>
+      </c>
+      <c r="AL136">
+        <v>1.28</v>
+      </c>
+      <c r="AM136">
+        <v>2.1</v>
+      </c>
+      <c r="AN136">
+        <v>1.58</v>
+      </c>
+      <c r="AO136">
+        <v>0.62</v>
+      </c>
+      <c r="AP136">
+        <v>1.69</v>
+      </c>
+      <c r="AQ136">
+        <v>0.57</v>
+      </c>
+      <c r="AR136">
+        <v>1.53</v>
+      </c>
+      <c r="AS136">
+        <v>1.33</v>
+      </c>
+      <c r="AT136">
+        <v>2.86</v>
+      </c>
+      <c r="AU136">
+        <v>6</v>
+      </c>
+      <c r="AV136">
+        <v>6</v>
+      </c>
+      <c r="AW136">
+        <v>5</v>
+      </c>
+      <c r="AX136">
+        <v>6</v>
+      </c>
+      <c r="AY136">
+        <v>11</v>
+      </c>
+      <c r="AZ136">
+        <v>12</v>
+      </c>
+      <c r="BA136">
+        <v>1</v>
+      </c>
+      <c r="BB136">
+        <v>5</v>
+      </c>
+      <c r="BC136">
+        <v>6</v>
+      </c>
+      <c r="BD136">
+        <v>1.29</v>
+      </c>
+      <c r="BE136">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF136">
+        <v>4.25</v>
+      </c>
+      <c r="BG136">
+        <v>1.31</v>
+      </c>
+      <c r="BH136">
+        <v>2.92</v>
+      </c>
+      <c r="BI136">
+        <v>1.63</v>
+      </c>
+      <c r="BJ136">
+        <v>2.21</v>
+      </c>
+      <c r="BK136">
+        <v>2.03</v>
+      </c>
+      <c r="BL136">
+        <v>1.75</v>
+      </c>
+      <c r="BM136">
+        <v>2.62</v>
+      </c>
+      <c r="BN136">
+        <v>1.38</v>
+      </c>
+      <c r="BO136">
+        <v>3.58</v>
+      </c>
+      <c r="BP136">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="242">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,12 @@
     <t>['43', '76', '86']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -709,9 +715,6 @@
     <t>['55', '70']</t>
   </si>
   <si>
-    <t>['69']</t>
-  </si>
-  <si>
     <t>['23', '48']</t>
   </si>
   <si>
@@ -731,6 +734,12 @@
   </si>
   <si>
     <t>['72']</t>
+  </si>
+  <si>
+    <t>['34', '52']</t>
+  </si>
+  <si>
+    <t>['32', '38']</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1966,7 +1975,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2584,7 +2593,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2662,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ8">
         <v>0.79</v>
@@ -2871,7 +2880,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ9">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3074,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10">
         <v>0.93</v>
@@ -3408,7 +3417,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3486,7 +3495,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12">
         <v>1.79</v>
@@ -3695,7 +3704,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR13">
         <v>1.72</v>
@@ -4232,7 +4241,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4516,10 +4525,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ17">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR17">
         <v>1.21</v>
@@ -4644,7 +4653,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5134,7 +5143,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ20">
         <v>1.79</v>
@@ -5262,7 +5271,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5340,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21">
         <v>0.64</v>
@@ -5468,7 +5477,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5880,7 +5889,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5961,7 +5970,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ24">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR24">
         <v>1.24</v>
@@ -6086,7 +6095,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6167,7 +6176,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR25">
         <v>1.83</v>
@@ -6498,7 +6507,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6576,7 +6585,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ27">
         <v>1.79</v>
@@ -6785,7 +6794,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ28">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -6910,7 +6919,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7194,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ30">
         <v>0.29</v>
@@ -7322,7 +7331,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -8021,7 +8030,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -8558,7 +8567,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8639,7 +8648,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ37">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -8842,7 +8851,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ38">
         <v>0.64</v>
@@ -8970,7 +8979,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9463,7 +9472,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ41">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR41">
         <v>2.19</v>
@@ -9588,7 +9597,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -10000,7 +10009,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10081,7 +10090,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ44">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10206,7 +10215,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10284,10 +10293,10 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ45">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR45">
         <v>1.07</v>
@@ -10618,7 +10627,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10696,10 +10705,10 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ47">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR47">
         <v>1.05</v>
@@ -10824,7 +10833,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -10902,10 +10911,10 @@
         <v>1.25</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR48">
         <v>1.28</v>
@@ -11236,7 +11245,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11314,10 +11323,10 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ50">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11648,7 +11657,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11932,7 +11941,7 @@
         <v>1.2</v>
       </c>
       <c r="AP53">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ53">
         <v>1.36</v>
@@ -12060,7 +12069,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12141,7 +12150,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12266,7 +12275,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12472,7 +12481,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12550,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ56">
         <v>0.57</v>
@@ -12678,7 +12687,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12884,7 +12893,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -12965,7 +12974,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ58">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR58">
         <v>1.46</v>
@@ -13090,7 +13099,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13296,7 +13305,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13374,10 +13383,10 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ60">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR60">
         <v>1.4</v>
@@ -13502,7 +13511,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13580,7 +13589,7 @@
         <v>0.6</v>
       </c>
       <c r="AP61">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ61">
         <v>0.57</v>
@@ -13708,7 +13717,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13786,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ62">
         <v>0.29</v>
@@ -13914,7 +13923,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -13995,7 +14004,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ63">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR63">
         <v>1.5</v>
@@ -14120,7 +14129,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14326,7 +14335,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14407,7 +14416,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14816,7 +14825,7 @@
         <v>1.29</v>
       </c>
       <c r="AP67">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ67">
         <v>0.93</v>
@@ -15150,7 +15159,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15228,7 +15237,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69">
         <v>0.79</v>
@@ -15356,7 +15365,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15437,7 +15446,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ70">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR70">
         <v>1.99</v>
@@ -15562,7 +15571,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16261,7 +16270,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ74">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR74">
         <v>1.87</v>
@@ -16386,7 +16395,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16592,7 +16601,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16670,10 +16679,10 @@
         <v>1.14</v>
       </c>
       <c r="AP76">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR76">
         <v>1.07</v>
@@ -17004,7 +17013,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17082,7 +17091,7 @@
         <v>0.14</v>
       </c>
       <c r="AP78">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ78">
         <v>0.29</v>
@@ -17210,7 +17219,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17291,7 +17300,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ79">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR79">
         <v>1.42</v>
@@ -17494,10 +17503,10 @@
         <v>1.71</v>
       </c>
       <c r="AP80">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ80">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR80">
         <v>1.04</v>
@@ -17622,7 +17631,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17700,7 +17709,7 @@
         <v>1.13</v>
       </c>
       <c r="AP81">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ81">
         <v>1.36</v>
@@ -17828,7 +17837,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -17909,7 +17918,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ82">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR82">
         <v>1.46</v>
@@ -18112,7 +18121,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ83">
         <v>0.79</v>
@@ -18321,7 +18330,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR84">
         <v>1.41</v>
@@ -18730,7 +18739,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ86">
         <v>0.57</v>
@@ -18858,7 +18867,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19064,7 +19073,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19142,10 +19151,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ88">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR88">
         <v>1.51</v>
@@ -19270,7 +19279,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19682,7 +19691,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19888,7 +19897,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20712,7 +20721,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20996,7 +21005,7 @@
         <v>1.1</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ97">
         <v>0.93</v>
@@ -21124,7 +21133,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21330,7 +21339,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21408,7 +21417,7 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ99">
         <v>0.79</v>
@@ -21536,7 +21545,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21617,7 +21626,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ100">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR100">
         <v>2.09</v>
@@ -21742,7 +21751,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21823,7 +21832,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ101">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR101">
         <v>1.43</v>
@@ -21948,7 +21957,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22235,7 +22244,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22772,7 +22781,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22978,7 +22987,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23056,7 +23065,7 @@
         <v>2.1</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ107">
         <v>1.79</v>
@@ -23390,7 +23399,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23674,7 +23683,7 @@
         <v>0.45</v>
       </c>
       <c r="AP110">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ110">
         <v>0.64</v>
@@ -23802,7 +23811,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -23883,7 +23892,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ111">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR111">
         <v>1.34</v>
@@ -24295,7 +24304,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ113">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR113">
         <v>1.82</v>
@@ -24420,7 +24429,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24626,7 +24635,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24704,7 +24713,7 @@
         <v>1.91</v>
       </c>
       <c r="AP115">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ115">
         <v>1.79</v>
@@ -24832,7 +24841,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -24910,10 +24919,10 @@
         <v>2.4</v>
       </c>
       <c r="AP116">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ116">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR116">
         <v>1.46</v>
@@ -25038,7 +25047,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25116,7 +25125,7 @@
         <v>0.25</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ117">
         <v>0.29</v>
@@ -25450,7 +25459,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25528,7 +25537,7 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ119">
         <v>1.79</v>
@@ -25737,7 +25746,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ120">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR120">
         <v>1.91</v>
@@ -25862,7 +25871,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26274,7 +26283,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -26352,10 +26361,10 @@
         <v>1.73</v>
       </c>
       <c r="AP123">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ123">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR123">
         <v>1.1</v>
@@ -26686,7 +26695,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -27098,7 +27107,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27179,7 +27188,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ127">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR127">
         <v>1.33</v>
@@ -27304,7 +27313,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27382,7 +27391,7 @@
         <v>0.62</v>
       </c>
       <c r="AP128">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128">
         <v>0.64</v>
@@ -27510,7 +27519,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27716,7 +27725,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q130">
         <v>1.8</v>
@@ -28206,10 +28215,10 @@
         <v>1.18</v>
       </c>
       <c r="AP132">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR132">
         <v>1.42</v>
@@ -28412,7 +28421,7 @@
         <v>0.58</v>
       </c>
       <c r="AP133">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ133">
         <v>0.57</v>
@@ -28746,7 +28755,7 @@
         <v>172</v>
       </c>
       <c r="P135" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -28952,7 +28961,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29109,6 +29118,624 @@
       </c>
       <c r="BP136">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7483811</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F137">
+        <v>28</v>
+      </c>
+      <c r="G137" t="s">
+        <v>79</v>
+      </c>
+      <c r="H137" t="s">
+        <v>70</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>2</v>
+      </c>
+      <c r="N137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>81</v>
+      </c>
+      <c r="P137" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>7</v>
+      </c>
+      <c r="AA137">
+        <v>4.2</v>
+      </c>
+      <c r="AB137">
+        <v>1.45</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>1.98</v>
+      </c>
+      <c r="AH137">
+        <v>1.77</v>
+      </c>
+      <c r="AI137">
+        <v>0</v>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>0</v>
+      </c>
+      <c r="AN137">
+        <v>1.38</v>
+      </c>
+      <c r="AO137">
+        <v>2.08</v>
+      </c>
+      <c r="AP137">
+        <v>1.29</v>
+      </c>
+      <c r="AQ137">
+        <v>2.14</v>
+      </c>
+      <c r="AR137">
+        <v>1.25</v>
+      </c>
+      <c r="AS137">
+        <v>1.83</v>
+      </c>
+      <c r="AT137">
+        <v>3.08</v>
+      </c>
+      <c r="AU137">
+        <v>-1</v>
+      </c>
+      <c r="AV137">
+        <v>-1</v>
+      </c>
+      <c r="AW137">
+        <v>-1</v>
+      </c>
+      <c r="AX137">
+        <v>-1</v>
+      </c>
+      <c r="AY137">
+        <v>-1</v>
+      </c>
+      <c r="AZ137">
+        <v>-1</v>
+      </c>
+      <c r="BA137">
+        <v>-1</v>
+      </c>
+      <c r="BB137">
+        <v>-1</v>
+      </c>
+      <c r="BC137">
+        <v>-1</v>
+      </c>
+      <c r="BD137">
+        <v>0</v>
+      </c>
+      <c r="BE137">
+        <v>0</v>
+      </c>
+      <c r="BF137">
+        <v>0</v>
+      </c>
+      <c r="BG137">
+        <v>0</v>
+      </c>
+      <c r="BH137">
+        <v>0</v>
+      </c>
+      <c r="BI137">
+        <v>0</v>
+      </c>
+      <c r="BJ137">
+        <v>0</v>
+      </c>
+      <c r="BK137">
+        <v>0</v>
+      </c>
+      <c r="BL137">
+        <v>0</v>
+      </c>
+      <c r="BM137">
+        <v>0</v>
+      </c>
+      <c r="BN137">
+        <v>0</v>
+      </c>
+      <c r="BO137">
+        <v>0</v>
+      </c>
+      <c r="BP137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7483808</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45753.52083333334</v>
+      </c>
+      <c r="F138">
+        <v>28</v>
+      </c>
+      <c r="G138" t="s">
+        <v>78</v>
+      </c>
+      <c r="H138" t="s">
+        <v>74</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>2</v>
+      </c>
+      <c r="K138">
+        <v>3</v>
+      </c>
+      <c r="L138">
+        <v>1</v>
+      </c>
+      <c r="M138">
+        <v>2</v>
+      </c>
+      <c r="N138">
+        <v>3</v>
+      </c>
+      <c r="O138" t="s">
+        <v>174</v>
+      </c>
+      <c r="P138" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q138">
+        <v>3.4</v>
+      </c>
+      <c r="R138">
+        <v>2.2</v>
+      </c>
+      <c r="S138">
+        <v>2.75</v>
+      </c>
+      <c r="T138">
+        <v>1.36</v>
+      </c>
+      <c r="U138">
+        <v>3</v>
+      </c>
+      <c r="V138">
+        <v>2.63</v>
+      </c>
+      <c r="W138">
+        <v>1.44</v>
+      </c>
+      <c r="X138">
+        <v>6.5</v>
+      </c>
+      <c r="Y138">
+        <v>1.1</v>
+      </c>
+      <c r="Z138">
+        <v>3.04</v>
+      </c>
+      <c r="AA138">
+        <v>3.55</v>
+      </c>
+      <c r="AB138">
+        <v>2.18</v>
+      </c>
+      <c r="AC138">
+        <v>1.01</v>
+      </c>
+      <c r="AD138">
+        <v>11</v>
+      </c>
+      <c r="AE138">
+        <v>1.15</v>
+      </c>
+      <c r="AF138">
+        <v>4.25</v>
+      </c>
+      <c r="AG138">
+        <v>1.7</v>
+      </c>
+      <c r="AH138">
+        <v>1.95</v>
+      </c>
+      <c r="AI138">
+        <v>1.67</v>
+      </c>
+      <c r="AJ138">
+        <v>2.1</v>
+      </c>
+      <c r="AK138">
+        <v>1.56</v>
+      </c>
+      <c r="AL138">
+        <v>1.24</v>
+      </c>
+      <c r="AM138">
+        <v>1.38</v>
+      </c>
+      <c r="AN138">
+        <v>2</v>
+      </c>
+      <c r="AO138">
+        <v>1.33</v>
+      </c>
+      <c r="AP138">
+        <v>1.86</v>
+      </c>
+      <c r="AQ138">
+        <v>1.46</v>
+      </c>
+      <c r="AR138">
+        <v>1.64</v>
+      </c>
+      <c r="AS138">
+        <v>1.67</v>
+      </c>
+      <c r="AT138">
+        <v>3.31</v>
+      </c>
+      <c r="AU138">
+        <v>7</v>
+      </c>
+      <c r="AV138">
+        <v>8</v>
+      </c>
+      <c r="AW138">
+        <v>5</v>
+      </c>
+      <c r="AX138">
+        <v>8</v>
+      </c>
+      <c r="AY138">
+        <v>12</v>
+      </c>
+      <c r="AZ138">
+        <v>16</v>
+      </c>
+      <c r="BA138">
+        <v>4</v>
+      </c>
+      <c r="BB138">
+        <v>2</v>
+      </c>
+      <c r="BC138">
+        <v>6</v>
+      </c>
+      <c r="BD138">
+        <v>3.3</v>
+      </c>
+      <c r="BE138">
+        <v>6.95</v>
+      </c>
+      <c r="BF138">
+        <v>1.49</v>
+      </c>
+      <c r="BG138">
+        <v>1.25</v>
+      </c>
+      <c r="BH138">
+        <v>3.6</v>
+      </c>
+      <c r="BI138">
+        <v>1.44</v>
+      </c>
+      <c r="BJ138">
+        <v>2.6</v>
+      </c>
+      <c r="BK138">
+        <v>1.72</v>
+      </c>
+      <c r="BL138">
+        <v>2.07</v>
+      </c>
+      <c r="BM138">
+        <v>2.13</v>
+      </c>
+      <c r="BN138">
+        <v>1.68</v>
+      </c>
+      <c r="BO138">
+        <v>2.62</v>
+      </c>
+      <c r="BP138">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7483809</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45753.63541666666</v>
+      </c>
+      <c r="F139">
+        <v>28</v>
+      </c>
+      <c r="G139" t="s">
+        <v>76</v>
+      </c>
+      <c r="H139" t="s">
+        <v>73</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139" t="s">
+        <v>175</v>
+      </c>
+      <c r="P139" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q139">
+        <v>5.5</v>
+      </c>
+      <c r="R139">
+        <v>2.3</v>
+      </c>
+      <c r="S139">
+        <v>2.05</v>
+      </c>
+      <c r="T139">
+        <v>1.36</v>
+      </c>
+      <c r="U139">
+        <v>3</v>
+      </c>
+      <c r="V139">
+        <v>2.63</v>
+      </c>
+      <c r="W139">
+        <v>1.44</v>
+      </c>
+      <c r="X139">
+        <v>6</v>
+      </c>
+      <c r="Y139">
+        <v>1.11</v>
+      </c>
+      <c r="Z139">
+        <v>5.6</v>
+      </c>
+      <c r="AA139">
+        <v>4.1</v>
+      </c>
+      <c r="AB139">
+        <v>1.54</v>
+      </c>
+      <c r="AC139">
+        <v>1.01</v>
+      </c>
+      <c r="AD139">
+        <v>13</v>
+      </c>
+      <c r="AE139">
+        <v>1.16</v>
+      </c>
+      <c r="AF139">
+        <v>4.05</v>
+      </c>
+      <c r="AG139">
+        <v>1.73</v>
+      </c>
+      <c r="AH139">
+        <v>1.91</v>
+      </c>
+      <c r="AI139">
+        <v>1.83</v>
+      </c>
+      <c r="AJ139">
+        <v>1.83</v>
+      </c>
+      <c r="AK139">
+        <v>2.83</v>
+      </c>
+      <c r="AL139">
+        <v>1.15</v>
+      </c>
+      <c r="AM139">
+        <v>1.05</v>
+      </c>
+      <c r="AN139">
+        <v>0.62</v>
+      </c>
+      <c r="AO139">
+        <v>1.58</v>
+      </c>
+      <c r="AP139">
+        <v>0.79</v>
+      </c>
+      <c r="AQ139">
+        <v>1.46</v>
+      </c>
+      <c r="AR139">
+        <v>1.37</v>
+      </c>
+      <c r="AS139">
+        <v>1.7</v>
+      </c>
+      <c r="AT139">
+        <v>3.07</v>
+      </c>
+      <c r="AU139">
+        <v>8</v>
+      </c>
+      <c r="AV139">
+        <v>4</v>
+      </c>
+      <c r="AW139">
+        <v>10</v>
+      </c>
+      <c r="AX139">
+        <v>4</v>
+      </c>
+      <c r="AY139">
+        <v>18</v>
+      </c>
+      <c r="AZ139">
+        <v>8</v>
+      </c>
+      <c r="BA139">
+        <v>5</v>
+      </c>
+      <c r="BB139">
+        <v>4</v>
+      </c>
+      <c r="BC139">
+        <v>9</v>
+      </c>
+      <c r="BD139">
+        <v>3.74</v>
+      </c>
+      <c r="BE139">
+        <v>9.6</v>
+      </c>
+      <c r="BF139">
+        <v>1.34</v>
+      </c>
+      <c r="BG139">
+        <v>1.22</v>
+      </c>
+      <c r="BH139">
+        <v>3.8</v>
+      </c>
+      <c r="BI139">
+        <v>1.38</v>
+      </c>
+      <c r="BJ139">
+        <v>2.8</v>
+      </c>
+      <c r="BK139">
+        <v>1.65</v>
+      </c>
+      <c r="BL139">
+        <v>2.18</v>
+      </c>
+      <c r="BM139">
+        <v>2.03</v>
+      </c>
+      <c r="BN139">
+        <v>1.76</v>
+      </c>
+      <c r="BO139">
+        <v>2.5</v>
+      </c>
+      <c r="BP139">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -542,6 +542,9 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['29', '45', '46', '90+3']</t>
   </si>
   <si>
     <t>['83']</t>
@@ -1101,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1641,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3">
         <v>1.79</v>
@@ -1850,7 +1853,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ4">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1975,7 +1978,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2593,7 +2596,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3289,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11">
         <v>0.64</v>
@@ -3417,7 +3420,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4116,7 +4119,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ15">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR15">
         <v>1.3</v>
@@ -4241,7 +4244,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4653,7 +4656,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5271,7 +5274,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5477,7 +5480,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5764,7 +5767,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ23">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR23">
         <v>0.7</v>
@@ -5889,7 +5892,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -5967,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ24">
         <v>1.46</v>
@@ -6095,7 +6098,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6507,7 +6510,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6919,7 +6922,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7206,7 +7209,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ30">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR30">
         <v>1.03</v>
@@ -7331,7 +7334,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7615,7 +7618,7 @@
         <v>1.33</v>
       </c>
       <c r="AP32">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ32">
         <v>1.36</v>
@@ -8567,7 +8570,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8645,7 +8648,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37">
         <v>2.14</v>
@@ -8979,7 +8982,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9060,7 +9063,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ39">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR39">
         <v>2.18</v>
@@ -9597,7 +9600,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -10009,7 +10012,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10215,7 +10218,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10627,7 +10630,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10833,7 +10836,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11245,7 +11248,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11529,10 +11532,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ51">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR51">
         <v>1.32</v>
@@ -11657,7 +11660,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -12069,7 +12072,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12275,7 +12278,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12481,7 +12484,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12687,7 +12690,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12893,7 +12896,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13099,7 +13102,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13305,7 +13308,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13511,7 +13514,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13717,7 +13720,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13798,7 +13801,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ62">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -13923,7 +13926,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14129,7 +14132,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14335,7 +14338,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14413,7 +14416,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ65">
         <v>1.46</v>
@@ -15159,7 +15162,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15365,7 +15368,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15571,7 +15574,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -16395,7 +16398,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16473,7 +16476,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ75">
         <v>0.79</v>
@@ -16601,7 +16604,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17013,7 +17016,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17094,7 +17097,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ78">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR78">
         <v>1.13</v>
@@ -17219,7 +17222,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17631,7 +17634,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17837,7 +17840,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18867,7 +18870,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -19073,7 +19076,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19279,7 +19282,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19357,7 +19360,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ89">
         <v>0.93</v>
@@ -19566,7 +19569,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ90">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR90">
         <v>1.64</v>
@@ -19691,7 +19694,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19897,7 +19900,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20596,7 +20599,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ95">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -20721,7 +20724,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20799,7 +20802,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ96">
         <v>1.79</v>
@@ -21133,7 +21136,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21339,7 +21342,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21545,7 +21548,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21751,7 +21754,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21957,7 +21960,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22450,7 +22453,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ104">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR104">
         <v>1.82</v>
@@ -22653,7 +22656,7 @@
         <v>0.5</v>
       </c>
       <c r="AP105">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ105">
         <v>0.64</v>
@@ -22781,7 +22784,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22987,7 +22990,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23399,7 +23402,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23811,7 +23814,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -23889,7 +23892,7 @@
         <v>1.6</v>
       </c>
       <c r="AP111">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ111">
         <v>1.46</v>
@@ -24098,7 +24101,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ112">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR112">
         <v>1.41</v>
@@ -24429,7 +24432,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24635,7 +24638,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24841,7 +24844,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -25047,7 +25050,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25128,7 +25131,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ117">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR117">
         <v>1.5</v>
@@ -25459,7 +25462,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25871,7 +25874,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26155,7 +26158,7 @@
         <v>1.58</v>
       </c>
       <c r="AP122">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ122">
         <v>1.36</v>
@@ -26695,7 +26698,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -27107,7 +27110,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27185,7 +27188,7 @@
         <v>2</v>
       </c>
       <c r="AP127">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ127">
         <v>2.14</v>
@@ -27313,7 +27316,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27519,7 +27522,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27725,7 +27728,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q130">
         <v>1.8</v>
@@ -27806,7 +27809,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ130">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR130">
         <v>2.1</v>
@@ -28755,7 +28758,7 @@
         <v>172</v>
       </c>
       <c r="P135" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -28961,7 +28964,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29167,7 +29170,7 @@
         <v>81</v>
       </c>
       <c r="P137" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -29373,7 +29376,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q138">
         <v>3.4</v>
@@ -29736,6 +29739,212 @@
       </c>
       <c r="BP139">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7483814</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45755.54166666666</v>
+      </c>
+      <c r="F140">
+        <v>29</v>
+      </c>
+      <c r="G140" t="s">
+        <v>71</v>
+      </c>
+      <c r="H140" t="s">
+        <v>75</v>
+      </c>
+      <c r="I140">
+        <v>2</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>2</v>
+      </c>
+      <c r="L140">
+        <v>4</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>5</v>
+      </c>
+      <c r="O140" t="s">
+        <v>176</v>
+      </c>
+      <c r="P140" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q140">
+        <v>3.3</v>
+      </c>
+      <c r="R140">
+        <v>2</v>
+      </c>
+      <c r="S140">
+        <v>3.2</v>
+      </c>
+      <c r="T140">
+        <v>1.44</v>
+      </c>
+      <c r="U140">
+        <v>2.63</v>
+      </c>
+      <c r="V140">
+        <v>3.25</v>
+      </c>
+      <c r="W140">
+        <v>1.33</v>
+      </c>
+      <c r="X140">
+        <v>7.5</v>
+      </c>
+      <c r="Y140">
+        <v>1.07</v>
+      </c>
+      <c r="Z140">
+        <v>2.64</v>
+      </c>
+      <c r="AA140">
+        <v>3.19</v>
+      </c>
+      <c r="AB140">
+        <v>2.64</v>
+      </c>
+      <c r="AC140">
+        <v>1.06</v>
+      </c>
+      <c r="AD140">
+        <v>8</v>
+      </c>
+      <c r="AE140">
+        <v>1.36</v>
+      </c>
+      <c r="AF140">
+        <v>3</v>
+      </c>
+      <c r="AG140">
+        <v>2.1</v>
+      </c>
+      <c r="AH140">
+        <v>1.61</v>
+      </c>
+      <c r="AI140">
+        <v>1.83</v>
+      </c>
+      <c r="AJ140">
+        <v>1.83</v>
+      </c>
+      <c r="AK140">
+        <v>1.48</v>
+      </c>
+      <c r="AL140">
+        <v>1.28</v>
+      </c>
+      <c r="AM140">
+        <v>1.44</v>
+      </c>
+      <c r="AN140">
+        <v>1.29</v>
+      </c>
+      <c r="AO140">
+        <v>0.29</v>
+      </c>
+      <c r="AP140">
+        <v>1.4</v>
+      </c>
+      <c r="AQ140">
+        <v>0.27</v>
+      </c>
+      <c r="AR140">
+        <v>1.3</v>
+      </c>
+      <c r="AS140">
+        <v>1.24</v>
+      </c>
+      <c r="AT140">
+        <v>2.54</v>
+      </c>
+      <c r="AU140">
+        <v>10</v>
+      </c>
+      <c r="AV140">
+        <v>5</v>
+      </c>
+      <c r="AW140">
+        <v>7</v>
+      </c>
+      <c r="AX140">
+        <v>3</v>
+      </c>
+      <c r="AY140">
+        <v>17</v>
+      </c>
+      <c r="AZ140">
+        <v>8</v>
+      </c>
+      <c r="BA140">
+        <v>1</v>
+      </c>
+      <c r="BB140">
+        <v>9</v>
+      </c>
+      <c r="BC140">
+        <v>10</v>
+      </c>
+      <c r="BD140">
+        <v>1.89</v>
+      </c>
+      <c r="BE140">
+        <v>6.2</v>
+      </c>
+      <c r="BF140">
+        <v>2.34</v>
+      </c>
+      <c r="BG140">
+        <v>1.32</v>
+      </c>
+      <c r="BH140">
+        <v>2.88</v>
+      </c>
+      <c r="BI140">
+        <v>1.68</v>
+      </c>
+      <c r="BJ140">
+        <v>2.14</v>
+      </c>
+      <c r="BK140">
+        <v>2.11</v>
+      </c>
+      <c r="BL140">
+        <v>1.7</v>
+      </c>
+      <c r="BM140">
+        <v>2.69</v>
+      </c>
+      <c r="BN140">
+        <v>1.36</v>
+      </c>
+      <c r="BO140">
+        <v>3.75</v>
+      </c>
+      <c r="BP140">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1104,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP140"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -1647,7 +1647,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ3">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ12">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15">
         <v>0.27</v>
@@ -5149,7 +5149,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ20">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -6176,7 +6176,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ25">
         <v>1.46</v>
@@ -6591,7 +6591,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ27">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR27">
         <v>0.98</v>
@@ -8236,7 +8236,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ35">
         <v>0.79</v>
@@ -9269,7 +9269,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ40">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9678,7 +9678,7 @@
         <v>1.25</v>
       </c>
       <c r="AP42">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ42">
         <v>1.36</v>
@@ -12356,10 +12356,10 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ55">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR55">
         <v>1.92</v>
@@ -14622,7 +14622,7 @@
         <v>0.67</v>
       </c>
       <c r="AP66">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ66">
         <v>0.64</v>
@@ -15655,7 +15655,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ71">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -16270,7 +16270,7 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ74">
         <v>1.46</v>
@@ -16891,7 +16891,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ77">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR77">
         <v>2</v>
@@ -18536,7 +18536,7 @@
         <v>0.86</v>
       </c>
       <c r="AP85">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ85">
         <v>0.57</v>
@@ -19775,7 +19775,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ91">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR91">
         <v>1.34</v>
@@ -20390,7 +20390,7 @@
         <v>1.22</v>
       </c>
       <c r="AP94">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20805,7 +20805,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ96">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -22450,7 +22450,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ104">
         <v>0.27</v>
@@ -23071,7 +23071,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ107">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -24304,7 +24304,7 @@
         <v>1.3</v>
       </c>
       <c r="AP113">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ113">
         <v>1.46</v>
@@ -24719,7 +24719,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ115">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR115">
         <v>1.09</v>
@@ -25543,7 +25543,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ119">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR119">
         <v>1.44</v>
@@ -26570,7 +26570,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ124">
         <v>0.79</v>
@@ -27603,7 +27603,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ129">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR129">
         <v>1.87</v>
@@ -28630,7 +28630,7 @@
         <v>1.46</v>
       </c>
       <c r="AP134">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ134">
         <v>1.36</v>
@@ -29263,31 +29263,31 @@
         <v>3.08</v>
       </c>
       <c r="AU137">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV137">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW137">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX137">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY137">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AZ137">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA137">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB137">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC137">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD137">
         <v>0</v>
@@ -29945,6 +29945,212 @@
       </c>
       <c r="BP140">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7483813</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45756.5</v>
+      </c>
+      <c r="F141">
+        <v>29</v>
+      </c>
+      <c r="G141" t="s">
+        <v>70</v>
+      </c>
+      <c r="H141" t="s">
+        <v>77</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>2</v>
+      </c>
+      <c r="O141" t="s">
+        <v>170</v>
+      </c>
+      <c r="P141" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q141">
+        <v>2</v>
+      </c>
+      <c r="R141">
+        <v>2.3</v>
+      </c>
+      <c r="S141">
+        <v>5.5</v>
+      </c>
+      <c r="T141">
+        <v>1.36</v>
+      </c>
+      <c r="U141">
+        <v>2.9</v>
+      </c>
+      <c r="V141">
+        <v>2.7</v>
+      </c>
+      <c r="W141">
+        <v>1.4</v>
+      </c>
+      <c r="X141">
+        <v>6.7</v>
+      </c>
+      <c r="Y141">
+        <v>1.09</v>
+      </c>
+      <c r="Z141">
+        <v>1.51</v>
+      </c>
+      <c r="AA141">
+        <v>4.1</v>
+      </c>
+      <c r="AB141">
+        <v>6</v>
+      </c>
+      <c r="AC141">
+        <v>1.04</v>
+      </c>
+      <c r="AD141">
+        <v>9</v>
+      </c>
+      <c r="AE141">
+        <v>1.28</v>
+      </c>
+      <c r="AF141">
+        <v>3.45</v>
+      </c>
+      <c r="AG141">
+        <v>1.87</v>
+      </c>
+      <c r="AH141">
+        <v>1.87</v>
+      </c>
+      <c r="AI141">
+        <v>1.95</v>
+      </c>
+      <c r="AJ141">
+        <v>1.7</v>
+      </c>
+      <c r="AK141">
+        <v>1.09</v>
+      </c>
+      <c r="AL141">
+        <v>1.18</v>
+      </c>
+      <c r="AM141">
+        <v>2.45</v>
+      </c>
+      <c r="AN141">
+        <v>2.36</v>
+      </c>
+      <c r="AO141">
+        <v>1.79</v>
+      </c>
+      <c r="AP141">
+        <v>2.27</v>
+      </c>
+      <c r="AQ141">
+        <v>1.73</v>
+      </c>
+      <c r="AR141">
+        <v>1.82</v>
+      </c>
+      <c r="AS141">
+        <v>1.5</v>
+      </c>
+      <c r="AT141">
+        <v>3.32</v>
+      </c>
+      <c r="AU141">
+        <v>-1</v>
+      </c>
+      <c r="AV141">
+        <v>-1</v>
+      </c>
+      <c r="AW141">
+        <v>-1</v>
+      </c>
+      <c r="AX141">
+        <v>-1</v>
+      </c>
+      <c r="AY141">
+        <v>-1</v>
+      </c>
+      <c r="AZ141">
+        <v>-1</v>
+      </c>
+      <c r="BA141">
+        <v>-1</v>
+      </c>
+      <c r="BB141">
+        <v>-1</v>
+      </c>
+      <c r="BC141">
+        <v>-1</v>
+      </c>
+      <c r="BD141">
+        <v>1.28</v>
+      </c>
+      <c r="BE141">
+        <v>10.5</v>
+      </c>
+      <c r="BF141">
+        <v>4.1</v>
+      </c>
+      <c r="BG141">
+        <v>1.28</v>
+      </c>
+      <c r="BH141">
+        <v>3.08</v>
+      </c>
+      <c r="BI141">
+        <v>1.52</v>
+      </c>
+      <c r="BJ141">
+        <v>2.24</v>
+      </c>
+      <c r="BK141">
+        <v>1.92</v>
+      </c>
+      <c r="BL141">
+        <v>1.75</v>
+      </c>
+      <c r="BM141">
+        <v>2.46</v>
+      </c>
+      <c r="BN141">
+        <v>1.43</v>
+      </c>
+      <c r="BO141">
+        <v>3.34</v>
+      </c>
+      <c r="BP141">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -30087,31 +30087,31 @@
         <v>3.32</v>
       </c>
       <c r="AU141">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV141">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW141">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX141">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY141">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AZ141">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA141">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB141">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC141">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD141">
         <v>1.28</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="245">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,9 @@
     <t>['29', '45', '46', '90+3']</t>
   </si>
   <si>
+    <t>['24', '67', '76']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -743,6 +746,9 @@
   </si>
   <si>
     <t>['32', '38']</t>
+  </si>
+  <si>
+    <t>['31', '86']</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1850,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ4">
         <v>0.27</v>
@@ -1978,7 +1984,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
@@ -2059,7 +2065,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ5">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2265,7 +2271,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2596,7 +2602,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3295,7 +3301,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ11">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR11">
         <v>1.27</v>
@@ -3420,7 +3426,7 @@
         <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3498,7 +3504,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12">
         <v>1.73</v>
@@ -3704,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ13">
         <v>1.46</v>
@@ -3913,7 +3919,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR14">
         <v>1.88</v>
@@ -4244,7 +4250,7 @@
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4656,7 +4662,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -5274,7 +5280,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5352,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ21">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR21">
         <v>1.05</v>
@@ -5480,7 +5486,7 @@
         <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5558,10 +5564,10 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ22">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5892,7 +5898,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q24">
         <v>4.6</v>
@@ -6098,7 +6104,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6382,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ26">
         <v>0.57</v>
@@ -6510,7 +6516,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>4.06</v>
@@ -6922,7 +6928,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7334,7 +7340,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -7415,7 +7421,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ31">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR31">
         <v>1.26</v>
@@ -7621,7 +7627,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ32">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -8442,7 +8448,7 @@
         <v>1.2</v>
       </c>
       <c r="AP36">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ36">
         <v>0.93</v>
@@ -8570,7 +8576,7 @@
         <v>81</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>5.5</v>
@@ -8857,7 +8863,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ38">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR38">
         <v>1.19</v>
@@ -8982,7 +8988,7 @@
         <v>108</v>
       </c>
       <c r="P39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>1.8</v>
@@ -9600,7 +9606,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -9681,7 +9687,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ42">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR42">
         <v>2.18</v>
@@ -10012,7 +10018,7 @@
         <v>81</v>
       </c>
       <c r="P44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10218,7 +10224,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10630,7 +10636,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -10708,7 +10714,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47">
         <v>2.14</v>
@@ -10836,7 +10842,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11248,7 +11254,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q50">
         <v>6.1</v>
@@ -11660,7 +11666,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -11738,10 +11744,10 @@
         <v>0.2</v>
       </c>
       <c r="AP52">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ52">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -11944,10 +11950,10 @@
         <v>1.2</v>
       </c>
       <c r="AP53">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR53">
         <v>1.07</v>
@@ -12072,7 +12078,7 @@
         <v>111</v>
       </c>
       <c r="P54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12278,7 +12284,7 @@
         <v>81</v>
       </c>
       <c r="P55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -12484,7 +12490,7 @@
         <v>81</v>
       </c>
       <c r="P56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -12562,7 +12568,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ56">
         <v>0.57</v>
@@ -12690,7 +12696,7 @@
         <v>115</v>
       </c>
       <c r="P57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q57">
         <v>1.95</v>
@@ -12896,7 +12902,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q58">
         <v>8</v>
@@ -13102,7 +13108,7 @@
         <v>116</v>
       </c>
       <c r="P59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13308,7 +13314,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q60">
         <v>3.6</v>
@@ -13514,7 +13520,7 @@
         <v>89</v>
       </c>
       <c r="P61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13720,7 +13726,7 @@
         <v>117</v>
       </c>
       <c r="P62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -13798,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ62">
         <v>0.27</v>
@@ -13926,7 +13932,7 @@
         <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q63">
         <v>4.3</v>
@@ -14004,7 +14010,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ63">
         <v>1.46</v>
@@ -14132,7 +14138,7 @@
         <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14213,7 +14219,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ64">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR64">
         <v>1.37</v>
@@ -14338,7 +14344,7 @@
         <v>120</v>
       </c>
       <c r="P65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14625,7 +14631,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ66">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR66">
         <v>1.87</v>
@@ -15162,7 +15168,7 @@
         <v>123</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15368,7 +15374,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70">
         <v>3.2</v>
@@ -15574,7 +15580,7 @@
         <v>114</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>4.75</v>
@@ -15861,7 +15867,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ72">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR72">
         <v>1.36</v>
@@ -16067,7 +16073,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ73">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16398,7 +16404,7 @@
         <v>125</v>
       </c>
       <c r="P75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q75">
         <v>2.91</v>
@@ -16604,7 +16610,7 @@
         <v>126</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16682,7 +16688,7 @@
         <v>1.14</v>
       </c>
       <c r="AP76">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ76">
         <v>1.46</v>
@@ -17016,7 +17022,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -17222,7 +17228,7 @@
         <v>81</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17300,7 +17306,7 @@
         <v>2.43</v>
       </c>
       <c r="AP79">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ79">
         <v>2.14</v>
@@ -17506,7 +17512,7 @@
         <v>1.71</v>
       </c>
       <c r="AP80">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ80">
         <v>1.46</v>
@@ -17634,7 +17640,7 @@
         <v>130</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17715,7 +17721,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ81">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -17840,7 +17846,7 @@
         <v>131</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q82">
         <v>3.5</v>
@@ -18124,7 +18130,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ83">
         <v>0.79</v>
@@ -18870,7 +18876,7 @@
         <v>134</v>
       </c>
       <c r="P87" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q87">
         <v>1.69</v>
@@ -18951,7 +18957,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ87">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19076,7 +19082,7 @@
         <v>135</v>
       </c>
       <c r="P88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19282,7 +19288,7 @@
         <v>101</v>
       </c>
       <c r="P89" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -19694,7 +19700,7 @@
         <v>137</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>3.75</v>
@@ -19772,7 +19778,7 @@
         <v>1.88</v>
       </c>
       <c r="AP91">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ91">
         <v>1.73</v>
@@ -19900,7 +19906,7 @@
         <v>138</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19981,7 +19987,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ92">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20187,7 +20193,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ93">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20596,7 +20602,7 @@
         <v>0.11</v>
       </c>
       <c r="AP95">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ95">
         <v>0.27</v>
@@ -20724,7 +20730,7 @@
         <v>141</v>
       </c>
       <c r="P96" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21136,7 +21142,7 @@
         <v>143</v>
       </c>
       <c r="P98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q98">
         <v>3.25</v>
@@ -21342,7 +21348,7 @@
         <v>81</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q99">
         <v>3.55</v>
@@ -21548,7 +21554,7 @@
         <v>144</v>
       </c>
       <c r="P100" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q100">
         <v>2.65</v>
@@ -21754,7 +21760,7 @@
         <v>145</v>
       </c>
       <c r="P101" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21960,7 +21966,7 @@
         <v>146</v>
       </c>
       <c r="P102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -22041,7 +22047,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ102">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR102">
         <v>1.84</v>
@@ -22244,7 +22250,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ103">
         <v>1.46</v>
@@ -22659,7 +22665,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ105">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -22784,7 +22790,7 @@
         <v>149</v>
       </c>
       <c r="P106" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22990,7 +22996,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q107">
         <v>2.82</v>
@@ -23402,7 +23408,7 @@
         <v>152</v>
       </c>
       <c r="P109" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q109">
         <v>2.2</v>
@@ -23686,10 +23692,10 @@
         <v>0.45</v>
       </c>
       <c r="AP110">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ110">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR110">
         <v>1.09</v>
@@ -23814,7 +23820,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q111">
         <v>5.2</v>
@@ -24432,7 +24438,7 @@
         <v>154</v>
       </c>
       <c r="P114" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q114">
         <v>3.8</v>
@@ -24510,10 +24516,10 @@
         <v>1.64</v>
       </c>
       <c r="AP114">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ114">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR114">
         <v>1.48</v>
@@ -24638,7 +24644,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -24716,7 +24722,7 @@
         <v>1.91</v>
       </c>
       <c r="AP115">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
         <v>1.73</v>
@@ -24844,7 +24850,7 @@
         <v>156</v>
       </c>
       <c r="P116" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q116">
         <v>5.5</v>
@@ -25050,7 +25056,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q117">
         <v>2.12</v>
@@ -25334,7 +25340,7 @@
         <v>0.64</v>
       </c>
       <c r="AP118">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ118">
         <v>0.57</v>
@@ -25462,7 +25468,7 @@
         <v>159</v>
       </c>
       <c r="P119" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q119">
         <v>3.75</v>
@@ -25874,7 +25880,7 @@
         <v>160</v>
       </c>
       <c r="P121" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -26161,7 +26167,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ122">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR122">
         <v>1.32</v>
@@ -26364,7 +26370,7 @@
         <v>1.73</v>
       </c>
       <c r="AP123">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ123">
         <v>1.46</v>
@@ -26698,7 +26704,7 @@
         <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q125">
         <v>2.85</v>
@@ -26779,7 +26785,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ125">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR125">
         <v>1.44</v>
@@ -26982,7 +26988,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ126">
         <v>0.93</v>
@@ -27110,7 +27116,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q127">
         <v>6.5</v>
@@ -27316,7 +27322,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27397,7 +27403,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ128">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR128">
         <v>1.54</v>
@@ -27522,7 +27528,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27728,7 +27734,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q130">
         <v>1.8</v>
@@ -28424,7 +28430,7 @@
         <v>0.58</v>
       </c>
       <c r="AP133">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ133">
         <v>0.57</v>
@@ -28633,7 +28639,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ134">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR134">
         <v>1.81</v>
@@ -28758,7 +28764,7 @@
         <v>172</v>
       </c>
       <c r="P135" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -28964,7 +28970,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29170,7 +29176,7 @@
         <v>81</v>
       </c>
       <c r="P137" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -29248,7 +29254,7 @@
         <v>2.08</v>
       </c>
       <c r="AP137">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ137">
         <v>2.14</v>
@@ -29376,7 +29382,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q138">
         <v>3.4</v>
@@ -29994,7 +30000,7 @@
         <v>170</v>
       </c>
       <c r="P141" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q141">
         <v>2</v>
@@ -30151,6 +30157,418 @@
       </c>
       <c r="BP141">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7483812</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45757.45833333334</v>
+      </c>
+      <c r="F142">
+        <v>29</v>
+      </c>
+      <c r="G142" t="s">
+        <v>79</v>
+      </c>
+      <c r="H142" t="s">
+        <v>78</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>3</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>3</v>
+      </c>
+      <c r="O142" t="s">
+        <v>177</v>
+      </c>
+      <c r="P142" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q142">
+        <v>0</v>
+      </c>
+      <c r="R142">
+        <v>0</v>
+      </c>
+      <c r="S142">
+        <v>0</v>
+      </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+      <c r="U142">
+        <v>0</v>
+      </c>
+      <c r="V142">
+        <v>0</v>
+      </c>
+      <c r="W142">
+        <v>0</v>
+      </c>
+      <c r="X142">
+        <v>0</v>
+      </c>
+      <c r="Y142">
+        <v>0</v>
+      </c>
+      <c r="Z142">
+        <v>3.25</v>
+      </c>
+      <c r="AA142">
+        <v>3.25</v>
+      </c>
+      <c r="AB142">
+        <v>2.2</v>
+      </c>
+      <c r="AC142">
+        <v>0</v>
+      </c>
+      <c r="AD142">
+        <v>0</v>
+      </c>
+      <c r="AE142">
+        <v>0</v>
+      </c>
+      <c r="AF142">
+        <v>0</v>
+      </c>
+      <c r="AG142">
+        <v>2.15</v>
+      </c>
+      <c r="AH142">
+        <v>1.57</v>
+      </c>
+      <c r="AI142">
+        <v>0</v>
+      </c>
+      <c r="AJ142">
+        <v>0</v>
+      </c>
+      <c r="AK142">
+        <v>0</v>
+      </c>
+      <c r="AL142">
+        <v>0</v>
+      </c>
+      <c r="AM142">
+        <v>0</v>
+      </c>
+      <c r="AN142">
+        <v>1.29</v>
+      </c>
+      <c r="AO142">
+        <v>1.36</v>
+      </c>
+      <c r="AP142">
+        <v>1.4</v>
+      </c>
+      <c r="AQ142">
+        <v>1.27</v>
+      </c>
+      <c r="AR142">
+        <v>1.23</v>
+      </c>
+      <c r="AS142">
+        <v>1.47</v>
+      </c>
+      <c r="AT142">
+        <v>2.7</v>
+      </c>
+      <c r="AU142">
+        <v>-1</v>
+      </c>
+      <c r="AV142">
+        <v>-1</v>
+      </c>
+      <c r="AW142">
+        <v>-1</v>
+      </c>
+      <c r="AX142">
+        <v>-1</v>
+      </c>
+      <c r="AY142">
+        <v>-1</v>
+      </c>
+      <c r="AZ142">
+        <v>-1</v>
+      </c>
+      <c r="BA142">
+        <v>-1</v>
+      </c>
+      <c r="BB142">
+        <v>-1</v>
+      </c>
+      <c r="BC142">
+        <v>-1</v>
+      </c>
+      <c r="BD142">
+        <v>0</v>
+      </c>
+      <c r="BE142">
+        <v>0</v>
+      </c>
+      <c r="BF142">
+        <v>0</v>
+      </c>
+      <c r="BG142">
+        <v>0</v>
+      </c>
+      <c r="BH142">
+        <v>0</v>
+      </c>
+      <c r="BI142">
+        <v>0</v>
+      </c>
+      <c r="BJ142">
+        <v>0</v>
+      </c>
+      <c r="BK142">
+        <v>0</v>
+      </c>
+      <c r="BL142">
+        <v>0</v>
+      </c>
+      <c r="BM142">
+        <v>0</v>
+      </c>
+      <c r="BN142">
+        <v>0</v>
+      </c>
+      <c r="BO142">
+        <v>0</v>
+      </c>
+      <c r="BP142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7483815</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45757.55208333334</v>
+      </c>
+      <c r="F143">
+        <v>29</v>
+      </c>
+      <c r="G143" t="s">
+        <v>72</v>
+      </c>
+      <c r="H143" t="s">
+        <v>76</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>2</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143" t="s">
+        <v>81</v>
+      </c>
+      <c r="P143" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q143">
+        <v>2.45</v>
+      </c>
+      <c r="R143">
+        <v>2.1</v>
+      </c>
+      <c r="S143">
+        <v>4.33</v>
+      </c>
+      <c r="T143">
+        <v>1.4</v>
+      </c>
+      <c r="U143">
+        <v>2.7</v>
+      </c>
+      <c r="V143">
+        <v>2.88</v>
+      </c>
+      <c r="W143">
+        <v>1.36</v>
+      </c>
+      <c r="X143">
+        <v>7.5</v>
+      </c>
+      <c r="Y143">
+        <v>1.07</v>
+      </c>
+      <c r="Z143">
+        <v>1.89</v>
+      </c>
+      <c r="AA143">
+        <v>3.45</v>
+      </c>
+      <c r="AB143">
+        <v>4</v>
+      </c>
+      <c r="AC143">
+        <v>1.06</v>
+      </c>
+      <c r="AD143">
+        <v>8</v>
+      </c>
+      <c r="AE143">
+        <v>1.33</v>
+      </c>
+      <c r="AF143">
+        <v>3.1</v>
+      </c>
+      <c r="AG143">
+        <v>1.91</v>
+      </c>
+      <c r="AH143">
+        <v>1.83</v>
+      </c>
+      <c r="AI143">
+        <v>1.8</v>
+      </c>
+      <c r="AJ143">
+        <v>1.83</v>
+      </c>
+      <c r="AK143">
+        <v>1.2</v>
+      </c>
+      <c r="AL143">
+        <v>1.25</v>
+      </c>
+      <c r="AM143">
+        <v>1.85</v>
+      </c>
+      <c r="AN143">
+        <v>1.57</v>
+      </c>
+      <c r="AO143">
+        <v>0.64</v>
+      </c>
+      <c r="AP143">
+        <v>1.47</v>
+      </c>
+      <c r="AQ143">
+        <v>0.8</v>
+      </c>
+      <c r="AR143">
+        <v>1.51</v>
+      </c>
+      <c r="AS143">
+        <v>1.24</v>
+      </c>
+      <c r="AT143">
+        <v>2.75</v>
+      </c>
+      <c r="AU143">
+        <v>5</v>
+      </c>
+      <c r="AV143">
+        <v>4</v>
+      </c>
+      <c r="AW143">
+        <v>13</v>
+      </c>
+      <c r="AX143">
+        <v>7</v>
+      </c>
+      <c r="AY143">
+        <v>18</v>
+      </c>
+      <c r="AZ143">
+        <v>11</v>
+      </c>
+      <c r="BA143">
+        <v>9</v>
+      </c>
+      <c r="BB143">
+        <v>3</v>
+      </c>
+      <c r="BC143">
+        <v>12</v>
+      </c>
+      <c r="BD143">
+        <v>0</v>
+      </c>
+      <c r="BE143">
+        <v>0</v>
+      </c>
+      <c r="BF143">
+        <v>0</v>
+      </c>
+      <c r="BG143">
+        <v>0</v>
+      </c>
+      <c r="BH143">
+        <v>0</v>
+      </c>
+      <c r="BI143">
+        <v>0</v>
+      </c>
+      <c r="BJ143">
+        <v>0</v>
+      </c>
+      <c r="BK143">
+        <v>0</v>
+      </c>
+      <c r="BL143">
+        <v>0</v>
+      </c>
+      <c r="BM143">
+        <v>0</v>
+      </c>
+      <c r="BN143">
+        <v>0</v>
+      </c>
+      <c r="BO143">
+        <v>0</v>
+      </c>
+      <c r="BP143">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovenia PrvaLiga_20242025.xlsx
@@ -1797,10 +1797,10 @@
         <v>8</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA3">
         <v>3</v>
@@ -2003,10 +2003,10 @@
         <v>6</v>
       </c>
       <c r="AY4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2209,10 +2209,10 @@
         <v>3</v>
       </c>
       <c r="AY5">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA5">
         <v>2</v>
@@ -2415,10 +2415,10 @@
         <v>8</v>
       </c>
       <c r="AY6">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="AZ6">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA6">
         <v>9</v>
@@ -2621,10 +2621,10 @@
         <v>10</v>
       </c>
       <c r="AY7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA7">
         <v>7</v>
@@ -2827,10 +2827,10 @@
         <v>6</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA8">
         <v>6</v>
@@ -3033,10 +3033,10 @@
         <v>7</v>
       </c>
       <c r="AY9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA9">
         <v>1</v>
@@ -3445,10 +3445,10 @@
         <v>9</v>
       </c>
       <c r="AY11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA11">
         <v>2</v>
@@ -3857,10 +3857,10 @@
         <v>3</v>
       </c>
       <c r="AY13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA13">
         <v>2</v>
@@ -4063,10 +4063,10 @@
         <v>5</v>
       </c>
       <c r="AY14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA14">
         <v>6</v>
@@ -4269,10 +4269,10 @@
         <v>5</v>
       </c>
       <c r="AY15">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="AZ15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA15">
         <v>7</v>
@@ -4681,10 +4681,10 @@
         <v>12</v>
       </c>
       <c r="AY17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA17">
         <v>6</v>
@@ -4890,7 +4890,7 @@
         <v>12</v>
       </c>
       <c r="AZ18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA18">
         <v>2</v>
@@ -5093,10 +5093,10 @@
         <v>6</v>
       </c>
       <c r="AY19">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA19">
         <v>2</v>
@@ -5299,10 +5299,10 @@
         <v>9</v>
       </c>
       <c r="AY20">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA20">
         <v>4</v>
@@ -5711,10 +5711,10 @@
         <v>7</v>
       </c>
       <c r="AY22">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AZ22">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA22">
         <v>3</v>
@@ -5917,10 +5917,10 @@
         <v>7</v>
       </c>
       <c r="AY23">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA23">
         <v>6</v>
@@ -6123,10 +6123,10 @@
         <v>5</v>
       </c>
       <c r="AY24">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA24">
         <v>3</v>
@@ -6329,10 +6329,10 @@
         <v>8</v>
       </c>
       <c r="AY25">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA25">
         <v>6</v>
@@ -6535,10 +6535,10 @@
         <v>6</v>
       </c>
       <c r="AY26">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ26">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA26">
         <v>9</v>
@@ -6741,10 +6741,10 @@
         <v>5</v>
       </c>
       <c r="AY27">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA27">
         <v>3</v>
@@ -6947,10 +6947,10 @@
         <v>6</v>
       </c>
       <c r="AY28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA28">
         <v>2</v>
@@ -7359,10 +7359,10 @@
         <v>13</v>
       </c>
       <c r="AY30">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BA30">
         <v>4</v>
@@ -7565,10 +7565,10 @@
         <v>4</v>
       </c>
       <c r="AY31">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA31">
         <v>4</v>
@@ -7771,7 +7771,7 @@
         <v>3</v>
       </c>
       <c r="AY32">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ32">
         <v>8</v>
@@ -8183,10 +8183,10 @@
         <v>6</v>
       </c>
       <c r="AY34">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ34">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA34">
         <v>3</v>
@@ -8392,7 +8392,7 @@
         <v>22</v>
       </c>
       <c r="AZ35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA35">
         <v>7</v>
@@ -8801,10 +8801,10 @@
         <v>5</v>
       </c>
       <c r="AY37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ37">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA37">
         <v>4</v>
@@ -9007,10 +9007,10 @@
         <v>7</v>
       </c>
       <c r="AY38">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ38">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA38">
         <v>4</v>
@@ -9213,10 +9213,10 @@
         <v>5</v>
       </c>
       <c r="AY39">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AZ39">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA39">
         <v>8</v>
@@ -9419,10 +9419,10 @@
         <v>7</v>
       </c>
       <c r="AY40">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ40">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA40">
         <v>3</v>
@@ -9625,10 +9625,10 @@
         <v>8</v>
       </c>
       <c r="AY41">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ41">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA41">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>4</v>
       </c>
       <c r="AZ42">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA42">
         <v>8</v>
@@ -10037,10 +10037,10 @@
         <v>6</v>
       </c>
       <c r="AY43">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ43">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA43">
         <v>4</v>
@@ -10243,10 +10243,10 @@
         <v>8</v>
       </c>
       <c r="AY44">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ44">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA44">
         <v>3</v>
@@ -10449,10 +10449,10 @@
         <v>8</v>
       </c>
       <c r="AY45">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ45">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA45">
         <v>2</v>
@@ -10655,10 +10655,10 @@
         <v>6</v>
       </c>
       <c r="AY46">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA46">
         <v>5</v>
@@ -11067,7 +11067,7 @@
         <v>4</v>
       </c>
       <c r="AY48">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ48">
         <v>12</v>
@@ -11479,10 +11479,10 @@
         <v>9</v>
       </c>
       <c r="AY50">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ50">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA50">
         <v>6</v>
@@ -11891,10 +11891,10 @@
         <v>6</v>
       </c>
       <c r="AY52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ52">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA52">
         <v>4</v>
@@ -13130,7 +13130,7 @@
         <v>11</v>
       </c>
       <c r="AZ58">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA58">
         <v>3</v>
@@ -14160,7 +14160,7 @@
         <v>5</v>
       </c>
       <c r="AZ63">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA63">
         <v>2</v>
@@ -15187,7 +15187,7 @@
         <v>10</v>
       </c>
       <c r="AY68">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ68">
         <v>14</v>
@@ -15396,7 +15396,7 @@
         <v>15</v>
       </c>
       <c r="AZ69">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA69">
         <v>2</v>
@@ -16011,7 +16011,7 @@
         <v>5</v>
       </c>
       <c r="AY72">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ72">
         <v>5</v>
@@ -16426,7 +16426,7 @@
         <v>3</v>
       </c>
       <c r="AZ74">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA74">
         <v>4</v>
@@ -16844,10 +16844,10 @@
         <v>4</v>
       </c>
       <c r="BB76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC76">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD76">
         <v>0</v>
@@ -17453,10 +17453,10 @@
         <v>10</v>
       </c>
       <c r="AY79">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ79">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA79">
         <v>3</v>
@@ -17865,10 +17865,10 @@
         <v>6</v>
       </c>
       <c r="AY81">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ81">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA81">
         <v>4</v>
@@ -18074,7 +18074,7 @@
         <v>9</v>
       </c>
       <c r="AZ82">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA82">
         <v>4</v>
@@ -18483,10 +18483,10 @@
         <v>5</v>
       </c>
       <c r="AY84">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ84">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA84">
         <v>2</v>
@@ -18689,10 +18689,10 @@
         <v>6</v>
       </c>
       <c r="AY85">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ85">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA85">
         <v>13</v>
@@ -18895,10 +18895,10 @@
         <v>5</v>
       </c>
       <c r="AY86">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ86">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA86">
         <v>4</v>
@@ -19101,10 +19101,10 @@
         <v>1</v>
       </c>
       <c r="AY87">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="AZ87">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA87">
         <v>12</v>
@@ -19310,7 +19310,7 @@
         <v>5</v>
       </c>
       <c r="AZ88">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA88">
         <v>4</v>
@@ -19719,10 +19719,10 @@
         <v>2</v>
       </c>
       <c r="AY90">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA90">
         <v>10</v>
@@ -19925,10 +19925,10 @@
         <v>5</v>
       </c>
       <c r="AY91">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ91">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA91">
         <v>8</v>
